--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -741,9 +741,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -883,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2560</v>
+        <v>2515</v>
       </c>
       <c r="D2">
-        <v>0.59</v>
+        <v>-1.76</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -895,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-11.2</v>
+        <v>-12.76</v>
       </c>
       <c r="H2">
-        <v>18.03</v>
+        <v>15.95</v>
       </c>
       <c r="I2">
-        <v>-1.56</v>
+        <v>-1.6</v>
       </c>
       <c r="J2">
-        <v>-7.29</v>
+        <v>-8.51</v>
       </c>
       <c r="K2">
-        <v>-0.64</v>
+        <v>-3.1</v>
       </c>
       <c r="L2">
-        <v>-7.97</v>
+        <v>-9.4</v>
       </c>
       <c r="M2">
-        <v>13.75</v>
+        <v>13.64</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>2552.22</v>
+        <v>2544.02</v>
       </c>
       <c r="Q2">
-        <v>2578.9</v>
+        <v>2571.66</v>
       </c>
       <c r="R2">
-        <v>2608.79</v>
+        <v>2608.11</v>
       </c>
       <c r="S2">
-        <v>2588.3</v>
+        <v>2586.91</v>
       </c>
       <c r="T2">
-        <v>-1.09</v>
+        <v>-2.78</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,43 +947,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>46.09</v>
+        <v>41.71</v>
       </c>
       <c r="Z2">
-        <v>-25.75</v>
+        <v>-27.96</v>
       </c>
       <c r="AA2">
-        <v>-25.08</v>
+        <v>-25.66</v>
       </c>
       <c r="AB2">
-        <v>-0.67</v>
+        <v>-2.3</v>
       </c>
       <c r="AC2">
-        <v>49.7</v>
+        <v>44.48</v>
       </c>
       <c r="AD2">
-        <v>49.42</v>
+        <v>47.48</v>
       </c>
       <c r="AE2">
-        <v>61.96</v>
+        <v>61.52</v>
       </c>
       <c r="AF2">
-        <v>-56.42</v>
+        <v>18.77</v>
       </c>
       <c r="AG2">
-        <v>2693.02</v>
+        <v>2682.5</v>
       </c>
       <c r="AH2">
-        <v>2464.79</v>
+        <v>2460.83</v>
       </c>
       <c r="AI2">
-        <v>2725.6</v>
+        <v>2713.71</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>16.12</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,58 +994,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
       </c>
       <c r="F3">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G3">
-        <v>-27.59</v>
+        <v>-27.79</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-2.92</v>
+        <v>-1.75</v>
       </c>
       <c r="J3">
-        <v>-11.39</v>
+        <v>-10.87</v>
       </c>
       <c r="K3">
-        <v>-2.59</v>
+        <v>-2.75</v>
       </c>
       <c r="L3">
-        <v>-26.61</v>
+        <v>-26.27</v>
       </c>
       <c r="M3">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P3">
-        <v>734.66</v>
+        <v>732.0599999999999</v>
       </c>
       <c r="Q3">
-        <v>759.33</v>
+        <v>755.3099999999999</v>
       </c>
       <c r="R3">
-        <v>773.4400000000001</v>
+        <v>773.16</v>
       </c>
       <c r="S3">
-        <v>865.61</v>
+        <v>864.22</v>
       </c>
       <c r="T3">
-        <v>-15.55</v>
+        <v>-15.65</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1062,43 +1060,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.46</v>
+        <v>33.75</v>
       </c>
       <c r="Z3">
-        <v>-14.9</v>
+        <v>-15.06</v>
       </c>
       <c r="AA3">
-        <v>-12.38</v>
+        <v>-12.91</v>
       </c>
       <c r="AB3">
-        <v>-2.52</v>
+        <v>-2.14</v>
       </c>
       <c r="AC3">
-        <v>29.64</v>
+        <v>24.76</v>
       </c>
       <c r="AD3">
-        <v>26.31</v>
+        <v>26.61</v>
       </c>
       <c r="AE3">
-        <v>12.66</v>
+        <v>12.07</v>
       </c>
       <c r="AF3">
-        <v>-20.16</v>
+        <v>-2.57</v>
       </c>
       <c r="AG3">
-        <v>818.96</v>
+        <v>811.46</v>
       </c>
       <c r="AH3">
-        <v>699.7</v>
+        <v>699.15</v>
       </c>
       <c r="AI3">
-        <v>770.9</v>
+        <v>764.91</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>43.31</v>
+        <v>44.34</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="E4">
         <v>796.55</v>
@@ -1121,46 +1119,46 @@
         <v>535.95</v>
       </c>
       <c r="G4">
-        <v>-32.21</v>
+        <v>-32.71</v>
       </c>
       <c r="H4">
-        <v>0.76</v>
+        <v>0.01</v>
       </c>
       <c r="I4">
-        <v>-2.37</v>
+        <v>0.01</v>
       </c>
       <c r="J4">
-        <v>-4.88</v>
+        <v>-6.52</v>
       </c>
       <c r="K4">
-        <v>-10.27</v>
+        <v>-11.08</v>
       </c>
       <c r="L4">
-        <v>-27.01</v>
+        <v>-27.42</v>
       </c>
       <c r="M4">
-        <v>-4</v>
+        <v>-4.03</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>540.6900000000001</v>
+        <v>540.7</v>
       </c>
       <c r="Q4">
-        <v>552.9400000000001</v>
+        <v>551.98</v>
       </c>
       <c r="R4">
-        <v>565.39</v>
+        <v>564.38</v>
       </c>
       <c r="S4">
-        <v>661.53</v>
+        <v>660.49</v>
       </c>
       <c r="T4">
-        <v>-18.37</v>
+        <v>-18.85</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,43 +1173,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.58</v>
+        <v>37.57</v>
       </c>
       <c r="Z4">
-        <v>-8.1</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="AA4">
-        <v>-7.47</v>
+        <v>-7.65</v>
       </c>
       <c r="AB4">
-        <v>-0.63</v>
+        <v>-0.73</v>
       </c>
       <c r="AC4">
-        <v>43.48</v>
+        <v>33.1</v>
       </c>
       <c r="AD4">
-        <v>43.77</v>
+        <v>42.4</v>
       </c>
       <c r="AE4">
-        <v>11.25</v>
+        <v>11.03</v>
       </c>
       <c r="AF4">
-        <v>-0.68</v>
+        <v>-7.22</v>
       </c>
       <c r="AG4">
-        <v>571.9400000000001</v>
+        <v>572.38</v>
       </c>
       <c r="AH4">
-        <v>533.9299999999999</v>
+        <v>531.5700000000001</v>
       </c>
       <c r="AI4">
-        <v>570.17</v>
+        <v>569.55</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>33.92</v>
+        <v>37.42</v>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1409,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.02</v>
+        <v>-7.29</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.29</v>
+        <v>-8.51</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.27</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.59</v>
+        <v>-11.39</v>
       </c>
       <c r="D8" s="5">
-        <v>-11.39</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-0.8</v>
+        <v>-10.87</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-2.15</v>
+        <v>-4.88</v>
       </c>
       <c r="D9" s="5">
-        <v>-4.88</v>
+        <v>-6.52</v>
       </c>
       <c r="E9" s="6">
-        <v>-2.73</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-2.71</v>
+        <v>-1.56</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.15</v>
+        <v>-1.6</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-2.29</v>
+        <v>-2.92</v>
       </c>
       <c r="D11" s="5">
-        <v>-2.92</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.63</v>
+        <v>-1.75</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-1.55</v>
+        <v>-2.37</v>
       </c>
       <c r="D12" s="5">
-        <v>-2.37</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.82</v>
+        <v>0.01</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.38</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-7.37</v>
+        <v>-7.97</v>
       </c>
       <c r="D13" s="5">
-        <v>-7.97</v>
+        <v>-9.4</v>
       </c>
       <c r="E13" s="6">
-        <v>-0.6</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-27.34</v>
+        <v>-26.61</v>
       </c>
       <c r="D14" s="5">
-        <v>-26.61</v>
+        <v>-26.27</v>
       </c>
       <c r="E14" s="7">
-        <v>0.73</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-27.19</v>
+        <v>-27.01</v>
       </c>
       <c r="D15" s="5">
-        <v>-27.01</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.18</v>
+        <v>-27.42</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.33</v>
+        <v>-0.64</v>
       </c>
       <c r="D16" s="5">
-        <v>-0.64</v>
-      </c>
-      <c r="E16" s="7">
-        <v>4.69</v>
+        <v>-3.1</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-4.28</v>
+        <v>-2.59</v>
       </c>
       <c r="D17" s="5">
-        <v>-2.59</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.69</v>
+        <v>-2.75</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-13.28</v>
+        <v>-10.27</v>
       </c>
       <c r="D18" s="5">
-        <v>-10.27</v>
-      </c>
-      <c r="E18" s="7">
-        <v>3.01</v>
+        <v>-11.08</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,47 +1611,47 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-11.72</v>
+        <v>-11.2</v>
       </c>
       <c r="D19" s="5">
-        <v>-11.2</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.52</v>
+        <v>-12.76</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>2545</v>
+        <v>-27.59</v>
       </c>
       <c r="D20" s="5">
-        <v>2560</v>
-      </c>
-      <c r="E20" s="7">
-        <v>15</v>
+        <v>-27.79</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>44.28</v>
+        <v>-32.21</v>
       </c>
       <c r="D21" s="5">
-        <v>46.09</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.81</v>
+        <v>-32.71</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1661,16 +1659,16 @@
         <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>-67.29000000000001</v>
+        <v>2560</v>
       </c>
       <c r="D22" s="5">
-        <v>-56.42</v>
-      </c>
-      <c r="E22" s="7">
-        <v>10.87</v>
+        <v>2515</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-45</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1678,16 +1676,16 @@
         <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>-36.7</v>
+        <v>731</v>
       </c>
       <c r="D23" s="5">
-        <v>-20.16</v>
-      </c>
-      <c r="E23" s="7">
-        <v>16.54</v>
+        <v>729</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1695,16 +1693,118 @@
         <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>540</v>
+      </c>
+      <c r="D24" s="5">
+        <v>536</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>46.09</v>
+      </c>
+      <c r="D25" s="5">
+        <v>41.71</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-4.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>34.46</v>
+      </c>
+      <c r="D26" s="5">
+        <v>33.75</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>39.58</v>
+      </c>
+      <c r="D27" s="5">
+        <v>37.57</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="5">
-        <v>-67.68000000000001</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C28" s="5">
+        <v>-56.42</v>
+      </c>
+      <c r="D28" s="5">
+        <v>18.77</v>
+      </c>
+      <c r="E28" s="7">
+        <v>75.19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-20.16</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-2.57</v>
+      </c>
+      <c r="E29" s="7">
+        <v>17.59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
         <v>-0.68</v>
       </c>
-      <c r="E24" s="7">
-        <v>67</v>
+      <c r="D30" s="5">
+        <v>-7.22</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-6.54</v>
       </c>
     </row>
   </sheetData>
@@ -1769,16 +1869,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>40</v>
+        <v>37.7</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-7.9</v>
+        <v>-8.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-4.5</v>
+        <v>-5.6</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1897,13 +1997,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1375</v>
+        <v>0.1364</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0039</v>
+        <v>0.005</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.04</v>
+        <v>-0.0403</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,7 +741,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -881,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2515</v>
+        <v>2490</v>
       </c>
       <c r="D2">
-        <v>-1.76</v>
+        <v>-0.99</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -893,46 +895,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-12.76</v>
+        <v>-13.63</v>
       </c>
       <c r="H2">
-        <v>15.95</v>
+        <v>14.8</v>
       </c>
       <c r="I2">
-        <v>-1.6</v>
+        <v>-2.81</v>
       </c>
       <c r="J2">
-        <v>-8.51</v>
+        <v>-6.38</v>
       </c>
       <c r="K2">
-        <v>-3.1</v>
+        <v>-5.47</v>
       </c>
       <c r="L2">
-        <v>-9.4</v>
+        <v>-10.42</v>
       </c>
       <c r="M2">
-        <v>13.64</v>
+        <v>13.23</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P2">
-        <v>2544.02</v>
+        <v>2529.62</v>
       </c>
       <c r="Q2">
-        <v>2571.66</v>
+        <v>2559.7</v>
       </c>
       <c r="R2">
-        <v>2608.11</v>
+        <v>2607.34</v>
       </c>
       <c r="S2">
-        <v>2586.91</v>
+        <v>2585.64</v>
       </c>
       <c r="T2">
-        <v>-2.78</v>
+        <v>-3.7</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +949,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>41.71</v>
+        <v>39.47</v>
       </c>
       <c r="Z2">
-        <v>-27.96</v>
+        <v>-31.36</v>
       </c>
       <c r="AA2">
-        <v>-25.66</v>
+        <v>-26.8</v>
       </c>
       <c r="AB2">
-        <v>-2.3</v>
+        <v>-4.56</v>
       </c>
       <c r="AC2">
-        <v>44.48</v>
+        <v>30.2</v>
       </c>
       <c r="AD2">
-        <v>47.48</v>
+        <v>41.46</v>
       </c>
       <c r="AE2">
-        <v>61.52</v>
+        <v>59.82</v>
       </c>
       <c r="AF2">
-        <v>18.77</v>
+        <v>1.19</v>
       </c>
       <c r="AG2">
-        <v>2682.5</v>
+        <v>2648.37</v>
       </c>
       <c r="AH2">
-        <v>2460.83</v>
+        <v>2471.04</v>
       </c>
       <c r="AI2">
-        <v>2713.71</v>
+        <v>2680.61</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>15.08</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,7 +999,7 @@
         <v>729</v>
       </c>
       <c r="D3">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1012,19 +1014,19 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-1.75</v>
+        <v>-0.82</v>
       </c>
       <c r="J3">
-        <v>-10.87</v>
+        <v>-9.93</v>
       </c>
       <c r="K3">
-        <v>-2.75</v>
+        <v>-5.27</v>
       </c>
       <c r="L3">
-        <v>-26.27</v>
+        <v>-26.56</v>
       </c>
       <c r="M3">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="N3">
         <v>66</v>
@@ -1033,19 +1035,19 @@
         <v>18</v>
       </c>
       <c r="P3">
-        <v>732.0599999999999</v>
+        <v>730.86</v>
       </c>
       <c r="Q3">
-        <v>755.3099999999999</v>
+        <v>750.99</v>
       </c>
       <c r="R3">
-        <v>773.16</v>
+        <v>772.78</v>
       </c>
       <c r="S3">
-        <v>864.22</v>
+        <v>862.8200000000001</v>
       </c>
       <c r="T3">
-        <v>-15.65</v>
+        <v>-15.51</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,40 +1065,40 @@
         <v>33.75</v>
       </c>
       <c r="Z3">
-        <v>-15.06</v>
+        <v>-15.01</v>
       </c>
       <c r="AA3">
-        <v>-12.91</v>
+        <v>-13.33</v>
       </c>
       <c r="AB3">
-        <v>-2.14</v>
+        <v>-1.68</v>
       </c>
       <c r="AC3">
-        <v>24.76</v>
+        <v>22.33</v>
       </c>
       <c r="AD3">
-        <v>26.61</v>
+        <v>25.58</v>
       </c>
       <c r="AE3">
-        <v>12.07</v>
+        <v>11.83</v>
       </c>
       <c r="AF3">
-        <v>-2.57</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AG3">
-        <v>811.46</v>
+        <v>800.5700000000001</v>
       </c>
       <c r="AH3">
-        <v>699.15</v>
+        <v>701.4</v>
       </c>
       <c r="AI3">
-        <v>764.91</v>
+        <v>761.8</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>44.34</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D4">
-        <v>-0.74</v>
+        <v>0.19</v>
       </c>
       <c r="E4">
         <v>796.55</v>
@@ -1119,46 +1121,46 @@
         <v>535.95</v>
       </c>
       <c r="G4">
-        <v>-32.71</v>
+        <v>-32.58</v>
       </c>
       <c r="H4">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="I4">
-        <v>0.01</v>
+        <v>-1.47</v>
       </c>
       <c r="J4">
-        <v>-6.52</v>
+        <v>-3.28</v>
       </c>
       <c r="K4">
-        <v>-11.08</v>
+        <v>-12.33</v>
       </c>
       <c r="L4">
-        <v>-27.42</v>
+        <v>-28.64</v>
       </c>
       <c r="M4">
-        <v>-4.03</v>
+        <v>-4.24</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P4">
-        <v>540.7</v>
+        <v>539.1</v>
       </c>
       <c r="Q4">
-        <v>551.98</v>
+        <v>550.39</v>
       </c>
       <c r="R4">
-        <v>564.38</v>
+        <v>563.52</v>
       </c>
       <c r="S4">
-        <v>660.49</v>
+        <v>659.46</v>
       </c>
       <c r="T4">
-        <v>-18.85</v>
+        <v>-18.57</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,43 +1175,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.57</v>
+        <v>38.41</v>
       </c>
       <c r="Z4">
-        <v>-8.380000000000001</v>
+        <v>-8.43</v>
       </c>
       <c r="AA4">
-        <v>-7.65</v>
+        <v>-7.81</v>
       </c>
       <c r="AB4">
-        <v>-0.73</v>
+        <v>-0.62</v>
       </c>
       <c r="AC4">
-        <v>33.1</v>
+        <v>28.97</v>
       </c>
       <c r="AD4">
-        <v>42.4</v>
+        <v>35.18</v>
       </c>
       <c r="AE4">
-        <v>11.03</v>
+        <v>10.69</v>
       </c>
       <c r="AF4">
-        <v>-7.22</v>
+        <v>-40.05</v>
       </c>
       <c r="AG4">
-        <v>572.38</v>
+        <v>570.23</v>
       </c>
       <c r="AH4">
-        <v>531.5700000000001</v>
+        <v>530.54</v>
       </c>
       <c r="AI4">
-        <v>569.55</v>
+        <v>566.65</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>37.42</v>
+        <v>40.66</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1407,13 +1409,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.29</v>
+        <v>-8.51</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.51</v>
+        <v>-6.38</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.22</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1426,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-11.39</v>
+        <v>-10.87</v>
       </c>
       <c r="D8" s="5">
-        <v>-10.87</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.52</v>
+        <v>-9.93</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-4.88</v>
+        <v>-6.52</v>
       </c>
       <c r="D9" s="5">
-        <v>-6.52</v>
+        <v>-3.28</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.64</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1460,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.56</v>
+        <v>-1.6</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.04</v>
+        <v>-2.81</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1477,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-2.92</v>
+        <v>-1.75</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.75</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.17</v>
+        <v>-0.82</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.93</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1494,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-2.37</v>
+        <v>0.01</v>
       </c>
       <c r="D12" s="5">
-        <v>0.01</v>
+        <v>-1.47</v>
       </c>
       <c r="E12" s="7">
-        <v>2.38</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1511,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-7.97</v>
+        <v>-9.4</v>
       </c>
       <c r="D13" s="5">
-        <v>-9.4</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-1.43</v>
+        <v>-10.42</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1528,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-26.61</v>
+        <v>-26.27</v>
       </c>
       <c r="D14" s="5">
-        <v>-26.27</v>
+        <v>-26.56</v>
       </c>
       <c r="E14" s="7">
-        <v>0.34</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1545,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-27.01</v>
+        <v>-27.42</v>
       </c>
       <c r="D15" s="5">
-        <v>-27.42</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.41</v>
+        <v>-28.64</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-0.64</v>
+        <v>-3.1</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.1</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.46</v>
+        <v>-5.47</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1579,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-2.59</v>
+        <v>-2.75</v>
       </c>
       <c r="D17" s="5">
-        <v>-2.75</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.16</v>
+        <v>-5.27</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.52</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1596,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-10.27</v>
+        <v>-11.08</v>
       </c>
       <c r="D18" s="5">
-        <v>-11.08</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.8100000000000001</v>
+        <v>-12.33</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,81 +1613,81 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-11.2</v>
+        <v>-12.76</v>
       </c>
       <c r="D19" s="5">
-        <v>-12.76</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.56</v>
+        <v>-13.63</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-27.59</v>
+        <v>-32.71</v>
       </c>
       <c r="D20" s="5">
-        <v>-27.79</v>
+        <v>-32.58</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.2</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21" s="5">
-        <v>-32.21</v>
+        <v>2515</v>
       </c>
       <c r="D21" s="5">
-        <v>-32.71</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.5</v>
+        <v>2490</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-25</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2560</v>
+        <v>536</v>
       </c>
       <c r="D22" s="5">
-        <v>2515</v>
+        <v>537</v>
       </c>
       <c r="E22" s="6">
-        <v>-45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C23" s="5">
-        <v>731</v>
+        <v>41.71</v>
       </c>
       <c r="D23" s="5">
-        <v>729</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2</v>
+        <v>39.47</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1693,16 +1695,16 @@
         <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C24" s="5">
-        <v>540</v>
+        <v>37.57</v>
       </c>
       <c r="D24" s="5">
-        <v>536</v>
+        <v>38.41</v>
       </c>
       <c r="E24" s="6">
-        <v>-4</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1710,16 +1712,16 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C25" s="5">
-        <v>46.09</v>
+        <v>18.77</v>
       </c>
       <c r="D25" s="5">
-        <v>41.71</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-4.38</v>
+        <v>1.19</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-17.58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1727,16 +1729,16 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C26" s="5">
-        <v>34.46</v>
+        <v>-2.57</v>
       </c>
       <c r="D26" s="5">
-        <v>33.75</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.71</v>
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-7.4</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1744,67 +1746,16 @@
         <v>39</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C27" s="5">
-        <v>39.58</v>
+        <v>-7.22</v>
       </c>
       <c r="D27" s="5">
-        <v>37.57</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-56.42</v>
-      </c>
-      <c r="D28" s="5">
-        <v>18.77</v>
-      </c>
-      <c r="E28" s="7">
-        <v>75.19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-20.16</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-2.57</v>
-      </c>
-      <c r="E29" s="7">
-        <v>17.59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-0.68</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-7.22</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-6.54</v>
+        <v>-40.05</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-32.83</v>
       </c>
     </row>
   </sheetData>
@@ -1869,16 +1820,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>37.7</v>
+        <v>37.2</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.6</v>
+        <v>-6.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-5.6</v>
+        <v>-7.7</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1997,13 +1948,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1364</v>
+        <v>0.1323</v>
       </c>
       <c r="B2" s="13">
-        <v>0.005</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0403</v>
+        <v>-0.0424</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,9 +741,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -883,10 +882,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2490</v>
+        <v>2499.5</v>
       </c>
       <c r="D2">
-        <v>-0.99</v>
+        <v>0.38</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -895,46 +894,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-13.63</v>
+        <v>-13.3</v>
       </c>
       <c r="H2">
-        <v>14.8</v>
+        <v>15.24</v>
       </c>
       <c r="I2">
-        <v>-2.81</v>
+        <v>-1.52</v>
       </c>
       <c r="J2">
-        <v>-6.38</v>
+        <v>-8.42</v>
       </c>
       <c r="K2">
-        <v>-5.47</v>
+        <v>-5.52</v>
       </c>
       <c r="L2">
-        <v>-10.42</v>
+        <v>-9.82</v>
       </c>
       <c r="M2">
-        <v>13.23</v>
+        <v>13.56</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P2">
-        <v>2529.62</v>
+        <v>2521.9</v>
       </c>
       <c r="Q2">
-        <v>2559.7</v>
+        <v>2554.57</v>
       </c>
       <c r="R2">
-        <v>2607.34</v>
+        <v>2608.21</v>
       </c>
       <c r="S2">
-        <v>2585.64</v>
+        <v>2584.57</v>
       </c>
       <c r="T2">
-        <v>-3.7</v>
+        <v>-3.29</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,43 +948,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>39.47</v>
+        <v>40.77</v>
       </c>
       <c r="Z2">
-        <v>-31.36</v>
+        <v>-32.91</v>
       </c>
       <c r="AA2">
-        <v>-26.8</v>
+        <v>-28.02</v>
       </c>
       <c r="AB2">
-        <v>-4.56</v>
+        <v>-4.89</v>
       </c>
       <c r="AC2">
-        <v>30.2</v>
+        <v>13.28</v>
       </c>
       <c r="AD2">
-        <v>41.46</v>
+        <v>29.32</v>
       </c>
       <c r="AE2">
-        <v>59.82</v>
+        <v>57.32</v>
       </c>
       <c r="AF2">
-        <v>1.19</v>
+        <v>-17.29</v>
       </c>
       <c r="AG2">
-        <v>2648.37</v>
+        <v>2644.75</v>
       </c>
       <c r="AH2">
-        <v>2471.04</v>
+        <v>2464.39</v>
       </c>
       <c r="AI2">
-        <v>2680.61</v>
+        <v>2662.55</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>15.89</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,58 +995,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
       </c>
       <c r="F3">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="G3">
-        <v>-27.79</v>
+        <v>-28.18</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.82</v>
+        <v>-1.27</v>
       </c>
       <c r="J3">
-        <v>-9.93</v>
+        <v>-11.09</v>
       </c>
       <c r="K3">
-        <v>-5.27</v>
+        <v>-5.54</v>
       </c>
       <c r="L3">
-        <v>-26.56</v>
+        <v>-27.33</v>
       </c>
       <c r="M3">
-        <v>0.41</v>
+        <v>-0.03</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P3">
-        <v>730.86</v>
+        <v>729</v>
       </c>
       <c r="Q3">
-        <v>750.99</v>
+        <v>746.8200000000001</v>
       </c>
       <c r="R3">
-        <v>772.78</v>
+        <v>772.21</v>
       </c>
       <c r="S3">
-        <v>862.8200000000001</v>
+        <v>861.47</v>
       </c>
       <c r="T3">
-        <v>-15.51</v>
+        <v>-15.84</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1062,43 +1061,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.75</v>
+        <v>32.2</v>
       </c>
       <c r="Z3">
-        <v>-15.01</v>
+        <v>-15.12</v>
       </c>
       <c r="AA3">
-        <v>-13.33</v>
+        <v>-13.69</v>
       </c>
       <c r="AB3">
-        <v>-1.68</v>
+        <v>-1.43</v>
       </c>
       <c r="AC3">
-        <v>22.33</v>
+        <v>14.63</v>
       </c>
       <c r="AD3">
-        <v>25.58</v>
+        <v>20.58</v>
       </c>
       <c r="AE3">
-        <v>11.83</v>
+        <v>11.3</v>
       </c>
       <c r="AF3">
-        <v>-9.970000000000001</v>
+        <v>-26.46</v>
       </c>
       <c r="AG3">
-        <v>800.5700000000001</v>
+        <v>789.67</v>
       </c>
       <c r="AH3">
-        <v>701.4</v>
+        <v>703.97</v>
       </c>
       <c r="AI3">
-        <v>761.8</v>
+        <v>760.66</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>46.07</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1108,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>537</v>
+        <v>538.05</v>
       </c>
       <c r="D4">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="E4">
         <v>796.55</v>
@@ -1121,46 +1120,46 @@
         <v>535.95</v>
       </c>
       <c r="G4">
-        <v>-32.58</v>
+        <v>-32.45</v>
       </c>
       <c r="H4">
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="I4">
-        <v>-1.47</v>
+        <v>-0.82</v>
       </c>
       <c r="J4">
-        <v>-3.28</v>
+        <v>-5.4</v>
       </c>
       <c r="K4">
-        <v>-12.33</v>
+        <v>-11.61</v>
       </c>
       <c r="L4">
-        <v>-28.64</v>
+        <v>-28.8</v>
       </c>
       <c r="M4">
-        <v>-4.24</v>
+        <v>-4.07</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>539.1</v>
+        <v>538.21</v>
       </c>
       <c r="Q4">
-        <v>550.39</v>
+        <v>548.91</v>
       </c>
       <c r="R4">
-        <v>563.52</v>
+        <v>562.8</v>
       </c>
       <c r="S4">
-        <v>659.46</v>
+        <v>658.47</v>
       </c>
       <c r="T4">
-        <v>-18.57</v>
+        <v>-18.29</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.41</v>
+        <v>39.33</v>
       </c>
       <c r="Z4">
-        <v>-8.43</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AA4">
-        <v>-7.81</v>
+        <v>-7.9</v>
       </c>
       <c r="AB4">
-        <v>-0.62</v>
+        <v>-0.38</v>
       </c>
       <c r="AC4">
-        <v>28.97</v>
+        <v>28.11</v>
       </c>
       <c r="AD4">
-        <v>35.18</v>
+        <v>30.06</v>
       </c>
       <c r="AE4">
-        <v>10.69</v>
+        <v>10.41</v>
       </c>
       <c r="AF4">
-        <v>-40.05</v>
+        <v>-58.61</v>
       </c>
       <c r="AG4">
-        <v>570.23</v>
+        <v>567.73</v>
       </c>
       <c r="AH4">
-        <v>530.54</v>
+        <v>530.09</v>
       </c>
       <c r="AI4">
         <v>566.65</v>
@@ -1211,7 +1210,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>40.66</v>
+        <v>41.71</v>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1409,13 +1408,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.51</v>
+        <v>-6.38</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.38</v>
+        <v>-8.42</v>
       </c>
       <c r="E7" s="6">
-        <v>2.13</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1425,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.87</v>
+        <v>-9.93</v>
       </c>
       <c r="D8" s="5">
-        <v>-9.93</v>
+        <v>-11.09</v>
       </c>
       <c r="E8" s="6">
-        <v>0.9399999999999999</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1442,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.52</v>
+        <v>-3.28</v>
       </c>
       <c r="D9" s="5">
-        <v>-3.28</v>
+        <v>-5.4</v>
       </c>
       <c r="E9" s="6">
-        <v>3.24</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1459,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.6</v>
+        <v>-2.81</v>
       </c>
       <c r="D10" s="5">
-        <v>-2.81</v>
+        <v>-1.52</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.21</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1476,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.75</v>
+        <v>-0.82</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.82</v>
+        <v>-1.27</v>
       </c>
       <c r="E11" s="6">
-        <v>0.93</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1493,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>0.01</v>
+        <v>-1.47</v>
       </c>
       <c r="D12" s="5">
-        <v>-1.47</v>
+        <v>-0.82</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.48</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1510,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-9.4</v>
+        <v>-10.42</v>
       </c>
       <c r="D13" s="5">
-        <v>-10.42</v>
+        <v>-9.82</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.02</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1527,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-26.27</v>
+        <v>-26.56</v>
       </c>
       <c r="D14" s="5">
-        <v>-26.56</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.29</v>
+        <v>-27.33</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1544,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-27.42</v>
+        <v>-28.64</v>
       </c>
       <c r="D15" s="5">
-        <v>-28.64</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.22</v>
+        <v>-28.8</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1561,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.1</v>
+        <v>-5.47</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.47</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.37</v>
+        <v>-5.52</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1578,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-2.75</v>
+        <v>-5.27</v>
       </c>
       <c r="D17" s="5">
-        <v>-5.27</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.52</v>
+        <v>-5.54</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1595,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-11.08</v>
+        <v>-12.33</v>
       </c>
       <c r="D18" s="5">
-        <v>-12.33</v>
+        <v>-11.61</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.25</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,81 +1612,81 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-12.76</v>
+        <v>-13.63</v>
       </c>
       <c r="D19" s="5">
-        <v>-13.63</v>
+        <v>-13.3</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.87</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-32.71</v>
+        <v>-27.79</v>
       </c>
       <c r="D20" s="5">
-        <v>-32.58</v>
+        <v>-28.18</v>
       </c>
       <c r="E20" s="6">
-        <v>0.13</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>2515</v>
+        <v>-32.58</v>
       </c>
       <c r="D21" s="5">
-        <v>2490</v>
+        <v>-32.45</v>
       </c>
       <c r="E21" s="7">
-        <v>-25</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>536</v>
+        <v>2490</v>
       </c>
       <c r="D22" s="5">
-        <v>537</v>
-      </c>
-      <c r="E22" s="6">
-        <v>1</v>
+        <v>2499.5</v>
+      </c>
+      <c r="E22" s="7">
+        <v>9.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>41.71</v>
+        <v>729</v>
       </c>
       <c r="D23" s="5">
-        <v>39.47</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.24</v>
+        <v>725</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1695,16 +1694,16 @@
         <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>37.57</v>
+        <v>537</v>
       </c>
       <c r="D24" s="5">
-        <v>38.41</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.84</v>
+        <v>538.05</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1712,16 +1711,16 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>18.77</v>
+        <v>39.47</v>
       </c>
       <c r="D25" s="5">
-        <v>1.19</v>
+        <v>40.77</v>
       </c>
       <c r="E25" s="7">
-        <v>-17.58</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1729,16 +1728,16 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>-2.57</v>
+        <v>33.75</v>
       </c>
       <c r="D26" s="5">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-7.4</v>
+        <v>32.2</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1746,16 +1745,67 @@
         <v>39</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>38.41</v>
+      </c>
+      <c r="D27" s="5">
+        <v>39.33</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="5">
-        <v>-7.22</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-17.29</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-18.48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-26.46</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-16.49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
         <v>-40.05</v>
       </c>
-      <c r="E27" s="7">
-        <v>-32.83</v>
+      <c r="D30" s="5">
+        <v>-58.61</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-18.56</v>
       </c>
     </row>
   </sheetData>
@@ -1820,16 +1870,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.5</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.7</v>
+        <v>-7.6</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1948,13 +1998,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1323</v>
+        <v>0.1356</v>
       </c>
       <c r="B2" s="13">
-        <v>0.004099999999999999</v>
+        <v>-0.0003</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0424</v>
+        <v>-0.0407</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -882,10 +882,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2499.5</v>
+        <v>2485</v>
       </c>
       <c r="D2">
-        <v>0.38</v>
+        <v>-0.58</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -894,25 +894,25 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-13.3</v>
+        <v>-13.8</v>
       </c>
       <c r="H2">
-        <v>15.24</v>
+        <v>14.57</v>
       </c>
       <c r="I2">
-        <v>-1.52</v>
+        <v>-2.36</v>
       </c>
       <c r="J2">
-        <v>-8.42</v>
+        <v>-4.5</v>
       </c>
       <c r="K2">
-        <v>-5.52</v>
+        <v>-3.27</v>
       </c>
       <c r="L2">
-        <v>-9.82</v>
+        <v>-8.69</v>
       </c>
       <c r="M2">
-        <v>13.56</v>
+        <v>13.36</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -921,19 +921,19 @@
         <v>37</v>
       </c>
       <c r="P2">
-        <v>2521.9</v>
+        <v>2509.9</v>
       </c>
       <c r="Q2">
-        <v>2554.57</v>
+        <v>2546.26</v>
       </c>
       <c r="R2">
-        <v>2608.21</v>
+        <v>2608.53</v>
       </c>
       <c r="S2">
-        <v>2584.57</v>
+        <v>2583.4</v>
       </c>
       <c r="T2">
-        <v>-3.29</v>
+        <v>-3.81</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -948,43 +948,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>40.77</v>
+        <v>39.38</v>
       </c>
       <c r="Z2">
-        <v>-32.91</v>
+        <v>-34.91</v>
       </c>
       <c r="AA2">
-        <v>-28.02</v>
+        <v>-29.4</v>
       </c>
       <c r="AB2">
-        <v>-4.89</v>
+        <v>-5.51</v>
       </c>
       <c r="AC2">
-        <v>13.28</v>
+        <v>5.32</v>
       </c>
       <c r="AD2">
-        <v>29.32</v>
+        <v>16.27</v>
       </c>
       <c r="AE2">
-        <v>57.32</v>
+        <v>55.87</v>
       </c>
       <c r="AF2">
-        <v>-17.29</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="AG2">
-        <v>2644.75</v>
+        <v>2629.3</v>
       </c>
       <c r="AH2">
-        <v>2464.39</v>
+        <v>2463.22</v>
       </c>
       <c r="AI2">
-        <v>2662.55</v>
+        <v>2656.3</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>16.9</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -995,10 +995,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D3">
-        <v>-0.55</v>
+        <v>0.28</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1007,22 +1007,22 @@
         <v>725</v>
       </c>
       <c r="G3">
-        <v>-28.18</v>
+        <v>-27.98</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="I3">
-        <v>-1.27</v>
+        <v>-0.55</v>
       </c>
       <c r="J3">
-        <v>-11.09</v>
+        <v>-10.06</v>
       </c>
       <c r="K3">
-        <v>-5.54</v>
+        <v>-5.42</v>
       </c>
       <c r="L3">
-        <v>-27.33</v>
+        <v>-26.34</v>
       </c>
       <c r="M3">
         <v>-0.03</v>
@@ -1034,19 +1034,19 @@
         <v>17</v>
       </c>
       <c r="P3">
-        <v>729</v>
+        <v>728.2</v>
       </c>
       <c r="Q3">
-        <v>746.8200000000001</v>
+        <v>742.1900000000001</v>
       </c>
       <c r="R3">
-        <v>772.21</v>
+        <v>771.66</v>
       </c>
       <c r="S3">
-        <v>861.47</v>
+        <v>860.09</v>
       </c>
       <c r="T3">
-        <v>-15.84</v>
+        <v>-15.47</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1061,43 +1061,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>32.2</v>
+        <v>33.83</v>
       </c>
       <c r="Z3">
-        <v>-15.12</v>
+        <v>-14.88</v>
       </c>
       <c r="AA3">
-        <v>-13.69</v>
+        <v>-13.93</v>
       </c>
       <c r="AB3">
-        <v>-1.43</v>
+        <v>-0.95</v>
       </c>
       <c r="AC3">
-        <v>14.63</v>
+        <v>14.92</v>
       </c>
       <c r="AD3">
-        <v>20.58</v>
+        <v>17.3</v>
       </c>
       <c r="AE3">
-        <v>11.3</v>
+        <v>10.93</v>
       </c>
       <c r="AF3">
-        <v>-26.46</v>
+        <v>-32.31</v>
       </c>
       <c r="AG3">
-        <v>789.67</v>
+        <v>768.9</v>
       </c>
       <c r="AH3">
-        <v>703.97</v>
+        <v>715.48</v>
       </c>
       <c r="AI3">
-        <v>760.66</v>
+        <v>759.34</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>47.58</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1108,58 +1108,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>538.05</v>
+        <v>535.85</v>
       </c>
       <c r="D4">
-        <v>0.2</v>
+        <v>-0.41</v>
       </c>
       <c r="E4">
         <v>796.55</v>
       </c>
       <c r="F4">
-        <v>535.95</v>
+        <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-32.45</v>
+        <v>-32.73</v>
       </c>
       <c r="H4">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.82</v>
+        <v>-0.77</v>
       </c>
       <c r="J4">
-        <v>-5.4</v>
+        <v>-5.59</v>
       </c>
       <c r="K4">
-        <v>-11.61</v>
+        <v>-11.42</v>
       </c>
       <c r="L4">
-        <v>-28.8</v>
+        <v>-29.64</v>
       </c>
       <c r="M4">
-        <v>-4.07</v>
+        <v>-4.24</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>538.21</v>
+        <v>537.38</v>
       </c>
       <c r="Q4">
-        <v>548.91</v>
+        <v>547.52</v>
       </c>
       <c r="R4">
-        <v>562.8</v>
+        <v>562.04</v>
       </c>
       <c r="S4">
-        <v>658.47</v>
+        <v>657.46</v>
       </c>
       <c r="T4">
-        <v>-18.29</v>
+        <v>-18.5</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1174,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.33</v>
+        <v>38.05</v>
       </c>
       <c r="Z4">
-        <v>-8.279999999999999</v>
+        <v>-8.25</v>
       </c>
       <c r="AA4">
-        <v>-7.9</v>
+        <v>-7.97</v>
       </c>
       <c r="AB4">
-        <v>-0.38</v>
+        <v>-0.28</v>
       </c>
       <c r="AC4">
-        <v>28.11</v>
+        <v>29.8</v>
       </c>
       <c r="AD4">
-        <v>30.06</v>
+        <v>28.96</v>
       </c>
       <c r="AE4">
-        <v>10.41</v>
+        <v>9.98</v>
       </c>
       <c r="AF4">
-        <v>-58.61</v>
+        <v>-77.95</v>
       </c>
       <c r="AG4">
-        <v>567.73</v>
+        <v>565.86</v>
       </c>
       <c r="AH4">
-        <v>530.09</v>
+        <v>529.1799999999999</v>
       </c>
       <c r="AI4">
         <v>566.65</v>
@@ -1210,7 +1210,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>41.71</v>
+        <v>42.34</v>
       </c>
     </row>
   </sheetData>
@@ -1408,13 +1408,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.38</v>
+        <v>-8.42</v>
       </c>
       <c r="D7" s="5">
-        <v>-8.42</v>
+        <v>-4.5</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.04</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1425,13 +1425,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-9.93</v>
+        <v>-11.09</v>
       </c>
       <c r="D8" s="5">
-        <v>-11.09</v>
+        <v>-10.06</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.16</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1442,13 +1442,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-3.28</v>
+        <v>-5.4</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.4</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-2.12</v>
+        <v>-5.59</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1459,13 +1459,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-2.81</v>
+        <v>-1.52</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.52</v>
+        <v>-2.36</v>
       </c>
       <c r="E10" s="7">
-        <v>1.29</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1476,13 +1476,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.82</v>
+        <v>-1.27</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.27</v>
+        <v>-0.55</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.45</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1493,13 +1493,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-1.47</v>
+        <v>-0.82</v>
       </c>
       <c r="D12" s="5">
-        <v>-0.82</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.65</v>
+        <v>-0.77</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1510,13 +1510,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-10.42</v>
+        <v>-9.82</v>
       </c>
       <c r="D13" s="5">
-        <v>-9.82</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.6</v>
+        <v>-8.69</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.13</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1527,13 +1527,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-26.56</v>
+        <v>-27.33</v>
       </c>
       <c r="D14" s="5">
-        <v>-27.33</v>
+        <v>-26.34</v>
       </c>
       <c r="E14" s="6">
-        <v>-0.77</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1544,13 +1544,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-28.64</v>
+        <v>-28.8</v>
       </c>
       <c r="D15" s="5">
-        <v>-28.8</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.16</v>
+        <v>-29.64</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1561,13 +1561,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.47</v>
+        <v>-5.52</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.52</v>
+        <v>-3.27</v>
       </c>
       <c r="E16" s="6">
-        <v>-0.05</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-5.27</v>
+        <v>-5.54</v>
       </c>
       <c r="D17" s="5">
-        <v>-5.54</v>
+        <v>-5.42</v>
       </c>
       <c r="E17" s="6">
-        <v>-0.27</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-12.33</v>
+        <v>-11.61</v>
       </c>
       <c r="D18" s="5">
-        <v>-11.61</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.72</v>
+        <v>-11.42</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.19</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-13.63</v>
+        <v>-13.3</v>
       </c>
       <c r="D19" s="5">
-        <v>-13.3</v>
+        <v>-13.8</v>
       </c>
       <c r="E19" s="7">
-        <v>0.33</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1629,13 +1629,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-27.79</v>
+        <v>-28.18</v>
       </c>
       <c r="D20" s="5">
-        <v>-28.18</v>
+        <v>-27.98</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.39</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1646,13 +1646,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-32.58</v>
+        <v>-32.45</v>
       </c>
       <c r="D21" s="5">
-        <v>-32.45</v>
+        <v>-32.73</v>
       </c>
       <c r="E21" s="7">
-        <v>0.13</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1663,13 +1663,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2490</v>
+        <v>2499.5</v>
       </c>
       <c r="D22" s="5">
-        <v>2499.5</v>
+        <v>2485</v>
       </c>
       <c r="E22" s="7">
-        <v>9.5</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1680,13 +1680,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D23" s="5">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E23" s="6">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1697,13 +1697,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>537</v>
+        <v>538.05</v>
       </c>
       <c r="D24" s="5">
-        <v>538.05</v>
+        <v>535.85</v>
       </c>
       <c r="E24" s="7">
-        <v>1.05</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1714,13 +1714,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>39.47</v>
+        <v>40.77</v>
       </c>
       <c r="D25" s="5">
-        <v>40.77</v>
+        <v>39.38</v>
       </c>
       <c r="E25" s="7">
-        <v>1.3</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1731,13 +1731,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>33.75</v>
+        <v>32.2</v>
       </c>
       <c r="D26" s="5">
-        <v>32.2</v>
+        <v>33.83</v>
       </c>
       <c r="E26" s="6">
-        <v>-1.55</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1748,13 +1748,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>38.41</v>
+        <v>39.33</v>
       </c>
       <c r="D27" s="5">
-        <v>39.33</v>
+        <v>38.05</v>
       </c>
       <c r="E27" s="7">
-        <v>0.92</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1765,13 +1765,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>1.19</v>
+        <v>-17.29</v>
       </c>
       <c r="D28" s="5">
-        <v>-17.29</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="E28" s="6">
-        <v>-18.48</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1782,13 +1782,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-9.970000000000001</v>
+        <v>-26.46</v>
       </c>
       <c r="D29" s="5">
-        <v>-26.46</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-16.49</v>
+        <v>-32.31</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-5.85</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1799,13 +1799,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-40.05</v>
+        <v>-58.61</v>
       </c>
       <c r="D30" s="5">
-        <v>-58.61</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-18.56</v>
+        <v>-77.95</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-19.34</v>
       </c>
     </row>
   </sheetData>
@@ -1870,16 +1870,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>37.4</v>
+        <v>37.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.300000000000001</v>
+        <v>-6.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.6</v>
+        <v>-6.7</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1356</v>
+        <v>0.1336</v>
       </c>
       <c r="B2" s="13">
         <v>-0.0003</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0407</v>
+        <v>-0.0424</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -882,10 +882,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2485</v>
+        <v>2523</v>
       </c>
       <c r="D2">
-        <v>-0.58</v>
+        <v>1.53</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -894,46 +894,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-13.8</v>
+        <v>-12.49</v>
       </c>
       <c r="H2">
-        <v>14.57</v>
+        <v>16.32</v>
       </c>
       <c r="I2">
-        <v>-2.36</v>
+        <v>-1.45</v>
       </c>
       <c r="J2">
-        <v>-4.5</v>
+        <v>-4.84</v>
       </c>
       <c r="K2">
-        <v>-3.27</v>
+        <v>-2.84</v>
       </c>
       <c r="L2">
-        <v>-8.69</v>
+        <v>-6.26</v>
       </c>
       <c r="M2">
-        <v>13.36</v>
+        <v>13.47</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>2509.9</v>
+        <v>2502.5</v>
       </c>
       <c r="Q2">
-        <v>2546.26</v>
+        <v>2540.17</v>
       </c>
       <c r="R2">
-        <v>2608.53</v>
+        <v>2609.07</v>
       </c>
       <c r="S2">
-        <v>2583.4</v>
+        <v>2582.2</v>
       </c>
       <c r="T2">
-        <v>-3.81</v>
+        <v>-2.29</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -948,34 +948,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>39.38</v>
+        <v>44.71</v>
       </c>
       <c r="Z2">
-        <v>-34.91</v>
+        <v>-33.04</v>
       </c>
       <c r="AA2">
-        <v>-29.4</v>
+        <v>-30.13</v>
       </c>
       <c r="AB2">
-        <v>-5.51</v>
+        <v>-2.92</v>
       </c>
       <c r="AC2">
-        <v>5.32</v>
+        <v>20.36</v>
       </c>
       <c r="AD2">
-        <v>16.27</v>
+        <v>12.99</v>
       </c>
       <c r="AE2">
-        <v>55.87</v>
+        <v>56.76</v>
       </c>
       <c r="AF2">
-        <v>90.51000000000001</v>
+        <v>-22.55</v>
       </c>
       <c r="AG2">
-        <v>2629.3</v>
+        <v>2609.48</v>
       </c>
       <c r="AH2">
-        <v>2463.22</v>
+        <v>2470.85</v>
       </c>
       <c r="AI2">
         <v>2656.3</v>
@@ -984,7 +984,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>18.4</v>
+        <v>16.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -995,7 +995,7 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D3">
         <v>0.28</v>
@@ -1007,46 +1007,46 @@
         <v>725</v>
       </c>
       <c r="G3">
-        <v>-27.98</v>
+        <v>-27.79</v>
       </c>
       <c r="H3">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
       <c r="I3">
-        <v>-0.55</v>
+        <v>-0.27</v>
       </c>
       <c r="J3">
-        <v>-10.06</v>
+        <v>-11.05</v>
       </c>
       <c r="K3">
-        <v>-5.42</v>
+        <v>-4.39</v>
       </c>
       <c r="L3">
-        <v>-26.34</v>
+        <v>-26.94</v>
       </c>
       <c r="M3">
-        <v>-0.03</v>
+        <v>0.24</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P3">
-        <v>728.2</v>
+        <v>727.8</v>
       </c>
       <c r="Q3">
-        <v>742.1900000000001</v>
+        <v>739.76</v>
       </c>
       <c r="R3">
-        <v>771.66</v>
+        <v>771.3</v>
       </c>
       <c r="S3">
-        <v>860.09</v>
+        <v>858.72</v>
       </c>
       <c r="T3">
-        <v>-15.47</v>
+        <v>-15.11</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1061,34 +1061,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.83</v>
+        <v>35.51</v>
       </c>
       <c r="Z3">
-        <v>-14.88</v>
+        <v>-14.36</v>
       </c>
       <c r="AA3">
-        <v>-13.93</v>
+        <v>-14.01</v>
       </c>
       <c r="AB3">
-        <v>-0.95</v>
+        <v>-0.34</v>
       </c>
       <c r="AC3">
-        <v>14.92</v>
+        <v>20.03</v>
       </c>
       <c r="AD3">
-        <v>17.3</v>
+        <v>16.53</v>
       </c>
       <c r="AE3">
-        <v>10.93</v>
+        <v>10.69</v>
       </c>
       <c r="AF3">
-        <v>-32.31</v>
+        <v>-50.82</v>
       </c>
       <c r="AG3">
-        <v>768.9</v>
+        <v>761.24</v>
       </c>
       <c r="AH3">
-        <v>715.48</v>
+        <v>718.28</v>
       </c>
       <c r="AI3">
         <v>759.34</v>
@@ -1097,7 +1097,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>49.09</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1108,10 +1108,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>535.85</v>
+        <v>543</v>
       </c>
       <c r="D4">
-        <v>-0.41</v>
+        <v>1.33</v>
       </c>
       <c r="E4">
         <v>796.55</v>
@@ -1120,46 +1120,46 @@
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-32.73</v>
+        <v>-31.83</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="I4">
-        <v>-0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J4">
-        <v>-5.59</v>
+        <v>-3.66</v>
       </c>
       <c r="K4">
-        <v>-11.42</v>
+        <v>-11.04</v>
       </c>
       <c r="L4">
-        <v>-29.64</v>
+        <v>-29</v>
       </c>
       <c r="M4">
-        <v>-4.24</v>
+        <v>-3.86</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P4">
-        <v>537.38</v>
+        <v>537.98</v>
       </c>
       <c r="Q4">
-        <v>547.52</v>
+        <v>546.4400000000001</v>
       </c>
       <c r="R4">
-        <v>562.04</v>
+        <v>561.39</v>
       </c>
       <c r="S4">
-        <v>657.46</v>
+        <v>656.4400000000001</v>
       </c>
       <c r="T4">
-        <v>-18.5</v>
+        <v>-17.28</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1174,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.05</v>
+        <v>44.4</v>
       </c>
       <c r="Z4">
-        <v>-8.25</v>
+        <v>-7.56</v>
       </c>
       <c r="AA4">
-        <v>-7.97</v>
+        <v>-7.89</v>
       </c>
       <c r="AB4">
-        <v>-0.28</v>
+        <v>0.33</v>
       </c>
       <c r="AC4">
-        <v>29.8</v>
+        <v>53.86</v>
       </c>
       <c r="AD4">
-        <v>28.96</v>
+        <v>37.26</v>
       </c>
       <c r="AE4">
-        <v>9.98</v>
+        <v>9.94</v>
       </c>
       <c r="AF4">
-        <v>-77.95</v>
+        <v>-6.62</v>
       </c>
       <c r="AG4">
-        <v>565.86</v>
+        <v>562.99</v>
       </c>
       <c r="AH4">
-        <v>529.1799999999999</v>
+        <v>529.88</v>
       </c>
       <c r="AI4">
         <v>566.65</v>
@@ -1210,7 +1210,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>42.34</v>
+        <v>39.16</v>
       </c>
     </row>
   </sheetData>
@@ -1408,13 +1408,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.42</v>
+        <v>-4.5</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.5</v>
+        <v>-4.84</v>
       </c>
       <c r="E7" s="6">
-        <v>3.92</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1425,13 +1425,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-11.09</v>
+        <v>-10.06</v>
       </c>
       <c r="D8" s="5">
-        <v>-10.06</v>
+        <v>-11.05</v>
       </c>
       <c r="E8" s="6">
-        <v>1.03</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1442,13 +1442,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.4</v>
+        <v>-5.59</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.59</v>
+        <v>-3.66</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.19</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1459,13 +1459,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.52</v>
+        <v>-2.36</v>
       </c>
       <c r="D10" s="5">
-        <v>-2.36</v>
+        <v>-1.45</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.84</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1476,13 +1476,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.27</v>
+        <v>-0.55</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.55</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.72</v>
+        <v>-0.27</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1493,13 +1493,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-0.82</v>
+        <v>-0.77</v>
       </c>
       <c r="D12" s="5">
-        <v>-0.77</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.05</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.33</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1510,13 +1510,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-9.82</v>
+        <v>-8.69</v>
       </c>
       <c r="D13" s="5">
-        <v>-8.69</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1.13</v>
+        <v>-6.26</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1527,13 +1527,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-27.33</v>
+        <v>-26.34</v>
       </c>
       <c r="D14" s="5">
-        <v>-26.34</v>
+        <v>-26.94</v>
       </c>
       <c r="E14" s="6">
-        <v>0.99</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1544,13 +1544,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-28.8</v>
+        <v>-29.64</v>
       </c>
       <c r="D15" s="5">
-        <v>-29.64</v>
+        <v>-29</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.84</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1561,13 +1561,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-5.52</v>
+        <v>-3.27</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.27</v>
-      </c>
-      <c r="E16" s="6">
-        <v>2.25</v>
+        <v>-2.84</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-5.54</v>
+        <v>-5.42</v>
       </c>
       <c r="D17" s="5">
-        <v>-5.42</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.12</v>
+        <v>-4.39</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.03</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-11.61</v>
+        <v>-11.42</v>
       </c>
       <c r="D18" s="5">
-        <v>-11.42</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.19</v>
+        <v>-11.04</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.38</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-13.3</v>
+        <v>-13.8</v>
       </c>
       <c r="D19" s="5">
-        <v>-13.8</v>
+        <v>-12.49</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.5</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1629,13 +1629,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-28.18</v>
+        <v>-27.98</v>
       </c>
       <c r="D20" s="5">
-        <v>-27.98</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.2</v>
+        <v>-27.79</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.19</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1646,13 +1646,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-32.45</v>
+        <v>-32.73</v>
       </c>
       <c r="D21" s="5">
-        <v>-32.73</v>
+        <v>-31.83</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.28</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1663,13 +1663,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2499.5</v>
+        <v>2485</v>
       </c>
       <c r="D22" s="5">
-        <v>2485</v>
+        <v>2523</v>
       </c>
       <c r="E22" s="7">
-        <v>-14.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1680,12 +1680,12 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D23" s="5">
-        <v>727</v>
-      </c>
-      <c r="E23" s="6">
+        <v>729</v>
+      </c>
+      <c r="E23" s="7">
         <v>2</v>
       </c>
     </row>
@@ -1697,13 +1697,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>538.05</v>
+        <v>535.85</v>
       </c>
       <c r="D24" s="5">
-        <v>535.85</v>
+        <v>543</v>
       </c>
       <c r="E24" s="7">
-        <v>-2.2</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1714,13 +1714,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>40.77</v>
+        <v>39.38</v>
       </c>
       <c r="D25" s="5">
-        <v>39.38</v>
+        <v>44.71</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.39</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1731,13 +1731,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>32.2</v>
+        <v>33.83</v>
       </c>
       <c r="D26" s="5">
-        <v>33.83</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1.63</v>
+        <v>35.51</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.68</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1748,13 +1748,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>39.33</v>
+        <v>38.05</v>
       </c>
       <c r="D27" s="5">
-        <v>38.05</v>
+        <v>44.4</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.28</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1765,13 +1765,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-17.29</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="D28" s="5">
-        <v>90.51000000000001</v>
+        <v>-22.55</v>
       </c>
       <c r="E28" s="6">
-        <v>107.8</v>
+        <v>-113.06</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1782,13 +1782,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-26.46</v>
+        <v>-32.31</v>
       </c>
       <c r="D29" s="5">
-        <v>-32.31</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-5.85</v>
+        <v>-50.82</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-18.51</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1799,13 +1799,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-58.61</v>
+        <v>-77.95</v>
       </c>
       <c r="D30" s="5">
-        <v>-77.95</v>
+        <v>-6.62</v>
       </c>
       <c r="E30" s="7">
-        <v>-19.34</v>
+        <v>71.33</v>
       </c>
     </row>
   </sheetData>
@@ -1870,16 +1870,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>37.1</v>
+        <v>41.5</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.7</v>
+        <v>-6.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-6.7</v>
+        <v>-6.1</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1336</v>
+        <v>0.1347</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0003</v>
+        <v>0.0024</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0424</v>
+        <v>-0.0386</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -882,10 +882,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="D2">
-        <v>1.53</v>
+        <v>0.08</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -894,25 +894,25 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-12.49</v>
+        <v>-12.42</v>
       </c>
       <c r="H2">
-        <v>16.32</v>
+        <v>16.42</v>
       </c>
       <c r="I2">
-        <v>-1.45</v>
+        <v>0.4</v>
       </c>
       <c r="J2">
-        <v>-4.84</v>
+        <v>-4.53</v>
       </c>
       <c r="K2">
-        <v>-2.84</v>
+        <v>-3.91</v>
       </c>
       <c r="L2">
-        <v>-6.26</v>
+        <v>-5.59</v>
       </c>
       <c r="M2">
-        <v>13.47</v>
+        <v>13.35</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -921,19 +921,19 @@
         <v>39</v>
       </c>
       <c r="P2">
-        <v>2502.5</v>
+        <v>2504.5</v>
       </c>
       <c r="Q2">
-        <v>2540.17</v>
+        <v>2537.36</v>
       </c>
       <c r="R2">
-        <v>2609.07</v>
+        <v>2610.51</v>
       </c>
       <c r="S2">
-        <v>2582.2</v>
+        <v>2581.62</v>
       </c>
       <c r="T2">
-        <v>-2.29</v>
+        <v>-2.19</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -948,34 +948,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>44.71</v>
+        <v>44.99</v>
       </c>
       <c r="Z2">
-        <v>-33.04</v>
+        <v>-31.05</v>
       </c>
       <c r="AA2">
-        <v>-30.13</v>
+        <v>-30.31</v>
       </c>
       <c r="AB2">
-        <v>-2.92</v>
+        <v>-0.74</v>
       </c>
       <c r="AC2">
-        <v>20.36</v>
+        <v>33.51</v>
       </c>
       <c r="AD2">
-        <v>12.99</v>
+        <v>19.73</v>
       </c>
       <c r="AE2">
-        <v>56.76</v>
+        <v>55.96</v>
       </c>
       <c r="AF2">
-        <v>-22.55</v>
+        <v>-6.01</v>
       </c>
       <c r="AG2">
-        <v>2609.48</v>
+        <v>2604.2</v>
       </c>
       <c r="AH2">
-        <v>2470.85</v>
+        <v>2470.52</v>
       </c>
       <c r="AI2">
         <v>2656.3</v>
@@ -984,7 +984,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>16.01</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -995,58 +995,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="D3">
-        <v>0.28</v>
+        <v>-0.82</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
       </c>
       <c r="F3">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G3">
-        <v>-27.79</v>
+        <v>-28.38</v>
       </c>
       <c r="H3">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.27</v>
+        <v>-0.82</v>
       </c>
       <c r="J3">
-        <v>-11.05</v>
+        <v>-7.02</v>
       </c>
       <c r="K3">
-        <v>-4.39</v>
+        <v>-4.81</v>
       </c>
       <c r="L3">
-        <v>-26.94</v>
+        <v>-26.6</v>
       </c>
       <c r="M3">
-        <v>0.24</v>
+        <v>0.09</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P3">
-        <v>727.8</v>
+        <v>726.6</v>
       </c>
       <c r="Q3">
-        <v>739.76</v>
+        <v>737.84</v>
       </c>
       <c r="R3">
-        <v>771.3</v>
+        <v>770.99</v>
       </c>
       <c r="S3">
-        <v>858.72</v>
+        <v>857.29</v>
       </c>
       <c r="T3">
-        <v>-15.11</v>
+        <v>-15.66</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1061,43 +1061,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.51</v>
+        <v>32.83</v>
       </c>
       <c r="Z3">
-        <v>-14.36</v>
+        <v>-14.27</v>
       </c>
       <c r="AA3">
-        <v>-14.01</v>
+        <v>-14.06</v>
       </c>
       <c r="AB3">
-        <v>-0.34</v>
+        <v>-0.2</v>
       </c>
       <c r="AC3">
-        <v>20.03</v>
+        <v>20.89</v>
       </c>
       <c r="AD3">
-        <v>16.53</v>
+        <v>18.62</v>
       </c>
       <c r="AE3">
-        <v>10.69</v>
+        <v>10.36</v>
       </c>
       <c r="AF3">
-        <v>-50.82</v>
+        <v>-40.86</v>
       </c>
       <c r="AG3">
-        <v>761.24</v>
+        <v>757.98</v>
       </c>
       <c r="AH3">
-        <v>718.28</v>
+        <v>717.6900000000001</v>
       </c>
       <c r="AI3">
-        <v>759.34</v>
+        <v>757.0700000000001</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>48.38</v>
+        <v>48.23</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1108,10 +1108,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>543</v>
+        <v>538.25</v>
       </c>
       <c r="D4">
-        <v>1.33</v>
+        <v>-0.87</v>
       </c>
       <c r="E4">
         <v>796.55</v>
@@ -1120,46 +1120,46 @@
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-31.83</v>
+        <v>-32.43</v>
       </c>
       <c r="H4">
-        <v>1.33</v>
+        <v>0.45</v>
       </c>
       <c r="I4">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="J4">
-        <v>-3.66</v>
+        <v>-4.68</v>
       </c>
       <c r="K4">
-        <v>-11.04</v>
+        <v>-11.05</v>
       </c>
       <c r="L4">
-        <v>-29</v>
+        <v>-29.75</v>
       </c>
       <c r="M4">
-        <v>-3.86</v>
+        <v>-4.08</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>537.98</v>
+        <v>538.4299999999999</v>
       </c>
       <c r="Q4">
-        <v>546.4400000000001</v>
+        <v>545.3</v>
       </c>
       <c r="R4">
-        <v>561.39</v>
+        <v>560.87</v>
       </c>
       <c r="S4">
-        <v>656.4400000000001</v>
+        <v>655.33</v>
       </c>
       <c r="T4">
-        <v>-17.28</v>
+        <v>-17.87</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1174,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>44.4</v>
+        <v>41.37</v>
       </c>
       <c r="Z4">
-        <v>-7.56</v>
+        <v>-7.31</v>
       </c>
       <c r="AA4">
-        <v>-7.89</v>
+        <v>-7.77</v>
       </c>
       <c r="AB4">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="AC4">
-        <v>53.86</v>
+        <v>62.88</v>
       </c>
       <c r="AD4">
-        <v>37.26</v>
+        <v>48.85</v>
       </c>
       <c r="AE4">
-        <v>9.94</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AF4">
-        <v>-6.62</v>
+        <v>-61.34</v>
       </c>
       <c r="AG4">
-        <v>562.99</v>
+        <v>560.73</v>
       </c>
       <c r="AH4">
-        <v>529.88</v>
+        <v>529.87</v>
       </c>
       <c r="AI4">
         <v>566.65</v>
@@ -1210,7 +1210,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>39.16</v>
+        <v>36.4</v>
       </c>
     </row>
   </sheetData>
@@ -1411,10 +1411,10 @@
         <v>-4.5</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.84</v>
+        <v>-4.53</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.34</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1428,10 +1428,10 @@
         <v>-10.06</v>
       </c>
       <c r="D8" s="5">
-        <v>-11.05</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-0.99</v>
+        <v>-7.02</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3.04</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1445,10 +1445,10 @@
         <v>-5.59</v>
       </c>
       <c r="D9" s="5">
-        <v>-3.66</v>
+        <v>-4.68</v>
       </c>
       <c r="E9" s="7">
-        <v>1.93</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1462,10 +1462,10 @@
         <v>-2.36</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.45</v>
+        <v>0.4</v>
       </c>
       <c r="E10" s="7">
-        <v>0.91</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1479,10 +1479,10 @@
         <v>-0.55</v>
       </c>
       <c r="D11" s="5">
+        <v>-0.82</v>
+      </c>
+      <c r="E11" s="6">
         <v>-0.27</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1496,10 +1496,10 @@
         <v>-0.77</v>
       </c>
       <c r="D12" s="5">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="E12" s="7">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1513,10 +1513,10 @@
         <v>-8.69</v>
       </c>
       <c r="D13" s="5">
-        <v>-6.26</v>
+        <v>-5.59</v>
       </c>
       <c r="E13" s="7">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1530,10 +1530,10 @@
         <v>-26.34</v>
       </c>
       <c r="D14" s="5">
-        <v>-26.94</v>
+        <v>-26.6</v>
       </c>
       <c r="E14" s="6">
-        <v>-0.6</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1547,10 +1547,10 @@
         <v>-29.64</v>
       </c>
       <c r="D15" s="5">
-        <v>-29</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.64</v>
+        <v>-29.75</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1564,10 +1564,10 @@
         <v>-3.27</v>
       </c>
       <c r="D16" s="5">
-        <v>-2.84</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.43</v>
+        <v>-3.91</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1581,10 +1581,10 @@
         <v>-5.42</v>
       </c>
       <c r="D17" s="5">
-        <v>-4.39</v>
+        <v>-4.81</v>
       </c>
       <c r="E17" s="7">
-        <v>1.03</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1598,10 +1598,10 @@
         <v>-11.42</v>
       </c>
       <c r="D18" s="5">
-        <v>-11.04</v>
+        <v>-11.05</v>
       </c>
       <c r="E18" s="7">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1615,10 +1615,10 @@
         <v>-13.8</v>
       </c>
       <c r="D19" s="5">
-        <v>-12.49</v>
+        <v>-12.42</v>
       </c>
       <c r="E19" s="7">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1632,10 +1632,10 @@
         <v>-27.98</v>
       </c>
       <c r="D20" s="5">
-        <v>-27.79</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.19</v>
+        <v>-28.38</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1649,10 +1649,10 @@
         <v>-32.73</v>
       </c>
       <c r="D21" s="5">
-        <v>-31.83</v>
+        <v>-32.43</v>
       </c>
       <c r="E21" s="7">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1666,10 +1666,10 @@
         <v>2485</v>
       </c>
       <c r="D22" s="5">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="E22" s="7">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1683,10 +1683,10 @@
         <v>727</v>
       </c>
       <c r="D23" s="5">
-        <v>729</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2</v>
+        <v>723</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1700,10 +1700,10 @@
         <v>535.85</v>
       </c>
       <c r="D24" s="5">
-        <v>543</v>
+        <v>538.25</v>
       </c>
       <c r="E24" s="7">
-        <v>7.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1717,10 +1717,10 @@
         <v>39.38</v>
       </c>
       <c r="D25" s="5">
-        <v>44.71</v>
+        <v>44.99</v>
       </c>
       <c r="E25" s="7">
-        <v>5.33</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1734,10 +1734,10 @@
         <v>33.83</v>
       </c>
       <c r="D26" s="5">
-        <v>35.51</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.68</v>
+        <v>32.83</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1751,10 +1751,10 @@
         <v>38.05</v>
       </c>
       <c r="D27" s="5">
-        <v>44.4</v>
+        <v>41.37</v>
       </c>
       <c r="E27" s="7">
-        <v>6.35</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1768,10 +1768,10 @@
         <v>90.51000000000001</v>
       </c>
       <c r="D28" s="5">
-        <v>-22.55</v>
+        <v>-6.01</v>
       </c>
       <c r="E28" s="6">
-        <v>-113.06</v>
+        <v>-96.52</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1785,10 +1785,10 @@
         <v>-32.31</v>
       </c>
       <c r="D29" s="5">
-        <v>-50.82</v>
+        <v>-40.86</v>
       </c>
       <c r="E29" s="6">
-        <v>-18.51</v>
+        <v>-8.550000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1802,10 +1802,10 @@
         <v>-77.95</v>
       </c>
       <c r="D30" s="5">
-        <v>-6.62</v>
+        <v>-61.34</v>
       </c>
       <c r="E30" s="7">
-        <v>71.33</v>
+        <v>16.61</v>
       </c>
     </row>
   </sheetData>
@@ -1870,16 +1870,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>41.5</v>
+        <v>39.7</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.5</v>
+        <v>-5.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-6.1</v>
+        <v>-6.6</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1347</v>
+        <v>0.1335</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0024</v>
+        <v>0.0009</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0386</v>
+        <v>-0.0408</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -243,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -741,8 +741,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -882,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2525</v>
+        <v>2551.7</v>
       </c>
       <c r="D2">
-        <v>0.08</v>
+        <v>1.06</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -894,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-12.42</v>
+        <v>-11.49</v>
       </c>
       <c r="H2">
-        <v>16.42</v>
+        <v>17.65</v>
       </c>
       <c r="I2">
-        <v>0.4</v>
+        <v>2.48</v>
       </c>
       <c r="J2">
-        <v>-4.53</v>
+        <v>-1.14</v>
       </c>
       <c r="K2">
-        <v>-3.91</v>
+        <v>-4.41</v>
       </c>
       <c r="L2">
-        <v>-5.59</v>
+        <v>-4.86</v>
       </c>
       <c r="M2">
-        <v>13.35</v>
+        <v>14.04</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="P2">
-        <v>2504.5</v>
+        <v>2516.84</v>
       </c>
       <c r="Q2">
-        <v>2537.36</v>
+        <v>2537.64</v>
       </c>
       <c r="R2">
-        <v>2610.51</v>
+        <v>2611.48</v>
       </c>
       <c r="S2">
-        <v>2581.62</v>
+        <v>2581.25</v>
       </c>
       <c r="T2">
-        <v>-2.19</v>
+        <v>-1.14</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -948,34 +947,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>44.99</v>
+        <v>48.65</v>
       </c>
       <c r="Z2">
-        <v>-31.05</v>
+        <v>-27</v>
       </c>
       <c r="AA2">
-        <v>-30.31</v>
+        <v>-29.65</v>
       </c>
       <c r="AB2">
-        <v>-0.74</v>
+        <v>2.65</v>
       </c>
       <c r="AC2">
-        <v>33.51</v>
+        <v>61.91</v>
       </c>
       <c r="AD2">
-        <v>19.73</v>
+        <v>38.59</v>
       </c>
       <c r="AE2">
-        <v>55.96</v>
+        <v>55.65</v>
       </c>
       <c r="AF2">
-        <v>-6.01</v>
+        <v>10.68</v>
       </c>
       <c r="AG2">
-        <v>2604.2</v>
+        <v>2604.68</v>
       </c>
       <c r="AH2">
-        <v>2470.52</v>
+        <v>2470.61</v>
       </c>
       <c r="AI2">
         <v>2656.3</v>
@@ -984,7 +983,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>13.94</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -995,37 +994,37 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D3">
-        <v>-0.82</v>
+        <v>-0.41</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
       </c>
       <c r="F3">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="G3">
-        <v>-28.38</v>
+        <v>-28.68</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.82</v>
+        <v>-1.23</v>
       </c>
       <c r="J3">
-        <v>-7.02</v>
+        <v>-5.44</v>
       </c>
       <c r="K3">
-        <v>-4.81</v>
+        <v>-5.16</v>
       </c>
       <c r="L3">
-        <v>-26.6</v>
+        <v>-27.28</v>
       </c>
       <c r="M3">
-        <v>0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="N3">
         <v>66</v>
@@ -1034,19 +1033,19 @@
         <v>20</v>
       </c>
       <c r="P3">
-        <v>726.6</v>
+        <v>724.8</v>
       </c>
       <c r="Q3">
-        <v>737.84</v>
+        <v>736.1799999999999</v>
       </c>
       <c r="R3">
-        <v>770.99</v>
+        <v>770.62</v>
       </c>
       <c r="S3">
-        <v>857.29</v>
+        <v>855.9</v>
       </c>
       <c r="T3">
-        <v>-15.66</v>
+        <v>-15.88</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1061,43 +1060,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>32.83</v>
+        <v>31.55</v>
       </c>
       <c r="Z3">
         <v>-14.27</v>
       </c>
       <c r="AA3">
-        <v>-14.06</v>
+        <v>-14.11</v>
       </c>
       <c r="AB3">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="AC3">
-        <v>20.89</v>
+        <v>13.96</v>
       </c>
       <c r="AD3">
-        <v>18.62</v>
+        <v>18.29</v>
       </c>
       <c r="AE3">
-        <v>10.36</v>
+        <v>10.35</v>
       </c>
       <c r="AF3">
-        <v>-40.86</v>
+        <v>-24.31</v>
       </c>
       <c r="AG3">
-        <v>757.98</v>
+        <v>756.48</v>
       </c>
       <c r="AH3">
-        <v>717.6900000000001</v>
+        <v>715.88</v>
       </c>
       <c r="AI3">
-        <v>757.0700000000001</v>
+        <v>751.3099999999999</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>48.23</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1108,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>538.25</v>
+        <v>536.3</v>
       </c>
       <c r="D4">
-        <v>-0.87</v>
+        <v>-0.36</v>
       </c>
       <c r="E4">
         <v>796.55</v>
@@ -1120,25 +1119,25 @@
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-32.43</v>
+        <v>-32.67</v>
       </c>
       <c r="H4">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="I4">
-        <v>0.42</v>
+        <v>-0.13</v>
       </c>
       <c r="J4">
-        <v>-4.68</v>
+        <v>-4.4</v>
       </c>
       <c r="K4">
-        <v>-11.05</v>
+        <v>-12.7</v>
       </c>
       <c r="L4">
-        <v>-29.75</v>
+        <v>-30.94</v>
       </c>
       <c r="M4">
-        <v>-4.08</v>
+        <v>-4.06</v>
       </c>
       <c r="N4">
         <v>34</v>
@@ -1147,19 +1146,19 @@
         <v>12</v>
       </c>
       <c r="P4">
-        <v>538.4299999999999</v>
+        <v>538.29</v>
       </c>
       <c r="Q4">
-        <v>545.3</v>
+        <v>544.46</v>
       </c>
       <c r="R4">
-        <v>560.87</v>
+        <v>560.38</v>
       </c>
       <c r="S4">
-        <v>655.33</v>
+        <v>654.28</v>
       </c>
       <c r="T4">
-        <v>-17.87</v>
+        <v>-18.03</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1174,43 +1173,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.37</v>
+        <v>40.15</v>
       </c>
       <c r="Z4">
-        <v>-7.31</v>
+        <v>-7.19</v>
       </c>
       <c r="AA4">
-        <v>-7.77</v>
+        <v>-7.66</v>
       </c>
       <c r="AB4">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="AC4">
-        <v>62.88</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="AD4">
-        <v>48.85</v>
+        <v>62.83</v>
       </c>
       <c r="AE4">
-        <v>9.619999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AF4">
-        <v>-61.34</v>
+        <v>-11.9</v>
       </c>
       <c r="AG4">
-        <v>560.73</v>
+        <v>559.9299999999999</v>
       </c>
       <c r="AH4">
-        <v>529.87</v>
+        <v>528.99</v>
       </c>
       <c r="AI4">
-        <v>566.65</v>
+        <v>564.71</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>36.4</v>
+        <v>36.19</v>
       </c>
     </row>
   </sheetData>
@@ -1408,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.5</v>
+        <v>-4.53</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.53</v>
+        <v>-1.14</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.03</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1425,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.06</v>
+        <v>-7.02</v>
       </c>
       <c r="D8" s="5">
-        <v>-7.02</v>
-      </c>
-      <c r="E8" s="7">
-        <v>3.04</v>
+        <v>-5.44</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.58</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1442,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.59</v>
+        <v>-4.68</v>
       </c>
       <c r="D9" s="5">
-        <v>-4.68</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.91</v>
+        <v>-4.4</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1459,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-2.36</v>
+        <v>0.4</v>
       </c>
       <c r="D10" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.76</v>
+        <v>2.48</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.08</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1476,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.55</v>
+        <v>-0.82</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.82</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.27</v>
+        <v>-1.23</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1493,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-0.77</v>
+        <v>0.42</v>
       </c>
       <c r="D12" s="5">
-        <v>0.42</v>
+        <v>-0.13</v>
       </c>
       <c r="E12" s="7">
-        <v>1.19</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1510,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-8.69</v>
+        <v>-5.59</v>
       </c>
       <c r="D13" s="5">
-        <v>-5.59</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.1</v>
+        <v>-4.86</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.73</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1527,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-26.34</v>
+        <v>-26.6</v>
       </c>
       <c r="D14" s="5">
-        <v>-26.6</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.26</v>
+        <v>-27.28</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1544,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-29.64</v>
+        <v>-29.75</v>
       </c>
       <c r="D15" s="5">
-        <v>-29.75</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.11</v>
+        <v>-30.94</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1561,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.27</v>
+        <v>-3.91</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.91</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.64</v>
+        <v>-4.41</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1578,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-5.42</v>
+        <v>-4.81</v>
       </c>
       <c r="D17" s="5">
-        <v>-4.81</v>
+        <v>-5.16</v>
       </c>
       <c r="E17" s="7">
-        <v>0.61</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1595,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-11.42</v>
+        <v>-11.05</v>
       </c>
       <c r="D18" s="5">
-        <v>-11.05</v>
+        <v>-12.7</v>
       </c>
       <c r="E18" s="7">
-        <v>0.37</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1612,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-13.8</v>
+        <v>-12.42</v>
       </c>
       <c r="D19" s="5">
-        <v>-12.42</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.38</v>
+        <v>-11.49</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.93</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1629,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-27.98</v>
+        <v>-28.38</v>
       </c>
       <c r="D20" s="5">
-        <v>-28.38</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.4</v>
+        <v>-28.68</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1646,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-32.73</v>
+        <v>-32.43</v>
       </c>
       <c r="D21" s="5">
-        <v>-32.43</v>
+        <v>-32.67</v>
       </c>
       <c r="E21" s="7">
-        <v>0.3</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1663,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2485</v>
+        <v>2525</v>
       </c>
       <c r="D22" s="5">
-        <v>2525</v>
-      </c>
-      <c r="E22" s="7">
-        <v>40</v>
+        <v>2551.7</v>
+      </c>
+      <c r="E22" s="6">
+        <v>26.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1680,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="D23" s="5">
-        <v>723</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-4</v>
+        <v>720</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1697,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>535.85</v>
+        <v>538.25</v>
       </c>
       <c r="D24" s="5">
-        <v>538.25</v>
+        <v>536.3</v>
       </c>
       <c r="E24" s="7">
-        <v>2.4</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1714,13 +1713,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>39.38</v>
+        <v>44.99</v>
       </c>
       <c r="D25" s="5">
-        <v>44.99</v>
-      </c>
-      <c r="E25" s="7">
-        <v>5.61</v>
+        <v>48.65</v>
+      </c>
+      <c r="E25" s="6">
+        <v>3.66</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1731,13 +1730,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>33.83</v>
+        <v>32.83</v>
       </c>
       <c r="D26" s="5">
-        <v>32.83</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1</v>
+        <v>31.55</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1748,13 +1747,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>38.05</v>
+        <v>41.37</v>
       </c>
       <c r="D27" s="5">
-        <v>41.37</v>
+        <v>40.15</v>
       </c>
       <c r="E27" s="7">
-        <v>3.32</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1765,13 +1764,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>90.51000000000001</v>
+        <v>-6.01</v>
       </c>
       <c r="D28" s="5">
-        <v>-6.01</v>
+        <v>10.68</v>
       </c>
       <c r="E28" s="6">
-        <v>-96.52</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1782,13 +1781,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-32.31</v>
+        <v>-40.86</v>
       </c>
       <c r="D29" s="5">
-        <v>-40.86</v>
+        <v>-24.31</v>
       </c>
       <c r="E29" s="6">
-        <v>-8.550000000000001</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1799,13 +1798,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-77.95</v>
+        <v>-61.34</v>
       </c>
       <c r="D30" s="5">
-        <v>-61.34</v>
-      </c>
-      <c r="E30" s="7">
-        <v>16.61</v>
+        <v>-11.9</v>
+      </c>
+      <c r="E30" s="6">
+        <v>49.44</v>
       </c>
     </row>
   </sheetData>
@@ -1870,16 +1869,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>39.7</v>
+        <v>40.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.4</v>
+        <v>-3.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-6.6</v>
+        <v>-7.4</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1998,13 +1997,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1335</v>
+        <v>0.1404</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0009</v>
+        <v>-0.0001</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0408</v>
+        <v>-0.0406</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.6 → 57.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.6</t>
+  </si>
+  <si>
+    <t>57.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,14 +386,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -741,7 +769,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -881,10 +911,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2551.7</v>
+        <v>2624</v>
       </c>
       <c r="D2">
-        <v>1.06</v>
+        <v>2.83</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -893,46 +923,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-11.49</v>
+        <v>-8.98</v>
       </c>
       <c r="H2">
-        <v>17.65</v>
+        <v>20.98</v>
       </c>
       <c r="I2">
-        <v>2.48</v>
+        <v>4.98</v>
       </c>
       <c r="J2">
-        <v>-1.14</v>
+        <v>3.06</v>
       </c>
       <c r="K2">
-        <v>-4.41</v>
+        <v>-2.09</v>
       </c>
       <c r="L2">
-        <v>-4.86</v>
+        <v>-2.34</v>
       </c>
       <c r="M2">
-        <v>14.04</v>
+        <v>14.68</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P2">
-        <v>2516.84</v>
+        <v>2541.74</v>
       </c>
       <c r="Q2">
-        <v>2537.64</v>
+        <v>2543.41</v>
       </c>
       <c r="R2">
-        <v>2611.48</v>
+        <v>2615</v>
       </c>
       <c r="S2">
-        <v>2581.25</v>
+        <v>2581.21</v>
       </c>
       <c r="T2">
-        <v>-1.14</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -944,37 +974,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>48.65</v>
+        <v>57</v>
       </c>
       <c r="Z2">
-        <v>-27</v>
+        <v>-17.75</v>
       </c>
       <c r="AA2">
-        <v>-29.65</v>
+        <v>-27.27</v>
       </c>
       <c r="AB2">
-        <v>2.65</v>
+        <v>9.52</v>
       </c>
       <c r="AC2">
-        <v>61.91</v>
+        <v>78.91</v>
       </c>
       <c r="AD2">
-        <v>38.59</v>
+        <v>58.11</v>
       </c>
       <c r="AE2">
-        <v>55.65</v>
+        <v>56.84</v>
       </c>
       <c r="AF2">
-        <v>10.68</v>
+        <v>65.33</v>
       </c>
       <c r="AG2">
-        <v>2604.68</v>
+        <v>2619.22</v>
       </c>
       <c r="AH2">
-        <v>2470.61</v>
+        <v>2467.6</v>
       </c>
       <c r="AI2">
         <v>2656.3</v>
@@ -983,7 +1013,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>13.82</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1024,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>720</v>
+        <v>725.05</v>
       </c>
       <c r="D3">
-        <v>-0.41</v>
+        <v>0.7</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1036,46 @@
         <v>720</v>
       </c>
       <c r="G3">
-        <v>-28.68</v>
+        <v>-28.18</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I3">
-        <v>-1.23</v>
+        <v>0.01</v>
       </c>
       <c r="J3">
+        <v>-3.73</v>
+      </c>
+      <c r="K3">
         <v>-5.44</v>
       </c>
-      <c r="K3">
-        <v>-5.16</v>
-      </c>
       <c r="L3">
-        <v>-27.28</v>
+        <v>-27.17</v>
       </c>
       <c r="M3">
-        <v>-0.01</v>
+        <v>0.13</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P3">
-        <v>724.8</v>
+        <v>724.8099999999999</v>
       </c>
       <c r="Q3">
-        <v>736.1799999999999</v>
+        <v>735.0700000000001</v>
       </c>
       <c r="R3">
-        <v>770.62</v>
+        <v>770.1799999999999</v>
       </c>
       <c r="S3">
-        <v>855.9</v>
+        <v>854.59</v>
       </c>
       <c r="T3">
-        <v>-15.88</v>
+        <v>-15.16</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,34 +1090,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.55</v>
+        <v>36.07</v>
       </c>
       <c r="Z3">
-        <v>-14.27</v>
+        <v>-13.71</v>
       </c>
       <c r="AA3">
-        <v>-14.11</v>
+        <v>-14.03</v>
       </c>
       <c r="AB3">
-        <v>-0.16</v>
+        <v>0.32</v>
       </c>
       <c r="AC3">
-        <v>13.96</v>
+        <v>17.25</v>
       </c>
       <c r="AD3">
-        <v>18.29</v>
+        <v>17.37</v>
       </c>
       <c r="AE3">
-        <v>10.35</v>
+        <v>10.21</v>
       </c>
       <c r="AF3">
-        <v>-24.31</v>
+        <v>-35.3</v>
       </c>
       <c r="AG3">
-        <v>756.48</v>
+        <v>755.24</v>
       </c>
       <c r="AH3">
-        <v>715.88</v>
+        <v>714.9</v>
       </c>
       <c r="AI3">
         <v>751.3099999999999</v>
@@ -1096,7 +1126,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>50.02</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1137,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>536.3</v>
+        <v>542</v>
       </c>
       <c r="D4">
-        <v>-0.36</v>
+        <v>1.06</v>
       </c>
       <c r="E4">
         <v>796.55</v>
@@ -1119,46 +1149,46 @@
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-32.67</v>
+        <v>-31.96</v>
       </c>
       <c r="H4">
-        <v>0.08</v>
+        <v>1.15</v>
       </c>
       <c r="I4">
-        <v>-0.13</v>
+        <v>0.73</v>
       </c>
       <c r="J4">
-        <v>-4.4</v>
+        <v>-2.01</v>
       </c>
       <c r="K4">
-        <v>-12.7</v>
+        <v>-12.1</v>
       </c>
       <c r="L4">
-        <v>-30.94</v>
+        <v>-31.28</v>
       </c>
       <c r="M4">
-        <v>-4.06</v>
+        <v>-3.86</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>538.29</v>
+        <v>539.08</v>
       </c>
       <c r="Q4">
-        <v>544.46</v>
+        <v>544.01</v>
       </c>
       <c r="R4">
-        <v>560.38</v>
+        <v>560.23</v>
       </c>
       <c r="S4">
-        <v>654.28</v>
+        <v>653.33</v>
       </c>
       <c r="T4">
-        <v>-18.03</v>
+        <v>-17.04</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,34 +1203,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.15</v>
+        <v>45.21</v>
       </c>
       <c r="Z4">
-        <v>-7.19</v>
+        <v>-6.56</v>
       </c>
       <c r="AA4">
-        <v>-7.66</v>
+        <v>-7.44</v>
       </c>
       <c r="AB4">
-        <v>0.47</v>
+        <v>0.88</v>
       </c>
       <c r="AC4">
         <v>71.76000000000001</v>
       </c>
       <c r="AD4">
-        <v>62.83</v>
+        <v>68.8</v>
       </c>
       <c r="AE4">
-        <v>9.4</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AF4">
-        <v>-11.9</v>
+        <v>-48.98</v>
       </c>
       <c r="AG4">
-        <v>559.9299999999999</v>
+        <v>559.21</v>
       </c>
       <c r="AH4">
-        <v>528.99</v>
+        <v>528.8200000000001</v>
       </c>
       <c r="AI4">
         <v>564.71</v>
@@ -1209,7 +1239,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>36.19</v>
+        <v>33.17</v>
       </c>
     </row>
   </sheetData>
@@ -1370,12 +1400,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,428 +1448,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.53</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-1.14</v>
       </c>
-      <c r="E7" s="6">
-        <v>3.39</v>
+      <c r="D7" s="6">
+        <v>3.06</v>
+      </c>
+      <c r="E7" s="7">
+        <v>4.2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-7.02</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-5.44</v>
       </c>
-      <c r="E8" s="6">
-        <v>1.58</v>
+      <c r="D8" s="6">
+        <v>-3.73</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.71</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-4.68</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-4.4</v>
       </c>
-      <c r="E9" s="6">
-        <v>0.28</v>
+      <c r="D9" s="6">
+        <v>-2.01</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.39</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>2.48</v>
       </c>
-      <c r="E10" s="6">
-        <v>2.08</v>
+      <c r="D10" s="6">
+        <v>4.98</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-0.82</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-1.23</v>
       </c>
+      <c r="D11" s="6">
+        <v>0.01</v>
+      </c>
       <c r="E11" s="7">
-        <v>-0.41</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-0.13</v>
       </c>
+      <c r="D12" s="6">
+        <v>0.73</v>
+      </c>
       <c r="E12" s="7">
-        <v>-0.55</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-5.59</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-4.86</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.73</v>
+      <c r="D13" s="6">
+        <v>-2.34</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-26.6</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-27.28</v>
       </c>
+      <c r="D14" s="6">
+        <v>-27.17</v>
+      </c>
       <c r="E14" s="7">
-        <v>-0.68</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-29.75</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-30.94</v>
       </c>
-      <c r="E15" s="7">
-        <v>-1.19</v>
+      <c r="D15" s="6">
+        <v>-31.28</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.91</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-4.41</v>
       </c>
+      <c r="D16" s="6">
+        <v>-2.09</v>
+      </c>
       <c r="E16" s="7">
-        <v>-0.5</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-4.81</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-5.16</v>
       </c>
-      <c r="E17" s="7">
-        <v>-0.35</v>
+      <c r="D17" s="6">
+        <v>-5.44</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-11.05</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-12.7</v>
       </c>
+      <c r="D18" s="6">
+        <v>-12.1</v>
+      </c>
       <c r="E18" s="7">
-        <v>-1.65</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-12.42</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-11.49</v>
       </c>
-      <c r="E19" s="6">
-        <v>0.93</v>
+      <c r="D19" s="6">
+        <v>-8.98</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.51</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-28.38</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-28.68</v>
       </c>
+      <c r="D20" s="6">
+        <v>-28.18</v>
+      </c>
       <c r="E20" s="7">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-32.43</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-32.67</v>
       </c>
+      <c r="D21" s="6">
+        <v>-31.96</v>
+      </c>
       <c r="E21" s="7">
-        <v>-0.24</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>2525</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>2551.7</v>
       </c>
-      <c r="E22" s="6">
-        <v>26.7</v>
+      <c r="D22" s="6">
+        <v>2624</v>
+      </c>
+      <c r="E22" s="7">
+        <v>72.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>723</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>720</v>
       </c>
+      <c r="D23" s="6">
+        <v>725.05</v>
+      </c>
       <c r="E23" s="7">
-        <v>-3</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>538.25</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>536.3</v>
       </c>
+      <c r="D24" s="6">
+        <v>542</v>
+      </c>
       <c r="E24" s="7">
-        <v>-1.95</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>44.99</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>48.65</v>
       </c>
-      <c r="E25" s="6">
-        <v>3.66</v>
+      <c r="D25" s="6">
+        <v>57</v>
+      </c>
+      <c r="E25" s="7">
+        <v>8.35</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>32.83</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>31.55</v>
       </c>
+      <c r="D26" s="6">
+        <v>36.07</v>
+      </c>
       <c r="E26" s="7">
-        <v>-1.28</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>41.37</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>40.15</v>
       </c>
+      <c r="D27" s="6">
+        <v>45.21</v>
+      </c>
       <c r="E27" s="7">
-        <v>-1.22</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-6.01</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>10.68</v>
       </c>
-      <c r="E28" s="6">
-        <v>16.69</v>
+      <c r="D28" s="6">
+        <v>65.33</v>
+      </c>
+      <c r="E28" s="7">
+        <v>54.65</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-40.86</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-24.31</v>
       </c>
-      <c r="E29" s="6">
-        <v>16.55</v>
+      <c r="D29" s="6">
+        <v>-35.3</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-10.99</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-61.34</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-11.9</v>
       </c>
-      <c r="E30" s="6">
-        <v>49.44</v>
+      <c r="D30" s="6">
+        <v>-48.98</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-37.08</v>
       </c>
     </row>
   </sheetData>
@@ -1830,60 +1895,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
-        <v>36.52</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>48.52</v>
+      </c>
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>40.1</v>
-      </c>
-      <c r="E2" s="10">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-3.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-7.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="11">
+        <v>46.1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>30</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-0.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1985,25 +2050,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1404</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0001</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0406</v>
+      <c r="A2" s="14">
+        <v>0.1468</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0013</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0386</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.6 → 57.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.6</t>
-  </si>
-  <si>
-    <t>57.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -386,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -769,9 +741,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -911,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2624</v>
+        <v>2618</v>
       </c>
       <c r="D2">
-        <v>2.83</v>
+        <v>0.31</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -923,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-8.98</v>
+        <v>-9.19</v>
       </c>
       <c r="H2">
-        <v>20.98</v>
+        <v>20.7</v>
       </c>
       <c r="I2">
-        <v>4.98</v>
+        <v>3.77</v>
       </c>
       <c r="J2">
-        <v>3.06</v>
+        <v>4.48</v>
       </c>
       <c r="K2">
-        <v>-2.09</v>
+        <v>-2.36</v>
       </c>
       <c r="L2">
-        <v>-2.34</v>
+        <v>-6.44</v>
       </c>
       <c r="M2">
-        <v>14.68</v>
+        <v>14.75</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P2">
-        <v>2541.74</v>
+        <v>2585.74</v>
       </c>
       <c r="Q2">
-        <v>2543.41</v>
+        <v>2551.91</v>
       </c>
       <c r="R2">
-        <v>2615</v>
+        <v>2622.65</v>
       </c>
       <c r="S2">
-        <v>2581.21</v>
+        <v>2580.91</v>
       </c>
       <c r="T2">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -977,34 +947,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>57</v>
+        <v>56.02</v>
       </c>
       <c r="Z2">
-        <v>-17.75</v>
+        <v>-5.69</v>
       </c>
       <c r="AA2">
-        <v>-27.27</v>
+        <v>-20.42</v>
       </c>
       <c r="AB2">
-        <v>9.52</v>
+        <v>14.73</v>
       </c>
       <c r="AC2">
-        <v>78.91</v>
+        <v>94.61</v>
       </c>
       <c r="AD2">
-        <v>58.11</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="AE2">
-        <v>56.84</v>
+        <v>52.52</v>
       </c>
       <c r="AF2">
-        <v>65.33</v>
+        <v>-6.51</v>
       </c>
       <c r="AG2">
-        <v>2619.22</v>
+        <v>2636.95</v>
       </c>
       <c r="AH2">
-        <v>2467.6</v>
+        <v>2466.86</v>
       </c>
       <c r="AI2">
         <v>2656.3</v>
@@ -1013,7 +983,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>18.35</v>
+        <v>25.93</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1024,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>725.05</v>
+        <v>729</v>
       </c>
       <c r="D3">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1036,46 +1006,46 @@
         <v>720</v>
       </c>
       <c r="G3">
-        <v>-28.18</v>
+        <v>-27.79</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>1.25</v>
       </c>
       <c r="I3">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-3.73</v>
+        <v>-1.86</v>
       </c>
       <c r="K3">
-        <v>-5.44</v>
+        <v>-6.41</v>
       </c>
       <c r="L3">
-        <v>-27.17</v>
+        <v>-26.77</v>
       </c>
       <c r="M3">
-        <v>0.13</v>
+        <v>-0.34</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P3">
-        <v>724.8099999999999</v>
+        <v>724.8</v>
       </c>
       <c r="Q3">
-        <v>735.0700000000001</v>
+        <v>733.75</v>
       </c>
       <c r="R3">
-        <v>770.1799999999999</v>
+        <v>768.96</v>
       </c>
       <c r="S3">
-        <v>854.59</v>
+        <v>851.98</v>
       </c>
       <c r="T3">
-        <v>-15.16</v>
+        <v>-14.43</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1090,34 +1060,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.07</v>
+        <v>39.57</v>
       </c>
       <c r="Z3">
-        <v>-13.71</v>
+        <v>-12.06</v>
       </c>
       <c r="AA3">
-        <v>-14.03</v>
+        <v>-13.46</v>
       </c>
       <c r="AB3">
-        <v>0.32</v>
+        <v>1.4</v>
       </c>
       <c r="AC3">
-        <v>17.25</v>
+        <v>80.8</v>
       </c>
       <c r="AD3">
-        <v>17.37</v>
+        <v>48.51</v>
       </c>
       <c r="AE3">
-        <v>10.21</v>
+        <v>10.05</v>
       </c>
       <c r="AF3">
-        <v>-35.3</v>
+        <v>-57.14</v>
       </c>
       <c r="AG3">
-        <v>755.24</v>
+        <v>753.86</v>
       </c>
       <c r="AH3">
-        <v>714.9</v>
+        <v>713.64</v>
       </c>
       <c r="AI3">
         <v>751.3099999999999</v>
@@ -1126,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>49.34</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1137,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>542</v>
+        <v>552.95</v>
       </c>
       <c r="D4">
-        <v>1.06</v>
+        <v>-0.33</v>
       </c>
       <c r="E4">
         <v>796.55</v>
@@ -1149,46 +1119,46 @@
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-31.96</v>
+        <v>-30.58</v>
       </c>
       <c r="H4">
-        <v>1.15</v>
+        <v>3.19</v>
       </c>
       <c r="I4">
-        <v>0.73</v>
+        <v>1.83</v>
       </c>
       <c r="J4">
-        <v>-2.01</v>
+        <v>-0.38</v>
       </c>
       <c r="K4">
-        <v>-12.1</v>
+        <v>-10.65</v>
       </c>
       <c r="L4">
-        <v>-31.28</v>
+        <v>-30.34</v>
       </c>
       <c r="M4">
-        <v>-3.86</v>
+        <v>-3.56</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>539.08</v>
+        <v>544.86</v>
       </c>
       <c r="Q4">
-        <v>544.01</v>
+        <v>544</v>
       </c>
       <c r="R4">
-        <v>560.23</v>
+        <v>560.37</v>
       </c>
       <c r="S4">
-        <v>653.33</v>
+        <v>651.47</v>
       </c>
       <c r="T4">
-        <v>-17.04</v>
+        <v>-15.12</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1203,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>45.21</v>
+        <v>53.11</v>
       </c>
       <c r="Z4">
-        <v>-6.56</v>
+        <v>-3.81</v>
       </c>
       <c r="AA4">
-        <v>-7.44</v>
+        <v>-6.32</v>
       </c>
       <c r="AB4">
-        <v>0.88</v>
+        <v>2.51</v>
       </c>
       <c r="AC4">
-        <v>71.76000000000001</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="AD4">
-        <v>68.8</v>
+        <v>84.17</v>
       </c>
       <c r="AE4">
-        <v>9.220000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="AF4">
-        <v>-48.98</v>
+        <v>-36.21</v>
       </c>
       <c r="AG4">
-        <v>559.21</v>
+        <v>559.17</v>
       </c>
       <c r="AH4">
-        <v>528.8200000000001</v>
+        <v>528.84</v>
       </c>
       <c r="AI4">
         <v>564.71</v>
@@ -1239,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>33.17</v>
+        <v>33.02</v>
       </c>
     </row>
   </sheetData>
@@ -1400,47 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1448,428 +1383,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="D7" s="6">
-        <v>3.06</v>
-      </c>
-      <c r="E7" s="7">
-        <v>4.2</v>
+      <c r="C7" s="5">
+        <v>4.04</v>
+      </c>
+      <c r="D7" s="5">
+        <v>4.48</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.44</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.44</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-3.73</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.71</v>
+      <c r="C8" s="5">
+        <v>-2.72</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-1.86</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-4.4</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-2.01</v>
+      <c r="C9" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-0.38</v>
       </c>
       <c r="E9" s="7">
-        <v>2.39</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>2.48</v>
-      </c>
-      <c r="D10" s="6">
-        <v>4.98</v>
+      <c r="C10" s="5">
+        <v>5.03</v>
+      </c>
+      <c r="D10" s="5">
+        <v>3.77</v>
       </c>
       <c r="E10" s="7">
-        <v>2.5</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
+        <v>-0.01</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
         <v>0.01</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.24</v>
-      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.83</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-6.7</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-6.44</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-27.44</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-26.77</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-29.86</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-30.34</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-3.3</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-2.36</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-7.61</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-6.41</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-10.52</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-10.65</v>
+      </c>
+      <c r="E18" s="7">
         <v>-0.13</v>
       </c>
-      <c r="D12" s="6">
-        <v>0.73</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-4.86</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.34</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-9.19</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-27.28</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-27.17</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-27.99</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-27.79</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-30.94</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-31.28</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-30.35</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-30.58</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-4.41</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.09</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2610</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2618</v>
+      </c>
+      <c r="E22" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-5.16</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-5.44</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>726.95</v>
+      </c>
+      <c r="D23" s="5">
+        <v>729</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-12.7</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-12.1</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>554.8</v>
+      </c>
+      <c r="D24" s="5">
+        <v>552.95</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-11.49</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-8.98</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>55.13</v>
+      </c>
+      <c r="D25" s="5">
+        <v>56.02</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-28.68</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-28.18</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>37.74</v>
+      </c>
+      <c r="D26" s="5">
+        <v>39.57</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-32.67</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-31.96</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>54.51</v>
+      </c>
+      <c r="D27" s="5">
+        <v>53.11</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2551.7</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2624</v>
-      </c>
-      <c r="E22" s="7">
-        <v>72.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-0.21</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-6.51</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-6.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>720</v>
-      </c>
-      <c r="D23" s="6">
-        <v>725.05</v>
-      </c>
-      <c r="E23" s="7">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-3.41</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-57.14</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-53.73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>536.3</v>
-      </c>
-      <c r="D24" s="6">
-        <v>542</v>
-      </c>
-      <c r="E24" s="7">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>48.65</v>
-      </c>
-      <c r="D25" s="6">
-        <v>57</v>
-      </c>
-      <c r="E25" s="7">
-        <v>8.35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>31.55</v>
-      </c>
-      <c r="D26" s="6">
-        <v>36.07</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>40.15</v>
-      </c>
-      <c r="D27" s="6">
-        <v>45.21</v>
-      </c>
-      <c r="E27" s="7">
-        <v>5.06</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>10.68</v>
-      </c>
-      <c r="D28" s="6">
-        <v>65.33</v>
-      </c>
-      <c r="E28" s="7">
-        <v>54.65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-24.31</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-35.3</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-10.99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-11.9</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-48.98</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-37.08</v>
+      <c r="C30" s="5">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-36.21</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-37.15</v>
       </c>
     </row>
   </sheetData>
@@ -1895,60 +1830,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>46.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>49.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-0.9</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="F2" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="G2" s="10">
         <v>-6.5</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2050,25 +1985,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1468</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0013</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0386</v>
+      <c r="A2" s="13">
+        <v>0.1475</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0034</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0356</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -151,13 +151,43 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>53.1 → 48.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.1</t>
+  </si>
+  <si>
+    <t>48.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -243,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -283,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,17 +389,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -881,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2618</v>
+        <v>2698</v>
       </c>
       <c r="D2">
-        <v>0.31</v>
+        <v>3.06</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -893,46 +924,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-9.19</v>
+        <v>-6.41</v>
       </c>
       <c r="H2">
-        <v>20.7</v>
+        <v>24.39</v>
       </c>
       <c r="I2">
-        <v>3.77</v>
+        <v>6.85</v>
       </c>
       <c r="J2">
-        <v>4.48</v>
+        <v>5.7</v>
       </c>
       <c r="K2">
-        <v>-2.36</v>
+        <v>1.5</v>
       </c>
       <c r="L2">
-        <v>-6.44</v>
+        <v>-3.42</v>
       </c>
       <c r="M2">
-        <v>14.75</v>
+        <v>15.15</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="P2">
-        <v>2585.74</v>
+        <v>2620.34</v>
       </c>
       <c r="Q2">
-        <v>2551.91</v>
+        <v>2560.25</v>
       </c>
       <c r="R2">
-        <v>2622.65</v>
+        <v>2624.15</v>
       </c>
       <c r="S2">
-        <v>2580.91</v>
+        <v>2581.22</v>
       </c>
       <c r="T2">
-        <v>1.44</v>
+        <v>4.52</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +978,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>56.02</v>
+        <v>63.75</v>
       </c>
       <c r="Z2">
-        <v>-5.69</v>
+        <v>5.24</v>
       </c>
       <c r="AA2">
-        <v>-20.42</v>
+        <v>-15.29</v>
       </c>
       <c r="AB2">
-        <v>14.73</v>
+        <v>20.53</v>
       </c>
       <c r="AC2">
         <v>94.61</v>
       </c>
       <c r="AD2">
-        <v>88.34999999999999</v>
+        <v>93.58</v>
       </c>
       <c r="AE2">
-        <v>52.52</v>
+        <v>55.28</v>
       </c>
       <c r="AF2">
-        <v>-6.51</v>
+        <v>65.2</v>
       </c>
       <c r="AG2">
-        <v>2636.95</v>
+        <v>2666.75</v>
       </c>
       <c r="AH2">
-        <v>2466.86</v>
+        <v>2453.74</v>
       </c>
       <c r="AI2">
-        <v>2656.3</v>
+        <v>2486.55</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>25.93</v>
+        <v>31.54</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>729</v>
+        <v>727.5</v>
       </c>
       <c r="D3">
-        <v>0.28</v>
+        <v>-0.21</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1037,46 @@
         <v>720</v>
       </c>
       <c r="G3">
-        <v>-27.79</v>
+        <v>-27.93</v>
       </c>
       <c r="H3">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="J3">
-        <v>-1.86</v>
+        <v>-1.63</v>
       </c>
       <c r="K3">
-        <v>-6.41</v>
+        <v>-4.11</v>
       </c>
       <c r="L3">
-        <v>-26.77</v>
+        <v>-26.82</v>
       </c>
       <c r="M3">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3">
-        <v>724.8</v>
+        <v>725.7</v>
       </c>
       <c r="Q3">
-        <v>733.75</v>
+        <v>733.36</v>
       </c>
       <c r="R3">
-        <v>768.96</v>
+        <v>767.97</v>
       </c>
       <c r="S3">
-        <v>851.98</v>
+        <v>850.6900000000001</v>
       </c>
       <c r="T3">
-        <v>-14.43</v>
+        <v>-14.48</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>39.57</v>
+        <v>38.67</v>
       </c>
       <c r="Z3">
-        <v>-12.06</v>
+        <v>-11.34</v>
       </c>
       <c r="AA3">
-        <v>-13.46</v>
+        <v>-13.04</v>
       </c>
       <c r="AB3">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>80.8</v>
+        <v>95.38</v>
       </c>
       <c r="AD3">
-        <v>48.51</v>
+        <v>74.55</v>
       </c>
       <c r="AE3">
-        <v>10.05</v>
+        <v>9.83</v>
       </c>
       <c r="AF3">
-        <v>-57.14</v>
+        <v>-32.73</v>
       </c>
       <c r="AG3">
-        <v>753.86</v>
+        <v>753.64</v>
       </c>
       <c r="AH3">
-        <v>713.64</v>
+        <v>713.0700000000001</v>
       </c>
       <c r="AI3">
         <v>751.3099999999999</v>
       </c>
       <c r="AJ3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>43.54</v>
+        <v>42.41</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,58 +1138,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>552.95</v>
+        <v>546.7</v>
       </c>
       <c r="D4">
-        <v>-0.33</v>
+        <v>-1.13</v>
       </c>
       <c r="E4">
-        <v>796.55</v>
+        <v>795.45</v>
       </c>
       <c r="F4">
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-30.58</v>
+        <v>-31.27</v>
       </c>
       <c r="H4">
-        <v>3.19</v>
+        <v>2.02</v>
       </c>
       <c r="I4">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="J4">
-        <v>-0.38</v>
+        <v>-1.11</v>
       </c>
       <c r="K4">
-        <v>-10.65</v>
+        <v>-10.32</v>
       </c>
       <c r="L4">
-        <v>-30.34</v>
+        <v>-31.37</v>
       </c>
       <c r="M4">
-        <v>-3.56</v>
+        <v>-4.25</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>544.86</v>
+        <v>546.55</v>
       </c>
       <c r="Q4">
-        <v>544</v>
+        <v>543.4</v>
       </c>
       <c r="R4">
-        <v>560.37</v>
+        <v>559.6799999999999</v>
       </c>
       <c r="S4">
-        <v>651.47</v>
+        <v>650.53</v>
       </c>
       <c r="T4">
-        <v>-15.12</v>
+        <v>-15.96</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,43 +1204,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>53.11</v>
+        <v>48.56</v>
       </c>
       <c r="Z4">
-        <v>-3.81</v>
+        <v>-3.36</v>
       </c>
       <c r="AA4">
-        <v>-6.32</v>
+        <v>-5.72</v>
       </c>
       <c r="AB4">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="AC4">
-        <v>97.23999999999999</v>
+        <v>85.53</v>
       </c>
       <c r="AD4">
-        <v>84.17</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="AE4">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AF4">
-        <v>-36.21</v>
+        <v>-33.14</v>
       </c>
       <c r="AG4">
-        <v>559.17</v>
+        <v>556.98</v>
       </c>
       <c r="AH4">
-        <v>528.84</v>
+        <v>529.83</v>
       </c>
       <c r="AI4">
         <v>564.71</v>
       </c>
       <c r="AJ4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AK4">
-        <v>33.02</v>
+        <v>31.23</v>
       </c>
     </row>
   </sheetData>
@@ -1360,7 +1391,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1370,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,428 +1449,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>4.04</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>4.48</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.44</v>
+      <c r="D7" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-2.72</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-1.86</v>
       </c>
-      <c r="E8" s="6">
-        <v>0.86</v>
+      <c r="D8" s="6">
+        <v>-1.63</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.23</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-0.38</v>
       </c>
-      <c r="E9" s="7">
-        <v>-1.08</v>
+      <c r="D9" s="6">
+        <v>-1.11</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>5.03</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>3.77</v>
       </c>
+      <c r="D10" s="6">
+        <v>6.85</v>
+      </c>
       <c r="E10" s="7">
-        <v>-1.26</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-0.01</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>0</v>
       </c>
-      <c r="E11" s="6">
-        <v>0.01</v>
+      <c r="D11" s="6">
+        <v>0.62</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.62</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>1.83</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.71</v>
+      <c r="D12" s="6">
+        <v>1.57</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-6.7</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-6.44</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.26</v>
+      <c r="D13" s="6">
+        <v>-3.42</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.02</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-27.44</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-26.77</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.67</v>
+      <c r="D14" s="6">
+        <v>-26.82</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-29.86</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-30.34</v>
       </c>
-      <c r="E15" s="7">
-        <v>-0.48</v>
+      <c r="D15" s="6">
+        <v>-31.37</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.3</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-2.36</v>
       </c>
-      <c r="E16" s="6">
-        <v>0.9399999999999999</v>
+      <c r="D16" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E16" s="7">
+        <v>3.86</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-7.61</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-6.41</v>
       </c>
-      <c r="E17" s="6">
-        <v>1.2</v>
+      <c r="D17" s="6">
+        <v>-4.11</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.3</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-10.52</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-10.65</v>
       </c>
+      <c r="D18" s="6">
+        <v>-10.32</v>
+      </c>
       <c r="E18" s="7">
-        <v>-0.13</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-9.470000000000001</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-9.19</v>
       </c>
-      <c r="E19" s="6">
-        <v>0.28</v>
+      <c r="D19" s="6">
+        <v>-6.41</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.78</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-27.99</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-27.79</v>
       </c>
-      <c r="E20" s="6">
-        <v>0.2</v>
+      <c r="D20" s="6">
+        <v>-27.93</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-30.35</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-30.58</v>
       </c>
-      <c r="E21" s="7">
-        <v>-0.23</v>
+      <c r="D21" s="6">
+        <v>-31.27</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>2610</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>2618</v>
       </c>
-      <c r="E22" s="6">
-        <v>8</v>
+      <c r="D22" s="6">
+        <v>2698</v>
+      </c>
+      <c r="E22" s="7">
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>726.95</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>729</v>
       </c>
-      <c r="E23" s="6">
-        <v>2.05</v>
+      <c r="D23" s="6">
+        <v>727.5</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>554.8</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>552.95</v>
       </c>
-      <c r="E24" s="7">
-        <v>-1.85</v>
+      <c r="D24" s="6">
+        <v>546.7</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-6.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>55.13</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>56.02</v>
       </c>
-      <c r="E25" s="6">
-        <v>0.89</v>
+      <c r="D25" s="6">
+        <v>63.75</v>
+      </c>
+      <c r="E25" s="7">
+        <v>7.73</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>37.74</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>39.57</v>
       </c>
-      <c r="E26" s="6">
-        <v>1.83</v>
+      <c r="D26" s="6">
+        <v>38.67</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>54.51</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>53.11</v>
       </c>
-      <c r="E27" s="7">
-        <v>-1.4</v>
+      <c r="D27" s="6">
+        <v>48.56</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-4.55</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-0.21</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>-6.51</v>
       </c>
+      <c r="D28" s="6">
+        <v>65.2</v>
+      </c>
       <c r="E28" s="7">
-        <v>-6.3</v>
+        <v>71.70999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-3.41</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-57.14</v>
       </c>
+      <c r="D29" s="6">
+        <v>-32.73</v>
+      </c>
       <c r="E29" s="7">
-        <v>-53.73</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-36.21</v>
       </c>
+      <c r="D30" s="6">
+        <v>-33.14</v>
+      </c>
       <c r="E30" s="7">
-        <v>-37.15</v>
+        <v>3.07</v>
       </c>
     </row>
   </sheetData>
@@ -1830,60 +1896,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>49.6</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>50.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-6.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-4.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1985,25 +2051,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1475</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0034</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0356</v>
+      <c r="A2" s="14">
+        <v>0.1515</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0036</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0425</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -178,16 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>53.1 → 48.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.1</t>
+    <t>48.6 → 52.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>48.6</t>
+  </si>
+  <si>
+    <t>52.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2698</v>
+        <v>2667.9</v>
       </c>
       <c r="D2">
-        <v>3.06</v>
+        <v>-1.12</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -924,46 +924,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-6.41</v>
+        <v>-7.46</v>
       </c>
       <c r="H2">
-        <v>24.39</v>
+        <v>23</v>
       </c>
       <c r="I2">
-        <v>6.85</v>
+        <v>4.55</v>
       </c>
       <c r="J2">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="K2">
-        <v>1.5</v>
+        <v>0.37</v>
       </c>
       <c r="L2">
-        <v>-3.42</v>
+        <v>-5.89</v>
       </c>
       <c r="M2">
-        <v>15.15</v>
+        <v>14.75</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P2">
-        <v>2620.34</v>
+        <v>2643.58</v>
       </c>
       <c r="Q2">
-        <v>2560.25</v>
+        <v>2566.55</v>
       </c>
       <c r="R2">
-        <v>2624.15</v>
+        <v>2624.34</v>
       </c>
       <c r="S2">
-        <v>2581.22</v>
+        <v>2581.27</v>
       </c>
       <c r="T2">
-        <v>4.52</v>
+        <v>3.36</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,43 +978,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>63.75</v>
+        <v>59.51</v>
       </c>
       <c r="Z2">
-        <v>5.24</v>
+        <v>11.35</v>
       </c>
       <c r="AA2">
-        <v>-15.29</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="AB2">
-        <v>20.53</v>
+        <v>21.31</v>
       </c>
       <c r="AC2">
-        <v>94.61</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="AD2">
-        <v>93.58</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="AE2">
-        <v>55.28</v>
+        <v>54.69</v>
       </c>
       <c r="AF2">
-        <v>65.2</v>
+        <v>-16.62</v>
       </c>
       <c r="AG2">
-        <v>2666.75</v>
+        <v>2682.93</v>
       </c>
       <c r="AH2">
-        <v>2453.74</v>
+        <v>2450.16</v>
       </c>
       <c r="AI2">
-        <v>2486.55</v>
+        <v>2510.43</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>31.54</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>727.5</v>
+        <v>727.2</v>
       </c>
       <c r="D3">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1037,46 +1037,46 @@
         <v>720</v>
       </c>
       <c r="G3">
-        <v>-27.93</v>
+        <v>-27.96</v>
       </c>
       <c r="H3">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>-1.63</v>
+        <v>-1.12</v>
       </c>
       <c r="K3">
-        <v>-4.11</v>
+        <v>-4.15</v>
       </c>
       <c r="L3">
-        <v>-26.82</v>
+        <v>-26.96</v>
       </c>
       <c r="M3">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>725.7</v>
+        <v>727.14</v>
       </c>
       <c r="Q3">
-        <v>733.36</v>
+        <v>732.3099999999999</v>
       </c>
       <c r="R3">
-        <v>767.97</v>
+        <v>766.8099999999999</v>
       </c>
       <c r="S3">
-        <v>850.6900000000001</v>
+        <v>849.42</v>
       </c>
       <c r="T3">
-        <v>-14.48</v>
+        <v>-14.39</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1091,34 +1091,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.67</v>
+        <v>38.48</v>
       </c>
       <c r="Z3">
-        <v>-11.34</v>
+        <v>-10.67</v>
       </c>
       <c r="AA3">
-        <v>-13.04</v>
+        <v>-12.57</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC3">
-        <v>95.38</v>
+        <v>91.77</v>
       </c>
       <c r="AD3">
-        <v>74.55</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="AE3">
-        <v>9.83</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AF3">
-        <v>-32.73</v>
+        <v>-16.9</v>
       </c>
       <c r="AG3">
-        <v>753.64</v>
+        <v>751.5</v>
       </c>
       <c r="AH3">
-        <v>713.0700000000001</v>
+        <v>713.11</v>
       </c>
       <c r="AI3">
         <v>751.3099999999999</v>
@@ -1127,7 +1127,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>42.41</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,58 +1138,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>546.7</v>
+        <v>553</v>
       </c>
       <c r="D4">
-        <v>-1.13</v>
+        <v>1.15</v>
       </c>
       <c r="E4">
-        <v>795.45</v>
+        <v>788.75</v>
       </c>
       <c r="F4">
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-31.27</v>
+        <v>-29.89</v>
       </c>
       <c r="H4">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="I4">
-        <v>1.57</v>
+        <v>3.11</v>
       </c>
       <c r="J4">
-        <v>-1.11</v>
+        <v>-1.03</v>
       </c>
       <c r="K4">
-        <v>-10.32</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L4">
-        <v>-31.37</v>
+        <v>-30.48</v>
       </c>
       <c r="M4">
-        <v>-4.25</v>
+        <v>-4.34</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>546.55</v>
+        <v>549.89</v>
       </c>
       <c r="Q4">
-        <v>543.4</v>
+        <v>543.22</v>
       </c>
       <c r="R4">
-        <v>559.6799999999999</v>
+        <v>559.26</v>
       </c>
       <c r="S4">
-        <v>650.53</v>
+        <v>649.55</v>
       </c>
       <c r="T4">
-        <v>-15.96</v>
+        <v>-14.86</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1204,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>48.56</v>
+        <v>52.94</v>
       </c>
       <c r="Z4">
-        <v>-3.36</v>
+        <v>-2.47</v>
       </c>
       <c r="AA4">
-        <v>-5.72</v>
+        <v>-5.07</v>
       </c>
       <c r="AB4">
-        <v>2.36</v>
+        <v>2.61</v>
       </c>
       <c r="AC4">
-        <v>85.53</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="AD4">
-        <v>88.76000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AE4">
-        <v>9.699999999999999</v>
+        <v>10.21</v>
       </c>
       <c r="AF4">
-        <v>-33.14</v>
+        <v>11.48</v>
       </c>
       <c r="AG4">
-        <v>556.98</v>
+        <v>556.11</v>
       </c>
       <c r="AH4">
-        <v>529.83</v>
+        <v>530.3200000000001</v>
       </c>
       <c r="AI4">
         <v>564.71</v>
@@ -1240,7 +1240,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>31.23</v>
+        <v>32.31</v>
       </c>
     </row>
   </sheetData>
@@ -1473,13 +1473,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>4.48</v>
+        <v>5.7</v>
       </c>
       <c r="D7" s="6">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="E7" s="7">
-        <v>1.22</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1490,13 +1490,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-1.86</v>
+        <v>-1.63</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.63</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.23</v>
+        <v>-1.12</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.51</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1507,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.38</v>
+        <v>-1.11</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.11</v>
+        <v>-1.03</v>
       </c>
       <c r="E9" s="8">
-        <v>-0.73</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1524,13 +1524,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>3.77</v>
+        <v>6.85</v>
       </c>
       <c r="D10" s="6">
-        <v>6.85</v>
+        <v>4.55</v>
       </c>
       <c r="E10" s="7">
-        <v>3.08</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1541,13 +1541,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="D11" s="6">
-        <v>0.62</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.62</v>
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.38</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1558,13 +1558,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="D12" s="6">
-        <v>1.57</v>
+        <v>3.11</v>
       </c>
       <c r="E12" s="8">
-        <v>-0.26</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1575,13 +1575,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.44</v>
+        <v>-3.42</v>
       </c>
       <c r="D13" s="6">
-        <v>-3.42</v>
+        <v>-5.89</v>
       </c>
       <c r="E13" s="7">
-        <v>3.02</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1592,13 +1592,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.77</v>
+        <v>-26.82</v>
       </c>
       <c r="D14" s="6">
-        <v>-26.82</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.05</v>
+        <v>-26.96</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1609,13 +1609,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-30.34</v>
+        <v>-31.37</v>
       </c>
       <c r="D15" s="6">
-        <v>-31.37</v>
+        <v>-30.48</v>
       </c>
       <c r="E15" s="8">
-        <v>-1.03</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1626,13 +1626,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.36</v>
+        <v>1.5</v>
       </c>
       <c r="D16" s="6">
-        <v>1.5</v>
+        <v>0.37</v>
       </c>
       <c r="E16" s="7">
-        <v>3.86</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1643,13 +1643,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.41</v>
+        <v>-4.11</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.11</v>
+        <v>-4.15</v>
       </c>
       <c r="E17" s="7">
-        <v>2.3</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1660,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-10.65</v>
+        <v>-10.32</v>
       </c>
       <c r="D18" s="6">
-        <v>-10.32</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.33</v>
+        <v>-9.279999999999999</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.04</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1677,13 +1677,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-9.19</v>
+        <v>-6.41</v>
       </c>
       <c r="D19" s="6">
-        <v>-6.41</v>
+        <v>-7.46</v>
       </c>
       <c r="E19" s="7">
-        <v>2.78</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1694,13 +1694,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-27.79</v>
+        <v>-27.93</v>
       </c>
       <c r="D20" s="6">
-        <v>-27.93</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.14</v>
+        <v>-27.96</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1711,13 +1711,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-30.58</v>
+        <v>-31.27</v>
       </c>
       <c r="D21" s="6">
-        <v>-31.27</v>
+        <v>-29.89</v>
       </c>
       <c r="E21" s="8">
-        <v>-0.6899999999999999</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1728,13 +1728,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>2618</v>
+        <v>2698</v>
       </c>
       <c r="D22" s="6">
-        <v>2698</v>
+        <v>2667.9</v>
       </c>
       <c r="E22" s="7">
-        <v>80</v>
+        <v>-30.1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1745,13 +1745,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>729</v>
+        <v>727.5</v>
       </c>
       <c r="D23" s="6">
-        <v>727.5</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.5</v>
+        <v>727.2</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1762,13 +1762,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>552.95</v>
+        <v>546.7</v>
       </c>
       <c r="D24" s="6">
-        <v>546.7</v>
+        <v>553</v>
       </c>
       <c r="E24" s="8">
-        <v>-6.25</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1779,13 +1779,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>56.02</v>
+        <v>63.75</v>
       </c>
       <c r="D25" s="6">
-        <v>63.75</v>
+        <v>59.51</v>
       </c>
       <c r="E25" s="7">
-        <v>7.73</v>
+        <v>-4.24</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1796,13 +1796,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>39.57</v>
+        <v>38.67</v>
       </c>
       <c r="D26" s="6">
-        <v>38.67</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.9</v>
+        <v>38.48</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1813,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>53.11</v>
+        <v>48.56</v>
       </c>
       <c r="D27" s="6">
-        <v>48.56</v>
+        <v>52.94</v>
       </c>
       <c r="E27" s="8">
-        <v>-4.55</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1830,13 +1830,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-6.51</v>
+        <v>65.2</v>
       </c>
       <c r="D28" s="6">
-        <v>65.2</v>
+        <v>-16.62</v>
       </c>
       <c r="E28" s="7">
-        <v>71.70999999999999</v>
+        <v>-81.81999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1847,13 +1847,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>-57.14</v>
+        <v>-32.73</v>
       </c>
       <c r="D29" s="6">
-        <v>-32.73</v>
-      </c>
-      <c r="E29" s="7">
-        <v>24.41</v>
+        <v>-16.9</v>
+      </c>
+      <c r="E29" s="8">
+        <v>15.83</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1864,13 +1864,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-36.21</v>
+        <v>-33.14</v>
       </c>
       <c r="D30" s="6">
-        <v>-33.14</v>
-      </c>
-      <c r="E30" s="7">
-        <v>3.07</v>
+        <v>11.48</v>
+      </c>
+      <c r="E30" s="8">
+        <v>44.62</v>
       </c>
     </row>
   </sheetData>
@@ -1941,10 +1941,10 @@
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2063,13 +2063,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1515</v>
+        <v>0.1475</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0036</v>
+        <v>-0.0034</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0425</v>
+        <v>-0.0434</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,16 +178,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.6 → 52.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.6</t>
+    <t>59.5 → 48.7</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>59.5</t>
+  </si>
+  <si>
+    <t>48.7</t>
+  </si>
+  <si>
+    <t>52.9 → 49.4</t>
   </si>
   <si>
     <t>52.9</t>
+  </si>
+  <si>
+    <t>49.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,8 +408,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -912,10 +921,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2667.9</v>
+        <v>2575</v>
       </c>
       <c r="D2">
-        <v>-1.12</v>
+        <v>-3.48</v>
       </c>
       <c r="E2">
         <v>2882.94</v>
@@ -924,46 +933,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-7.46</v>
+        <v>-10.68</v>
       </c>
       <c r="H2">
-        <v>23</v>
+        <v>18.72</v>
       </c>
       <c r="I2">
-        <v>4.55</v>
+        <v>-1.87</v>
       </c>
       <c r="J2">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="K2">
-        <v>0.37</v>
+        <v>-1.61</v>
       </c>
       <c r="L2">
-        <v>-5.89</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M2">
-        <v>14.75</v>
+        <v>13.54</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P2">
-        <v>2643.58</v>
+        <v>2633.78</v>
       </c>
       <c r="Q2">
-        <v>2566.55</v>
+        <v>2567.98</v>
       </c>
       <c r="R2">
-        <v>2624.34</v>
+        <v>2621.62</v>
       </c>
       <c r="S2">
-        <v>2581.27</v>
+        <v>2580.7</v>
       </c>
       <c r="T2">
-        <v>3.36</v>
+        <v>-0.22</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,37 +984,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>59.51</v>
+        <v>48.74</v>
       </c>
       <c r="Z2">
-        <v>11.35</v>
+        <v>8.59</v>
       </c>
       <c r="AA2">
-        <v>-9.960000000000001</v>
+        <v>-6.25</v>
       </c>
       <c r="AB2">
-        <v>21.31</v>
+        <v>14.84</v>
       </c>
       <c r="AC2">
-        <v>92.34999999999999</v>
+        <v>73.69</v>
       </c>
       <c r="AD2">
-        <v>93.84999999999999</v>
+        <v>86.88</v>
       </c>
       <c r="AE2">
-        <v>54.69</v>
+        <v>60.15</v>
       </c>
       <c r="AF2">
-        <v>-16.62</v>
+        <v>186.99</v>
       </c>
       <c r="AG2">
-        <v>2682.93</v>
+        <v>2684.02</v>
       </c>
       <c r="AH2">
-        <v>2450.16</v>
+        <v>2451.94</v>
       </c>
       <c r="AI2">
         <v>2510.43</v>
@@ -1014,7 +1023,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>36.4</v>
+        <v>31.88</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,58 +1034,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>727.2</v>
+        <v>711</v>
       </c>
       <c r="D3">
-        <v>-0.04</v>
+        <v>-2.23</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
       </c>
       <c r="F3">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="G3">
-        <v>-27.96</v>
+        <v>-29.57</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>-1.94</v>
       </c>
       <c r="J3">
-        <v>-1.12</v>
+        <v>-4.97</v>
       </c>
       <c r="K3">
-        <v>-4.15</v>
+        <v>-4.51</v>
       </c>
       <c r="L3">
-        <v>-26.96</v>
+        <v>-27.62</v>
       </c>
       <c r="M3">
-        <v>-0.34</v>
+        <v>-0.7</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>727.14</v>
+        <v>724.33</v>
       </c>
       <c r="Q3">
-        <v>732.3099999999999</v>
+        <v>730.16</v>
       </c>
       <c r="R3">
-        <v>766.8099999999999</v>
+        <v>765.29</v>
       </c>
       <c r="S3">
-        <v>849.42</v>
+        <v>848.05</v>
       </c>
       <c r="T3">
-        <v>-14.39</v>
+        <v>-16.16</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1091,43 +1100,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.48</v>
+        <v>30.01</v>
       </c>
       <c r="Z3">
-        <v>-10.67</v>
+        <v>-11.32</v>
       </c>
       <c r="AA3">
-        <v>-12.57</v>
+        <v>-12.32</v>
       </c>
       <c r="AB3">
-        <v>1.89</v>
+        <v>1</v>
       </c>
       <c r="AC3">
-        <v>91.77</v>
+        <v>58.44</v>
       </c>
       <c r="AD3">
-        <v>89.31999999999999</v>
+        <v>81.86</v>
       </c>
       <c r="AE3">
-        <v>9.619999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="AF3">
-        <v>-16.9</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="AG3">
-        <v>751.5</v>
+        <v>748.76</v>
       </c>
       <c r="AH3">
-        <v>713.11</v>
+        <v>711.5599999999999</v>
       </c>
       <c r="AI3">
-        <v>751.3099999999999</v>
+        <v>749.76</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>39.76</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,58 +1147,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D4">
-        <v>1.15</v>
+        <v>-0.9</v>
       </c>
       <c r="E4">
-        <v>788.75</v>
+        <v>787.8</v>
       </c>
       <c r="F4">
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-29.89</v>
+        <v>-30.44</v>
       </c>
       <c r="H4">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="I4">
-        <v>3.11</v>
+        <v>1.11</v>
       </c>
       <c r="J4">
-        <v>-1.03</v>
+        <v>-1.56</v>
       </c>
       <c r="K4">
-        <v>-9.279999999999999</v>
+        <v>-7.87</v>
       </c>
       <c r="L4">
-        <v>-30.48</v>
+        <v>-30.52</v>
       </c>
       <c r="M4">
-        <v>-4.34</v>
+        <v>-4.66</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>549.89</v>
+        <v>551.09</v>
       </c>
       <c r="Q4">
-        <v>543.22</v>
+        <v>543.35</v>
       </c>
       <c r="R4">
-        <v>559.26</v>
+        <v>558.58</v>
       </c>
       <c r="S4">
-        <v>649.55</v>
+        <v>648.53</v>
       </c>
       <c r="T4">
-        <v>-14.86</v>
+        <v>-15.5</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1213,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>52.94</v>
+        <v>49.35</v>
       </c>
       <c r="Z4">
-        <v>-2.47</v>
+        <v>-2.14</v>
       </c>
       <c r="AA4">
-        <v>-5.07</v>
+        <v>-4.49</v>
       </c>
       <c r="AB4">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AC4">
-        <v>82.43000000000001</v>
+        <v>75.03</v>
       </c>
       <c r="AD4">
-        <v>88.40000000000001</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="AE4">
-        <v>10.21</v>
+        <v>10.12</v>
       </c>
       <c r="AF4">
-        <v>11.48</v>
+        <v>-29.73</v>
       </c>
       <c r="AG4">
-        <v>556.11</v>
+        <v>556.39</v>
       </c>
       <c r="AH4">
-        <v>530.3200000000001</v>
+        <v>530.3099999999999</v>
       </c>
       <c r="AI4">
         <v>564.71</v>
@@ -1240,7 +1249,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>32.31</v>
+        <v>32.53</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1421,7 +1430,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -1439,444 +1448,464 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>5.7</v>
-      </c>
-      <c r="D7" s="6">
-        <v>5.4</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.3</v>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-1.63</v>
+        <v>5.4</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.51</v>
+        <v>1.3</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4.1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.08</v>
+        <v>-4.97</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>6.85</v>
+        <v>-1.03</v>
       </c>
       <c r="D10" s="6">
-        <v>4.55</v>
+        <v>-1.56</v>
       </c>
       <c r="E10" s="7">
-        <v>-2.3</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>0.62</v>
+        <v>4.55</v>
       </c>
       <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.38</v>
+        <v>-1.87</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-6.42</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>1.57</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6">
-        <v>3.11</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.54</v>
+        <v>-1.94</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-3.42</v>
+        <v>3.11</v>
       </c>
       <c r="D13" s="6">
-        <v>-5.89</v>
+        <v>1.11</v>
       </c>
       <c r="E13" s="7">
-        <v>-2.47</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.82</v>
+        <v>-5.89</v>
       </c>
       <c r="D14" s="6">
-        <v>-26.96</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.14</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-31.37</v>
+        <v>-26.96</v>
       </c>
       <c r="D15" s="6">
-        <v>-30.48</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.89</v>
+        <v>-27.62</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6">
-        <v>1.5</v>
+        <v>-30.48</v>
       </c>
       <c r="D16" s="6">
-        <v>0.37</v>
+        <v>-30.52</v>
       </c>
       <c r="E16" s="7">
-        <v>-1.13</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.11</v>
+        <v>0.37</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.15</v>
+        <v>-1.61</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.04</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-10.32</v>
+        <v>-4.15</v>
       </c>
       <c r="D18" s="6">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.04</v>
+        <v>-4.51</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-6.41</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="D19" s="6">
-        <v>-7.46</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.05</v>
+        <v>-7.87</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.41</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-27.93</v>
+        <v>-7.46</v>
       </c>
       <c r="D20" s="6">
-        <v>-27.96</v>
+        <v>-10.68</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.03</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-31.27</v>
+        <v>-27.96</v>
       </c>
       <c r="D21" s="6">
-        <v>-29.89</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.38</v>
+        <v>-29.57</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6">
-        <v>2698</v>
+        <v>-29.89</v>
       </c>
       <c r="D22" s="6">
-        <v>2667.9</v>
+        <v>-30.44</v>
       </c>
       <c r="E22" s="7">
-        <v>-30.1</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>727.5</v>
+        <v>2667.9</v>
       </c>
       <c r="D23" s="6">
-        <v>727.2</v>
+        <v>2575</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.3</v>
+        <v>-92.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>546.7</v>
+        <v>727.2</v>
       </c>
       <c r="D24" s="6">
-        <v>553</v>
-      </c>
-      <c r="E24" s="8">
-        <v>6.3</v>
+        <v>711</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-16.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6">
-        <v>63.75</v>
+        <v>553</v>
       </c>
       <c r="D25" s="6">
-        <v>59.51</v>
+        <v>548</v>
       </c>
       <c r="E25" s="7">
-        <v>-4.24</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>38.67</v>
+        <v>59.51</v>
       </c>
       <c r="D26" s="6">
-        <v>38.48</v>
+        <v>48.74</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.19</v>
+        <v>-10.77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>48.56</v>
+        <v>38.48</v>
       </c>
       <c r="D27" s="6">
-        <v>52.94</v>
-      </c>
-      <c r="E27" s="8">
-        <v>4.38</v>
+        <v>30.01</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="6">
-        <v>65.2</v>
+        <v>52.94</v>
       </c>
       <c r="D28" s="6">
-        <v>-16.62</v>
+        <v>49.35</v>
       </c>
       <c r="E28" s="7">
-        <v>-81.81999999999999</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>-32.73</v>
+        <v>-16.62</v>
       </c>
       <c r="D29" s="6">
-        <v>-16.9</v>
+        <v>186.99</v>
       </c>
       <c r="E29" s="8">
-        <v>15.83</v>
+        <v>203.61</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-33.14</v>
+        <v>-16.9</v>
       </c>
       <c r="D30" s="6">
+        <v>87.20999999999999</v>
+      </c>
+      <c r="E30" s="8">
+        <v>104.11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
         <v>11.48</v>
       </c>
-      <c r="E30" s="8">
-        <v>44.62</v>
+      <c r="D31" s="6">
+        <v>-29.73</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-41.21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1900,28 +1929,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1929,22 +1958,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="11">
-        <v>48.52</v>
+        <v>36.52</v>
       </c>
       <c r="C2" s="12">
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>50.3</v>
+        <v>42.7</v>
       </c>
       <c r="E2" s="11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>1.1</v>
+        <v>-1.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.4</v>
+        <v>-4.7</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2063,13 +2092,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1475</v>
+        <v>0.1354</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0034</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0434</v>
+        <v>-0.0466</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,43 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>59.5 → 48.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>59.5</t>
-  </si>
-  <si>
-    <t>48.7</t>
-  </si>
-  <si>
-    <t>52.9 → 49.4</t>
-  </si>
-  <si>
-    <t>52.9</t>
-  </si>
-  <si>
-    <t>49.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -398,15 +362,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -921,37 +884,37 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2575</v>
+        <v>2569</v>
       </c>
       <c r="D2">
-        <v>-3.48</v>
+        <v>-0.23</v>
       </c>
       <c r="E2">
-        <v>2882.94</v>
+        <v>2878.78</v>
       </c>
       <c r="F2">
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-10.68</v>
+        <v>-10.76</v>
       </c>
       <c r="H2">
-        <v>18.72</v>
+        <v>18.44</v>
       </c>
       <c r="I2">
-        <v>-1.87</v>
+        <v>-1.57</v>
       </c>
       <c r="J2">
-        <v>1.3</v>
+        <v>0.89</v>
       </c>
       <c r="K2">
-        <v>-1.61</v>
+        <v>0.79</v>
       </c>
       <c r="L2">
-        <v>-9.699999999999999</v>
+        <v>-10.89</v>
       </c>
       <c r="M2">
-        <v>13.54</v>
+        <v>13.27</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -960,19 +923,19 @@
         <v>45</v>
       </c>
       <c r="P2">
-        <v>2633.78</v>
+        <v>2625.58</v>
       </c>
       <c r="Q2">
-        <v>2567.98</v>
+        <v>2565.64</v>
       </c>
       <c r="R2">
-        <v>2621.62</v>
+        <v>2618.43</v>
       </c>
       <c r="S2">
-        <v>2580.7</v>
+        <v>2580.13</v>
       </c>
       <c r="T2">
-        <v>-0.22</v>
+        <v>-0.43</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -987,34 +950,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>48.74</v>
+        <v>48.14</v>
       </c>
       <c r="Z2">
-        <v>8.59</v>
+        <v>5.86</v>
       </c>
       <c r="AA2">
-        <v>-6.25</v>
+        <v>-3.83</v>
       </c>
       <c r="AB2">
-        <v>14.84</v>
+        <v>9.68</v>
       </c>
       <c r="AC2">
-        <v>73.69</v>
+        <v>52.34</v>
       </c>
       <c r="AD2">
-        <v>86.88</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="AE2">
-        <v>60.15</v>
+        <v>59.44</v>
       </c>
       <c r="AF2">
-        <v>186.99</v>
+        <v>-27.51</v>
       </c>
       <c r="AG2">
-        <v>2684.02</v>
+        <v>2679.48</v>
       </c>
       <c r="AH2">
-        <v>2451.94</v>
+        <v>2451.8</v>
       </c>
       <c r="AI2">
         <v>2510.43</v>
@@ -1023,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>31.88</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>711</v>
+        <v>720.3</v>
       </c>
       <c r="D3">
-        <v>-2.23</v>
+        <v>1.31</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1046,22 +1009,22 @@
         <v>711</v>
       </c>
       <c r="G3">
-        <v>-29.57</v>
+        <v>-28.65</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="I3">
-        <v>-1.94</v>
+        <v>-0.91</v>
       </c>
       <c r="J3">
-        <v>-4.97</v>
+        <v>-4.46</v>
       </c>
       <c r="K3">
-        <v>-4.51</v>
+        <v>-3.02</v>
       </c>
       <c r="L3">
-        <v>-27.62</v>
+        <v>-26.65</v>
       </c>
       <c r="M3">
         <v>-0.7</v>
@@ -1070,22 +1033,22 @@
         <v>66</v>
       </c>
       <c r="O3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>724.33</v>
+        <v>723</v>
       </c>
       <c r="Q3">
-        <v>730.16</v>
+        <v>728.76</v>
       </c>
       <c r="R3">
-        <v>765.29</v>
+        <v>763.72</v>
       </c>
       <c r="S3">
-        <v>848.05</v>
+        <v>846.6900000000001</v>
       </c>
       <c r="T3">
-        <v>-16.16</v>
+        <v>-14.93</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1100,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>30.01</v>
+        <v>38.4</v>
       </c>
       <c r="Z3">
-        <v>-11.32</v>
+        <v>-10.95</v>
       </c>
       <c r="AA3">
-        <v>-12.32</v>
+        <v>-12.04</v>
       </c>
       <c r="AB3">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AC3">
-        <v>58.44</v>
+        <v>58.07</v>
       </c>
       <c r="AD3">
-        <v>81.86</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="AE3">
-        <v>10.23</v>
+        <v>10.45</v>
       </c>
       <c r="AF3">
-        <v>87.20999999999999</v>
+        <v>-36.77</v>
       </c>
       <c r="AG3">
-        <v>748.76</v>
+        <v>745.8</v>
       </c>
       <c r="AH3">
-        <v>711.5599999999999</v>
+        <v>711.73</v>
       </c>
       <c r="AI3">
-        <v>749.76</v>
+        <v>744.99</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>41.57</v>
+        <v>43.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,7 +1113,7 @@
         <v>548</v>
       </c>
       <c r="D4">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1165,40 +1128,40 @@
         <v>2.27</v>
       </c>
       <c r="I4">
-        <v>1.11</v>
+        <v>-1.23</v>
       </c>
       <c r="J4">
-        <v>-1.56</v>
+        <v>0.48</v>
       </c>
       <c r="K4">
-        <v>-7.87</v>
+        <v>-6.57</v>
       </c>
       <c r="L4">
-        <v>-30.52</v>
+        <v>-30.37</v>
       </c>
       <c r="M4">
-        <v>-4.66</v>
+        <v>-4.88</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>551.09</v>
+        <v>549.73</v>
       </c>
       <c r="Q4">
-        <v>543.35</v>
+        <v>543.3200000000001</v>
       </c>
       <c r="R4">
-        <v>558.58</v>
+        <v>557.71</v>
       </c>
       <c r="S4">
-        <v>648.53</v>
+        <v>647.45</v>
       </c>
       <c r="T4">
-        <v>-15.5</v>
+        <v>-15.36</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1216,31 +1179,31 @@
         <v>49.35</v>
       </c>
       <c r="Z4">
-        <v>-2.14</v>
+        <v>-1.85</v>
       </c>
       <c r="AA4">
-        <v>-4.49</v>
+        <v>-3.96</v>
       </c>
       <c r="AB4">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
-        <v>75.03</v>
+        <v>76.58</v>
       </c>
       <c r="AD4">
-        <v>80.98999999999999</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="AE4">
-        <v>10.12</v>
+        <v>9.91</v>
       </c>
       <c r="AF4">
-        <v>-29.73</v>
+        <v>-42.03</v>
       </c>
       <c r="AG4">
-        <v>556.39</v>
+        <v>556.3200000000001</v>
       </c>
       <c r="AH4">
-        <v>530.3099999999999</v>
+        <v>530.3200000000001</v>
       </c>
       <c r="AI4">
         <v>564.71</v>
@@ -1249,7 +1212,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>32.53</v>
+        <v>30.16</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1410,502 +1373,396 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1.3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.89</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-4.97</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-4.46</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-1.56</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>5.4</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-1.87</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-1.57</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-1.94</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-0.91</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1.11</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-1.23</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-10.89</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-27.62</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-26.65</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-30.52</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-30.37</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-1.61</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-4.51</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-3.02</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-7.87</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-6.57</v>
+      </c>
+      <c r="E18" s="7">
         <v>1.3</v>
       </c>
-      <c r="E8" s="7">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-10.68</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-10.76</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-4.97</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-29.57</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-28.65</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2575</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2569</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>711</v>
+      </c>
+      <c r="D22" s="5">
+        <v>720.3</v>
+      </c>
+      <c r="E22" s="7">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="5">
+        <v>48.74</v>
+      </c>
+      <c r="D23" s="5">
+        <v>48.14</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="5">
+        <v>30.01</v>
+      </c>
+      <c r="D24" s="5">
+        <v>38.4</v>
+      </c>
+      <c r="E24" s="7">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="5">
+        <v>186.99</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-27.51</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-214.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="5">
+        <v>87.20999999999999</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-36.77</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-123.98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>4.55</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-1.87</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-6.42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-1.94</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>3.11</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1.11</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-5.89</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-3.81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-26.96</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-27.62</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-30.48</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-30.52</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.37</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.61</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-4.15</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-4.51</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-7.87</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-7.46</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-27.96</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-29.57</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-29.89</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-30.44</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2667.9</v>
-      </c>
-      <c r="D23" s="6">
-        <v>2575</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-92.90000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>727.2</v>
-      </c>
-      <c r="D24" s="6">
-        <v>711</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-16.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>553</v>
-      </c>
-      <c r="D25" s="6">
-        <v>548</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>59.51</v>
-      </c>
-      <c r="D26" s="6">
-        <v>48.74</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-10.77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>38.48</v>
-      </c>
-      <c r="D27" s="6">
-        <v>30.01</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-8.470000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>52.94</v>
-      </c>
-      <c r="D28" s="6">
-        <v>49.35</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-16.62</v>
-      </c>
-      <c r="D29" s="6">
-        <v>186.99</v>
-      </c>
-      <c r="E29" s="8">
-        <v>203.61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-16.9</v>
-      </c>
-      <c r="D30" s="6">
-        <v>87.20999999999999</v>
-      </c>
-      <c r="E30" s="8">
-        <v>104.11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>11.48</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C27" s="5">
         <v>-29.73</v>
       </c>
-      <c r="E31" s="7">
-        <v>-41.21</v>
+      <c r="D27" s="5">
+        <v>-42.03</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-12.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1925,60 +1782,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>42.7</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>45.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-2.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2080,25 +1937,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1354</v>
-      </c>
-      <c r="B2" s="14">
+      <c r="A2" s="13">
+        <v>0.1327</v>
+      </c>
+      <c r="B2" s="13">
         <v>-0.006999999999999999</v>
       </c>
-      <c r="C2" s="14">
-        <v>-0.0466</v>
+      <c r="C2" s="13">
+        <v>-0.0488</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.1 → 53.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.1</t>
+  </si>
+  <si>
+    <t>53.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -246,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,17 +389,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -744,7 +772,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -884,10 +913,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2569</v>
+        <v>2622.1</v>
       </c>
       <c r="D2">
-        <v>-0.23</v>
+        <v>2.07</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -896,46 +925,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-10.76</v>
+        <v>-8.92</v>
       </c>
       <c r="H2">
-        <v>18.44</v>
+        <v>20.89</v>
       </c>
       <c r="I2">
-        <v>-1.57</v>
+        <v>0.16</v>
       </c>
       <c r="J2">
-        <v>0.89</v>
+        <v>0.24</v>
       </c>
       <c r="K2">
-        <v>0.79</v>
+        <v>3.71</v>
       </c>
       <c r="L2">
-        <v>-10.89</v>
+        <v>-6.96</v>
       </c>
       <c r="M2">
-        <v>13.27</v>
+        <v>13.62</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="P2">
-        <v>2625.58</v>
+        <v>2626.4</v>
       </c>
       <c r="Q2">
-        <v>2565.64</v>
+        <v>2566.72</v>
       </c>
       <c r="R2">
-        <v>2618.43</v>
+        <v>2616.49</v>
       </c>
       <c r="S2">
-        <v>2580.13</v>
+        <v>2579.82</v>
       </c>
       <c r="T2">
-        <v>-0.43</v>
+        <v>1.64</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,37 +976,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>48.14</v>
+        <v>53.63</v>
       </c>
       <c r="Z2">
-        <v>5.86</v>
+        <v>7.88</v>
       </c>
       <c r="AA2">
-        <v>-3.83</v>
+        <v>-1.49</v>
       </c>
       <c r="AB2">
-        <v>9.68</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AC2">
-        <v>52.34</v>
+        <v>44.29</v>
       </c>
       <c r="AD2">
-        <v>72.79000000000001</v>
+        <v>56.77</v>
       </c>
       <c r="AE2">
-        <v>59.44</v>
+        <v>62.26</v>
       </c>
       <c r="AF2">
-        <v>-27.51</v>
+        <v>0.67</v>
       </c>
       <c r="AG2">
-        <v>2679.48</v>
+        <v>2682.34</v>
       </c>
       <c r="AH2">
-        <v>2451.8</v>
+        <v>2451.09</v>
       </c>
       <c r="AI2">
         <v>2510.43</v>
@@ -986,7 +1015,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>28.57</v>
+        <v>25.89</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,58 +1026,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>720.3</v>
+        <v>709</v>
       </c>
       <c r="D3">
-        <v>1.31</v>
+        <v>-1.57</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
       </c>
       <c r="F3">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G3">
-        <v>-28.65</v>
+        <v>-29.77</v>
       </c>
       <c r="H3">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.91</v>
+        <v>-2.74</v>
       </c>
       <c r="J3">
-        <v>-4.46</v>
+        <v>-5.23</v>
       </c>
       <c r="K3">
-        <v>-3.02</v>
+        <v>-5.25</v>
       </c>
       <c r="L3">
-        <v>-26.65</v>
+        <v>-27.16</v>
       </c>
       <c r="M3">
-        <v>-0.7</v>
+        <v>-1.18</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="Q3">
-        <v>728.76</v>
+        <v>726.5599999999999</v>
       </c>
       <c r="R3">
-        <v>763.72</v>
+        <v>762.3</v>
       </c>
       <c r="S3">
-        <v>846.6900000000001</v>
+        <v>845.29</v>
       </c>
       <c r="T3">
-        <v>-14.93</v>
+        <v>-16.12</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,34 +1092,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.4</v>
+        <v>33.19</v>
       </c>
       <c r="Z3">
-        <v>-10.95</v>
+        <v>-11.44</v>
       </c>
       <c r="AA3">
-        <v>-12.04</v>
+        <v>-11.92</v>
       </c>
       <c r="AB3">
-        <v>1.09</v>
+        <v>0.48</v>
       </c>
       <c r="AC3">
-        <v>58.07</v>
+        <v>40.34</v>
       </c>
       <c r="AD3">
-        <v>69.43000000000001</v>
+        <v>52.29</v>
       </c>
       <c r="AE3">
-        <v>10.45</v>
+        <v>12.24</v>
       </c>
       <c r="AF3">
-        <v>-36.77</v>
+        <v>210.49</v>
       </c>
       <c r="AG3">
-        <v>745.8</v>
+        <v>741.6799999999999</v>
       </c>
       <c r="AH3">
-        <v>711.73</v>
+        <v>711.45</v>
       </c>
       <c r="AI3">
         <v>744.99</v>
@@ -1099,7 +1128,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>43.69</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1139,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>548</v>
+        <v>543.35</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1122,46 +1151,46 @@
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-30.44</v>
+        <v>-31.03</v>
       </c>
       <c r="H4">
-        <v>2.27</v>
+        <v>1.4</v>
       </c>
       <c r="I4">
-        <v>-1.23</v>
+        <v>-1.74</v>
       </c>
       <c r="J4">
-        <v>0.48</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K4">
-        <v>-6.57</v>
+        <v>-6.3</v>
       </c>
       <c r="L4">
-        <v>-30.37</v>
+        <v>-30.03</v>
       </c>
       <c r="M4">
-        <v>-4.88</v>
+        <v>-5.18</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>549.73</v>
+        <v>547.8099999999999</v>
       </c>
       <c r="Q4">
-        <v>543.3200000000001</v>
+        <v>542.83</v>
       </c>
       <c r="R4">
-        <v>557.71</v>
+        <v>556.74</v>
       </c>
       <c r="S4">
-        <v>647.45</v>
+        <v>646.25</v>
       </c>
       <c r="T4">
-        <v>-15.36</v>
+        <v>-15.92</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1205,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>49.35</v>
+        <v>45.99</v>
       </c>
       <c r="Z4">
-        <v>-1.85</v>
+        <v>-1.98</v>
       </c>
       <c r="AA4">
-        <v>-3.96</v>
+        <v>-3.56</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AC4">
-        <v>76.58</v>
+        <v>62.42</v>
       </c>
       <c r="AD4">
-        <v>78.01000000000001</v>
+        <v>71.34</v>
       </c>
       <c r="AE4">
-        <v>9.91</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AF4">
-        <v>-42.03</v>
+        <v>6.11</v>
       </c>
       <c r="AG4">
-        <v>556.3200000000001</v>
+        <v>555</v>
       </c>
       <c r="AH4">
-        <v>530.3200000000001</v>
+        <v>530.67</v>
       </c>
       <c r="AI4">
         <v>564.71</v>
@@ -1212,7 +1241,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>30.16</v>
+        <v>26.69</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1373,12 +1402,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,377 +1450,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>0.89</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.41</v>
+      <c r="D7" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-4.97</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-4.46</v>
       </c>
+      <c r="D8" s="6">
+        <v>-5.23</v>
+      </c>
       <c r="E8" s="7">
-        <v>0.51</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>0.48</v>
       </c>
+      <c r="D9" s="6">
+        <v>-0.9399999999999999</v>
+      </c>
       <c r="E9" s="7">
-        <v>2.04</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-1.87</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-1.57</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.3</v>
+      <c r="D10" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.73</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-1.94</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-0.91</v>
       </c>
+      <c r="D11" s="6">
+        <v>-2.74</v>
+      </c>
       <c r="E11" s="7">
-        <v>1.03</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>1.11</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-1.23</v>
       </c>
-      <c r="E12" s="6">
-        <v>-2.34</v>
+      <c r="D12" s="6">
+        <v>-1.74</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-10.89</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.19</v>
+      <c r="D13" s="6">
+        <v>-6.96</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.93</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-27.62</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-26.65</v>
       </c>
+      <c r="D14" s="6">
+        <v>-27.16</v>
+      </c>
       <c r="E14" s="7">
-        <v>0.97</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-30.52</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-30.37</v>
       </c>
-      <c r="E15" s="7">
-        <v>0.15</v>
+      <c r="D15" s="6">
+        <v>-30.03</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.34</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-1.61</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>0.79</v>
       </c>
-      <c r="E16" s="7">
-        <v>2.4</v>
+      <c r="D16" s="6">
+        <v>3.71</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.92</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-4.51</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-3.02</v>
       </c>
+      <c r="D17" s="6">
+        <v>-5.25</v>
+      </c>
       <c r="E17" s="7">
-        <v>1.49</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-7.87</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-6.57</v>
       </c>
-      <c r="E18" s="7">
-        <v>1.3</v>
+      <c r="D18" s="6">
+        <v>-6.3</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.27</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-10.68</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-10.76</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.08</v>
+      <c r="D19" s="6">
+        <v>-8.92</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.84</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-29.57</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-28.65</v>
       </c>
+      <c r="D20" s="6">
+        <v>-29.77</v>
+      </c>
       <c r="E20" s="7">
-        <v>0.92</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-30.44</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-31.03</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="5">
-        <v>2575</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>2569</v>
       </c>
-      <c r="E21" s="6">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>2622.1</v>
+      </c>
+      <c r="E22" s="8">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>711</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>720.3</v>
       </c>
-      <c r="E22" s="7">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>709</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-11.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>548</v>
+      </c>
+      <c r="D24" s="6">
+        <v>543.35</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4.65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="5">
-        <v>48.74</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C25" s="6">
         <v>48.14</v>
       </c>
-      <c r="E23" s="6">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D25" s="6">
+        <v>53.63</v>
+      </c>
+      <c r="E25" s="8">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="5">
-        <v>30.01</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C26" s="6">
         <v>38.4</v>
       </c>
-      <c r="E24" s="7">
-        <v>8.390000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D26" s="6">
+        <v>33.19</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-5.21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>49.35</v>
+      </c>
+      <c r="D27" s="6">
+        <v>45.99</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="5">
-        <v>186.99</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C28" s="6">
         <v>-27.51</v>
       </c>
-      <c r="E25" s="6">
-        <v>-214.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D28" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="E28" s="8">
+        <v>28.18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="5">
-        <v>87.20999999999999</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C29" s="6">
         <v>-36.77</v>
       </c>
-      <c r="E26" s="6">
-        <v>-123.98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D29" s="6">
+        <v>210.49</v>
+      </c>
+      <c r="E29" s="8">
+        <v>247.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="5">
-        <v>-29.73</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C30" s="6">
         <v>-42.03</v>
       </c>
-      <c r="E27" s="6">
-        <v>-12.3</v>
+      <c r="D30" s="6">
+        <v>6.11</v>
+      </c>
+      <c r="E30" s="8">
+        <v>48.14</v>
       </c>
     </row>
   </sheetData>
@@ -1782,60 +1897,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
-        <v>36.52</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>48.52</v>
+      </c>
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>45.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-2.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="11">
+        <v>44.3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>30</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1937,25 +2052,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1327</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.006999999999999999</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0488</v>
+      <c r="A2" s="14">
+        <v>0.1362</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0118</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0518</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -178,16 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.1 → 53.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.1</t>
+    <t>53.6 → 46.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>53.6</t>
+  </si>
+  <si>
+    <t>46.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,8 +399,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -772,8 +772,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -913,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2622.1</v>
+        <v>2544.9</v>
       </c>
       <c r="D2">
-        <v>2.07</v>
+        <v>-2.94</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -925,46 +924,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-8.92</v>
+        <v>-11.6</v>
       </c>
       <c r="H2">
-        <v>20.89</v>
+        <v>17.33</v>
       </c>
       <c r="I2">
-        <v>0.16</v>
+        <v>-5.67</v>
       </c>
       <c r="J2">
-        <v>0.24</v>
+        <v>-2.14</v>
       </c>
       <c r="K2">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="L2">
-        <v>-6.96</v>
+        <v>-6.82</v>
       </c>
       <c r="M2">
-        <v>13.62</v>
+        <v>12.77</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="P2">
-        <v>2626.4</v>
+        <v>2595.78</v>
       </c>
       <c r="Q2">
-        <v>2566.72</v>
+        <v>2566.16</v>
       </c>
       <c r="R2">
-        <v>2616.49</v>
+        <v>2613.59</v>
       </c>
       <c r="S2">
-        <v>2579.82</v>
+        <v>2579.15</v>
       </c>
       <c r="T2">
-        <v>1.64</v>
+        <v>-1.33</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -976,37 +975,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>53.63</v>
+        <v>46</v>
       </c>
       <c r="Z2">
-        <v>7.88</v>
+        <v>3.22</v>
       </c>
       <c r="AA2">
-        <v>-1.49</v>
+        <v>-0.54</v>
       </c>
       <c r="AB2">
-        <v>9.369999999999999</v>
+        <v>3.76</v>
       </c>
       <c r="AC2">
-        <v>44.29</v>
+        <v>40.55</v>
       </c>
       <c r="AD2">
-        <v>56.77</v>
+        <v>45.73</v>
       </c>
       <c r="AE2">
-        <v>62.26</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AF2">
-        <v>0.67</v>
+        <v>13.63</v>
       </c>
       <c r="AG2">
-        <v>2682.34</v>
+        <v>2682.11</v>
       </c>
       <c r="AH2">
-        <v>2451.09</v>
+        <v>2450.21</v>
       </c>
       <c r="AI2">
         <v>2510.43</v>
@@ -1015,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>25.89</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1026,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>709</v>
+        <v>711.9</v>
       </c>
       <c r="D3">
-        <v>-1.57</v>
+        <v>0.41</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1038,46 +1037,46 @@
         <v>709</v>
       </c>
       <c r="G3">
-        <v>-29.77</v>
+        <v>-29.48</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="I3">
-        <v>-2.74</v>
+        <v>-2.14</v>
       </c>
       <c r="J3">
-        <v>-5.23</v>
+        <v>-5.46</v>
       </c>
       <c r="K3">
-        <v>-5.25</v>
+        <v>-5.54</v>
       </c>
       <c r="L3">
-        <v>-27.16</v>
+        <v>-25.67</v>
       </c>
       <c r="M3">
-        <v>-1.18</v>
+        <v>-1.07</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>719</v>
+        <v>715.88</v>
       </c>
       <c r="Q3">
-        <v>726.5599999999999</v>
+        <v>725.0599999999999</v>
       </c>
       <c r="R3">
-        <v>762.3</v>
+        <v>760.8099999999999</v>
       </c>
       <c r="S3">
-        <v>845.29</v>
+        <v>843.92</v>
       </c>
       <c r="T3">
-        <v>-16.12</v>
+        <v>-15.64</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1092,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.19</v>
+        <v>35.6</v>
       </c>
       <c r="Z3">
-        <v>-11.44</v>
+        <v>-11.47</v>
       </c>
       <c r="AA3">
-        <v>-11.92</v>
+        <v>-11.83</v>
       </c>
       <c r="AB3">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
       <c r="AC3">
-        <v>40.34</v>
+        <v>59.85</v>
       </c>
       <c r="AD3">
-        <v>52.29</v>
+        <v>52.76</v>
       </c>
       <c r="AE3">
-        <v>12.24</v>
+        <v>12.58</v>
       </c>
       <c r="AF3">
-        <v>210.49</v>
+        <v>60.57</v>
       </c>
       <c r="AG3">
-        <v>741.6799999999999</v>
+        <v>739.6900000000001</v>
       </c>
       <c r="AH3">
-        <v>711.45</v>
+        <v>710.4299999999999</v>
       </c>
       <c r="AI3">
-        <v>744.99</v>
+        <v>744.72</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>38.57</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1139,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>543.35</v>
+        <v>540.3</v>
       </c>
       <c r="D4">
-        <v>-0.85</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1151,46 +1150,46 @@
         <v>535.85</v>
       </c>
       <c r="G4">
-        <v>-31.03</v>
+        <v>-31.42</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>0.83</v>
       </c>
       <c r="I4">
-        <v>-1.74</v>
+        <v>-1.17</v>
       </c>
       <c r="J4">
-        <v>-0.9399999999999999</v>
+        <v>-2.31</v>
       </c>
       <c r="K4">
-        <v>-6.3</v>
+        <v>-5.94</v>
       </c>
       <c r="L4">
-        <v>-30.03</v>
+        <v>-30.32</v>
       </c>
       <c r="M4">
-        <v>-5.18</v>
+        <v>-5.31</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>547.8099999999999</v>
+        <v>546.53</v>
       </c>
       <c r="Q4">
-        <v>542.83</v>
+        <v>543.05</v>
       </c>
       <c r="R4">
-        <v>556.74</v>
+        <v>555.61</v>
       </c>
       <c r="S4">
-        <v>646.25</v>
+        <v>645.04</v>
       </c>
       <c r="T4">
-        <v>-15.92</v>
+        <v>-16.24</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1205,34 +1204,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>45.99</v>
+        <v>43.88</v>
       </c>
       <c r="Z4">
-        <v>-1.98</v>
+        <v>-2.3</v>
       </c>
       <c r="AA4">
-        <v>-3.56</v>
+        <v>-3.31</v>
       </c>
       <c r="AB4">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="AC4">
-        <v>62.42</v>
+        <v>51.04</v>
       </c>
       <c r="AD4">
-        <v>71.34</v>
+        <v>63.35</v>
       </c>
       <c r="AE4">
-        <v>9.859999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AF4">
-        <v>6.11</v>
+        <v>-1.22</v>
       </c>
       <c r="AG4">
-        <v>555</v>
+        <v>554.85</v>
       </c>
       <c r="AH4">
-        <v>530.67</v>
+        <v>531.26</v>
       </c>
       <c r="AI4">
         <v>564.71</v>
@@ -1241,7 +1240,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>26.69</v>
+        <v>24.33</v>
       </c>
     </row>
   </sheetData>
@@ -1474,13 +1473,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>0.89</v>
+        <v>0.24</v>
       </c>
       <c r="D7" s="6">
-        <v>0.24</v>
+        <v>-2.14</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.65</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1491,13 +1490,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-4.46</v>
+        <v>-5.23</v>
       </c>
       <c r="D8" s="6">
-        <v>-5.23</v>
+        <v>-5.46</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.77</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1508,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.48</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.9399999999999999</v>
+        <v>-2.31</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.42</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1525,13 +1524,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-1.57</v>
+        <v>0.16</v>
       </c>
       <c r="D10" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.73</v>
+        <v>-5.67</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-5.83</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1542,13 +1541,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.91</v>
+        <v>-2.74</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.74</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.83</v>
+        <v>-2.14</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1559,13 +1558,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-1.23</v>
+        <v>-1.74</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.74</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.51</v>
+        <v>-1.17</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1576,13 +1575,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-10.89</v>
+        <v>-6.96</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.96</v>
+        <v>-6.82</v>
       </c>
       <c r="E13" s="8">
-        <v>3.93</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1593,13 +1592,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-26.65</v>
+        <v>-27.16</v>
       </c>
       <c r="D14" s="6">
-        <v>-27.16</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.51</v>
+        <v>-25.67</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.49</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1610,13 +1609,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-30.37</v>
+        <v>-30.03</v>
       </c>
       <c r="D15" s="6">
-        <v>-30.03</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.34</v>
+        <v>-30.32</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1627,13 +1626,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>0.79</v>
+        <v>3.71</v>
       </c>
       <c r="D16" s="6">
-        <v>3.71</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.92</v>
+        <v>3.61</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1644,13 +1643,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.02</v>
+        <v>-5.25</v>
       </c>
       <c r="D17" s="6">
-        <v>-5.25</v>
+        <v>-5.54</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.23</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1661,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-6.57</v>
+        <v>-6.3</v>
       </c>
       <c r="D18" s="6">
-        <v>-6.3</v>
+        <v>-5.94</v>
       </c>
       <c r="E18" s="8">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1678,13 +1677,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-10.76</v>
+        <v>-8.92</v>
       </c>
       <c r="D19" s="6">
-        <v>-8.92</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.84</v>
+        <v>-11.6</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1695,13 +1694,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-28.65</v>
+        <v>-29.77</v>
       </c>
       <c r="D20" s="6">
-        <v>-29.77</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.12</v>
+        <v>-29.48</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1712,13 +1711,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-30.44</v>
+        <v>-31.03</v>
       </c>
       <c r="D21" s="6">
-        <v>-31.03</v>
+        <v>-31.42</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.59</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1729,13 +1728,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>2569</v>
+        <v>2622.1</v>
       </c>
       <c r="D22" s="6">
-        <v>2622.1</v>
-      </c>
-      <c r="E22" s="8">
-        <v>53.1</v>
+        <v>2544.9</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-77.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1746,13 +1745,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>720.3</v>
+        <v>709</v>
       </c>
       <c r="D23" s="6">
-        <v>709</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-11.3</v>
+        <v>711.9</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1763,13 +1762,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>548</v>
+        <v>543.35</v>
       </c>
       <c r="D24" s="6">
-        <v>543.35</v>
+        <v>540.3</v>
       </c>
       <c r="E24" s="7">
-        <v>-4.65</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1780,13 +1779,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>48.14</v>
+        <v>53.63</v>
       </c>
       <c r="D25" s="6">
-        <v>53.63</v>
-      </c>
-      <c r="E25" s="8">
-        <v>5.49</v>
+        <v>46</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-7.63</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1797,13 +1796,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>38.4</v>
+        <v>33.19</v>
       </c>
       <c r="D26" s="6">
-        <v>33.19</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-5.21</v>
+        <v>35.6</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2.41</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1814,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>49.35</v>
+        <v>45.99</v>
       </c>
       <c r="D27" s="6">
-        <v>45.99</v>
+        <v>43.88</v>
       </c>
       <c r="E27" s="7">
-        <v>-3.36</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1831,13 +1830,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-27.51</v>
+        <v>0.67</v>
       </c>
       <c r="D28" s="6">
-        <v>0.67</v>
+        <v>13.63</v>
       </c>
       <c r="E28" s="8">
-        <v>28.18</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1848,13 +1847,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>-36.77</v>
+        <v>210.49</v>
       </c>
       <c r="D29" s="6">
-        <v>210.49</v>
-      </c>
-      <c r="E29" s="8">
-        <v>247.26</v>
+        <v>60.57</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-149.92</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1865,13 +1864,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-42.03</v>
+        <v>6.11</v>
       </c>
       <c r="D30" s="6">
-        <v>6.11</v>
-      </c>
-      <c r="E30" s="8">
-        <v>48.14</v>
+        <v>-1.22</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-7.33</v>
       </c>
     </row>
   </sheetData>
@@ -1930,19 +1929,19 @@
         <v>40</v>
       </c>
       <c r="B2" s="11">
-        <v>48.52</v>
+        <v>36.52</v>
       </c>
       <c r="C2" s="12">
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>44.3</v>
+        <v>41.8</v>
       </c>
       <c r="E2" s="11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>-2</v>
+        <v>-3.3</v>
       </c>
       <c r="G2" s="11">
         <v>-2.6</v>
@@ -2064,13 +2063,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1362</v>
+        <v>0.1277</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0118</v>
+        <v>-0.0107</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0518</v>
+        <v>-0.05309999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>53.6 → 46.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.6</t>
-  </si>
-  <si>
-    <t>46.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,15 +362,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -912,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2544.9</v>
+        <v>2525.7</v>
       </c>
       <c r="D2">
-        <v>-2.94</v>
+        <v>-0.75</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -924,46 +896,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-11.6</v>
+        <v>-12.26</v>
       </c>
       <c r="H2">
-        <v>17.33</v>
+        <v>16.45</v>
       </c>
       <c r="I2">
-        <v>-5.67</v>
+        <v>-5.33</v>
       </c>
       <c r="J2">
-        <v>-2.14</v>
+        <v>-1.19</v>
       </c>
       <c r="K2">
-        <v>3.61</v>
+        <v>2.3</v>
       </c>
       <c r="L2">
-        <v>-6.82</v>
+        <v>-5.51</v>
       </c>
       <c r="M2">
-        <v>12.77</v>
+        <v>12.51</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P2">
-        <v>2595.78</v>
+        <v>2567.34</v>
       </c>
       <c r="Q2">
-        <v>2566.16</v>
+        <v>2564.34</v>
       </c>
       <c r="R2">
-        <v>2613.59</v>
+        <v>2610.51</v>
       </c>
       <c r="S2">
-        <v>2579.15</v>
+        <v>2578.53</v>
       </c>
       <c r="T2">
-        <v>-1.33</v>
+        <v>-2.05</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +950,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>46</v>
+        <v>44.32</v>
       </c>
       <c r="Z2">
-        <v>3.22</v>
+        <v>-2</v>
       </c>
       <c r="AA2">
-        <v>-0.54</v>
+        <v>-0.84</v>
       </c>
       <c r="AB2">
-        <v>3.76</v>
+        <v>-1.16</v>
       </c>
       <c r="AC2">
-        <v>40.55</v>
+        <v>35.32</v>
       </c>
       <c r="AD2">
-        <v>45.73</v>
+        <v>40.05</v>
       </c>
       <c r="AE2">
-        <v>64.68000000000001</v>
+        <v>64.91</v>
       </c>
       <c r="AF2">
-        <v>13.63</v>
+        <v>14.07</v>
       </c>
       <c r="AG2">
-        <v>2682.11</v>
+        <v>2681.7</v>
       </c>
       <c r="AH2">
-        <v>2450.21</v>
+        <v>2446.99</v>
       </c>
       <c r="AI2">
         <v>2510.43</v>
@@ -1014,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>23.57</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,37 +997,37 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>711.9</v>
+        <v>700.8</v>
       </c>
       <c r="D3">
-        <v>0.41</v>
+        <v>-1.56</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
       </c>
       <c r="F3">
-        <v>709</v>
+        <v>700.8</v>
       </c>
       <c r="G3">
-        <v>-29.48</v>
+        <v>-30.58</v>
       </c>
       <c r="H3">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-2.14</v>
+        <v>-3.63</v>
       </c>
       <c r="J3">
-        <v>-5.46</v>
+        <v>-5.55</v>
       </c>
       <c r="K3">
-        <v>-5.54</v>
+        <v>-7.08</v>
       </c>
       <c r="L3">
-        <v>-25.67</v>
+        <v>-26.36</v>
       </c>
       <c r="M3">
-        <v>-1.07</v>
+        <v>-1.5</v>
       </c>
       <c r="N3">
         <v>66</v>
@@ -1064,19 +1036,19 @@
         <v>23</v>
       </c>
       <c r="P3">
-        <v>715.88</v>
+        <v>710.6</v>
       </c>
       <c r="Q3">
-        <v>725.0599999999999</v>
+        <v>723.35</v>
       </c>
       <c r="R3">
-        <v>760.8099999999999</v>
+        <v>759.33</v>
       </c>
       <c r="S3">
-        <v>843.92</v>
+        <v>842.47</v>
       </c>
       <c r="T3">
-        <v>-15.64</v>
+        <v>-16.82</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1091,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.6</v>
+        <v>30.99</v>
       </c>
       <c r="Z3">
-        <v>-11.47</v>
+        <v>-12.24</v>
       </c>
       <c r="AA3">
-        <v>-11.83</v>
+        <v>-11.91</v>
       </c>
       <c r="AB3">
-        <v>0.37</v>
+        <v>-0.33</v>
       </c>
       <c r="AC3">
-        <v>59.85</v>
+        <v>34.03</v>
       </c>
       <c r="AD3">
-        <v>52.76</v>
+        <v>44.74</v>
       </c>
       <c r="AE3">
-        <v>12.58</v>
+        <v>12.53</v>
       </c>
       <c r="AF3">
-        <v>60.57</v>
+        <v>27.04</v>
       </c>
       <c r="AG3">
-        <v>739.6900000000001</v>
+        <v>740.8099999999999</v>
       </c>
       <c r="AH3">
-        <v>710.4299999999999</v>
+        <v>705.89</v>
       </c>
       <c r="AI3">
-        <v>744.72</v>
+        <v>740.42</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>34.37</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,58 +1110,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>540.3</v>
+        <v>533</v>
       </c>
       <c r="D4">
-        <v>-0.5600000000000001</v>
+        <v>-1.35</v>
       </c>
       <c r="E4">
         <v>787.8</v>
       </c>
       <c r="F4">
-        <v>535.85</v>
+        <v>533</v>
       </c>
       <c r="G4">
-        <v>-31.42</v>
+        <v>-32.34</v>
       </c>
       <c r="H4">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.17</v>
+        <v>-3.62</v>
       </c>
       <c r="J4">
-        <v>-2.31</v>
+        <v>-0.55</v>
       </c>
       <c r="K4">
-        <v>-5.94</v>
+        <v>-7.1</v>
       </c>
       <c r="L4">
-        <v>-30.32</v>
+        <v>-30.96</v>
       </c>
       <c r="M4">
-        <v>-5.31</v>
+        <v>-6.6</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>546.53</v>
+        <v>542.53</v>
       </c>
       <c r="Q4">
-        <v>543.05</v>
+        <v>542.45</v>
       </c>
       <c r="R4">
-        <v>555.61</v>
+        <v>554.3200000000001</v>
       </c>
       <c r="S4">
-        <v>645.04</v>
+        <v>643.84</v>
       </c>
       <c r="T4">
-        <v>-16.24</v>
+        <v>-17.22</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,43 +1176,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.88</v>
+        <v>39.23</v>
       </c>
       <c r="Z4">
-        <v>-2.3</v>
+        <v>-3.11</v>
       </c>
       <c r="AA4">
-        <v>-3.31</v>
+        <v>-3.27</v>
       </c>
       <c r="AB4">
-        <v>1.01</v>
+        <v>0.16</v>
       </c>
       <c r="AC4">
-        <v>51.04</v>
+        <v>30.27</v>
       </c>
       <c r="AD4">
-        <v>63.35</v>
+        <v>47.91</v>
       </c>
       <c r="AE4">
-        <v>9.640000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AF4">
-        <v>-1.22</v>
+        <v>-64.34</v>
       </c>
       <c r="AG4">
-        <v>554.85</v>
+        <v>555.02</v>
       </c>
       <c r="AH4">
-        <v>531.26</v>
+        <v>529.88</v>
       </c>
       <c r="AI4">
-        <v>564.71</v>
+        <v>563.65</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>24.33</v>
+        <v>24.49</v>
       </c>
     </row>
   </sheetData>
@@ -1401,47 +1373,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1449,428 +1386,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>0.24</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-2.14</v>
       </c>
-      <c r="E7" s="7">
-        <v>-2.38</v>
+      <c r="D7" s="5">
+        <v>-1.19</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.95</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.23</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-5.46</v>
       </c>
+      <c r="D8" s="5">
+        <v>-5.55</v>
+      </c>
       <c r="E8" s="7">
-        <v>-0.23</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-2.31</v>
       </c>
-      <c r="E9" s="7">
-        <v>-1.37</v>
+      <c r="D9" s="5">
+        <v>-0.55</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.76</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-5.67</v>
       </c>
-      <c r="E10" s="7">
-        <v>-5.83</v>
+      <c r="D10" s="5">
+        <v>-5.33</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.34</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-2.74</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-2.14</v>
       </c>
-      <c r="E11" s="8">
-        <v>0.6</v>
+      <c r="D11" s="5">
+        <v>-3.63</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-1.74</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-1.17</v>
       </c>
-      <c r="E12" s="8">
-        <v>0.57</v>
+      <c r="D12" s="5">
+        <v>-3.62</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-6.96</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-6.82</v>
       </c>
-      <c r="E13" s="8">
-        <v>0.14</v>
+      <c r="D13" s="5">
+        <v>-5.51</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.31</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-27.16</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-25.67</v>
       </c>
-      <c r="E14" s="8">
-        <v>1.49</v>
+      <c r="D14" s="5">
+        <v>-26.36</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-30.03</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-30.32</v>
       </c>
+      <c r="D15" s="5">
+        <v>-30.96</v>
+      </c>
       <c r="E15" s="7">
-        <v>-0.29</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>3.71</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>3.61</v>
       </c>
+      <c r="D16" s="5">
+        <v>2.3</v>
+      </c>
       <c r="E16" s="7">
-        <v>-0.1</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-5.25</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-5.54</v>
       </c>
+      <c r="D17" s="5">
+        <v>-7.08</v>
+      </c>
       <c r="E17" s="7">
-        <v>-0.29</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-6.3</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-5.94</v>
       </c>
-      <c r="E18" s="8">
-        <v>0.36</v>
+      <c r="D18" s="5">
+        <v>-7.1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-8.92</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-11.6</v>
       </c>
+      <c r="D19" s="5">
+        <v>-12.26</v>
+      </c>
       <c r="E19" s="7">
-        <v>-2.68</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-29.77</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-29.48</v>
       </c>
-      <c r="E20" s="8">
-        <v>0.29</v>
+      <c r="D20" s="5">
+        <v>-30.58</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-31.03</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-31.42</v>
       </c>
+      <c r="D21" s="5">
+        <v>-32.34</v>
+      </c>
       <c r="E21" s="7">
-        <v>-0.39</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>2622.1</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>2544.9</v>
       </c>
+      <c r="D22" s="5">
+        <v>2525.7</v>
+      </c>
       <c r="E22" s="7">
-        <v>-77.2</v>
+        <v>-19.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>709</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>711.9</v>
       </c>
-      <c r="E23" s="8">
-        <v>2.9</v>
+      <c r="D23" s="5">
+        <v>700.8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-11.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>543.35</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>540.3</v>
       </c>
+      <c r="D24" s="5">
+        <v>533</v>
+      </c>
       <c r="E24" s="7">
-        <v>-3.05</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>53.63</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>46</v>
       </c>
+      <c r="D25" s="5">
+        <v>44.32</v>
+      </c>
       <c r="E25" s="7">
-        <v>-7.63</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>33.19</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>35.6</v>
       </c>
-      <c r="E26" s="8">
-        <v>2.41</v>
+      <c r="D26" s="5">
+        <v>30.99</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.61</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>45.99</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>43.88</v>
       </c>
+      <c r="D27" s="5">
+        <v>39.23</v>
+      </c>
       <c r="E27" s="7">
-        <v>-2.11</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>0.67</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>13.63</v>
       </c>
-      <c r="E28" s="8">
-        <v>12.96</v>
+      <c r="D28" s="5">
+        <v>14.07</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.44</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>210.49</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>60.57</v>
       </c>
+      <c r="D29" s="5">
+        <v>27.04</v>
+      </c>
       <c r="E29" s="7">
-        <v>-149.92</v>
+        <v>-33.53</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>6.11</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-1.22</v>
       </c>
+      <c r="D30" s="5">
+        <v>-64.34</v>
+      </c>
       <c r="E30" s="7">
-        <v>-7.33</v>
+        <v>-63.12</v>
       </c>
     </row>
   </sheetData>
@@ -1896,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-2.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-2.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-4</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2051,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1277</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0107</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.05309999999999999</v>
+      <c r="A2" s="13">
+        <v>0.1251</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.015</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.066</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,7 +744,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -884,10 +885,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2525.7</v>
+        <v>2510.8</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>-0.59</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -896,25 +897,25 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-12.26</v>
+        <v>-12.78</v>
       </c>
       <c r="H2">
-        <v>16.45</v>
+        <v>15.76</v>
       </c>
       <c r="I2">
-        <v>-5.33</v>
+        <v>-2.49</v>
       </c>
       <c r="J2">
-        <v>-1.19</v>
+        <v>-2</v>
       </c>
       <c r="K2">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="L2">
-        <v>-5.51</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="M2">
-        <v>12.51</v>
+        <v>12</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -923,19 +924,19 @@
         <v>47</v>
       </c>
       <c r="P2">
-        <v>2567.34</v>
+        <v>2554.5</v>
       </c>
       <c r="Q2">
-        <v>2564.34</v>
+        <v>2562.98</v>
       </c>
       <c r="R2">
-        <v>2610.51</v>
+        <v>2608.22</v>
       </c>
       <c r="S2">
-        <v>2578.53</v>
+        <v>2577.78</v>
       </c>
       <c r="T2">
-        <v>-2.05</v>
+        <v>-2.6</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +951,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>44.32</v>
+        <v>43</v>
       </c>
       <c r="Z2">
-        <v>-2</v>
+        <v>-7.26</v>
       </c>
       <c r="AA2">
-        <v>-0.84</v>
+        <v>-2.12</v>
       </c>
       <c r="AB2">
-        <v>-1.16</v>
+        <v>-5.14</v>
       </c>
       <c r="AC2">
-        <v>35.32</v>
+        <v>15.82</v>
       </c>
       <c r="AD2">
-        <v>40.05</v>
+        <v>30.56</v>
       </c>
       <c r="AE2">
-        <v>64.91</v>
+        <v>63.8</v>
       </c>
       <c r="AF2">
-        <v>14.07</v>
+        <v>-11.19</v>
       </c>
       <c r="AG2">
-        <v>2681.7</v>
+        <v>2682.24</v>
       </c>
       <c r="AH2">
-        <v>2446.99</v>
+        <v>2443.72</v>
       </c>
       <c r="AI2">
         <v>2510.43</v>
@@ -986,7 +987,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>22.53</v>
+        <v>21.09</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +998,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>700.8</v>
+        <v>706.65</v>
       </c>
       <c r="D3">
-        <v>-1.56</v>
+        <v>0.83</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1009,46 +1010,46 @@
         <v>700.8</v>
       </c>
       <c r="G3">
-        <v>-30.58</v>
+        <v>-30</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="I3">
-        <v>-3.63</v>
+        <v>-0.61</v>
       </c>
       <c r="J3">
-        <v>-5.55</v>
+        <v>-3.86</v>
       </c>
       <c r="K3">
-        <v>-7.08</v>
+        <v>-5.41</v>
       </c>
       <c r="L3">
-        <v>-26.36</v>
+        <v>-25.66</v>
       </c>
       <c r="M3">
-        <v>-1.5</v>
+        <v>-1.17</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P3">
-        <v>710.6</v>
+        <v>709.73</v>
       </c>
       <c r="Q3">
-        <v>723.35</v>
+        <v>721.97</v>
       </c>
       <c r="R3">
-        <v>759.33</v>
+        <v>757.6</v>
       </c>
       <c r="S3">
-        <v>842.47</v>
+        <v>841.02</v>
       </c>
       <c r="T3">
-        <v>-16.82</v>
+        <v>-15.98</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,34 +1064,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>30.99</v>
+        <v>35.72</v>
       </c>
       <c r="Z3">
         <v>-12.24</v>
       </c>
       <c r="AA3">
-        <v>-11.91</v>
+        <v>-11.98</v>
       </c>
       <c r="AB3">
-        <v>-0.33</v>
+        <v>-0.26</v>
       </c>
       <c r="AC3">
-        <v>34.03</v>
+        <v>42.84</v>
       </c>
       <c r="AD3">
-        <v>44.74</v>
+        <v>45.57</v>
       </c>
       <c r="AE3">
-        <v>12.53</v>
+        <v>12.48</v>
       </c>
       <c r="AF3">
-        <v>27.04</v>
+        <v>-5.51</v>
       </c>
       <c r="AG3">
-        <v>740.8099999999999</v>
+        <v>740.14</v>
       </c>
       <c r="AH3">
-        <v>705.89</v>
+        <v>703.8</v>
       </c>
       <c r="AI3">
         <v>740.42</v>
@@ -1099,7 +1100,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>30.74</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1111,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>533</v>
+        <v>533.5</v>
       </c>
       <c r="D4">
-        <v>-1.35</v>
+        <v>0.09</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1122,46 +1123,46 @@
         <v>533</v>
       </c>
       <c r="G4">
-        <v>-32.34</v>
+        <v>-32.28</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I4">
-        <v>-3.62</v>
+        <v>-2.65</v>
       </c>
       <c r="J4">
-        <v>-0.55</v>
+        <v>-2.11</v>
       </c>
       <c r="K4">
-        <v>-7.1</v>
+        <v>-7.27</v>
       </c>
       <c r="L4">
-        <v>-30.96</v>
+        <v>-31.76</v>
       </c>
       <c r="M4">
-        <v>-6.6</v>
+        <v>-5.96</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>542.53</v>
+        <v>539.63</v>
       </c>
       <c r="Q4">
-        <v>542.45</v>
+        <v>542</v>
       </c>
       <c r="R4">
-        <v>554.3200000000001</v>
+        <v>553.15</v>
       </c>
       <c r="S4">
-        <v>643.84</v>
+        <v>642.66</v>
       </c>
       <c r="T4">
-        <v>-17.22</v>
+        <v>-16.99</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1177,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.23</v>
+        <v>39.71</v>
       </c>
       <c r="Z4">
-        <v>-3.11</v>
+        <v>-3.67</v>
       </c>
       <c r="AA4">
-        <v>-3.27</v>
+        <v>-3.35</v>
       </c>
       <c r="AB4">
-        <v>0.16</v>
+        <v>-0.32</v>
       </c>
       <c r="AC4">
-        <v>30.27</v>
+        <v>15.23</v>
       </c>
       <c r="AD4">
-        <v>47.91</v>
+        <v>32.18</v>
       </c>
       <c r="AE4">
-        <v>9.539999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="AF4">
-        <v>-64.34</v>
+        <v>-50.5</v>
       </c>
       <c r="AG4">
-        <v>555.02</v>
+        <v>555.2</v>
       </c>
       <c r="AH4">
-        <v>529.88</v>
+        <v>528.8099999999999</v>
       </c>
       <c r="AI4">
         <v>563.65</v>
@@ -1212,7 +1213,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>24.49</v>
+        <v>23.58</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1411,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-2.14</v>
+        <v>-1.19</v>
       </c>
       <c r="D7" s="5">
-        <v>-1.19</v>
+        <v>-2</v>
       </c>
       <c r="E7" s="6">
-        <v>0.95</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1428,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-5.46</v>
+        <v>-5.55</v>
       </c>
       <c r="D8" s="5">
-        <v>-5.55</v>
+        <v>-3.86</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.09</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1445,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-2.31</v>
+        <v>-0.55</v>
       </c>
       <c r="D9" s="5">
-        <v>-0.55</v>
+        <v>-2.11</v>
       </c>
       <c r="E9" s="6">
-        <v>1.76</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1462,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-5.67</v>
+        <v>-5.33</v>
       </c>
       <c r="D10" s="5">
-        <v>-5.33</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.34</v>
+        <v>-2.49</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.84</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1479,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-2.14</v>
+        <v>-3.63</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.63</v>
+        <v>-0.61</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.49</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1496,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-1.17</v>
+        <v>-3.62</v>
       </c>
       <c r="D12" s="5">
-        <v>-3.62</v>
+        <v>-2.65</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.45</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1513,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-6.82</v>
+        <v>-5.51</v>
       </c>
       <c r="D13" s="5">
-        <v>-5.51</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="E13" s="6">
-        <v>1.31</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1530,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-25.67</v>
+        <v>-26.36</v>
       </c>
       <c r="D14" s="5">
-        <v>-26.36</v>
+        <v>-25.66</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.6899999999999999</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1547,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-30.32</v>
+        <v>-30.96</v>
       </c>
       <c r="D15" s="5">
-        <v>-30.96</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.64</v>
+        <v>-31.76</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1564,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>3.61</v>
+        <v>2.3</v>
       </c>
       <c r="D16" s="5">
-        <v>2.3</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.31</v>
+        <v>0.6</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1581,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-5.54</v>
+        <v>-7.08</v>
       </c>
       <c r="D17" s="5">
-        <v>-7.08</v>
+        <v>-5.41</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.54</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1598,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-5.94</v>
+        <v>-7.1</v>
       </c>
       <c r="D18" s="5">
-        <v>-7.1</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.16</v>
+        <v>-7.27</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1615,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-11.6</v>
+        <v>-12.26</v>
       </c>
       <c r="D19" s="5">
-        <v>-12.26</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.66</v>
+        <v>-12.78</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1632,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-29.48</v>
+        <v>-30.58</v>
       </c>
       <c r="D20" s="5">
-        <v>-30.58</v>
+        <v>-30</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.1</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1649,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-31.42</v>
+        <v>-32.34</v>
       </c>
       <c r="D21" s="5">
-        <v>-32.34</v>
+        <v>-32.28</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.92</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1666,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2544.9</v>
+        <v>2525.7</v>
       </c>
       <c r="D22" s="5">
-        <v>2525.7</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-19.2</v>
+        <v>2510.8</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-14.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1683,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>711.9</v>
+        <v>700.8</v>
       </c>
       <c r="D23" s="5">
-        <v>700.8</v>
+        <v>706.65</v>
       </c>
       <c r="E23" s="7">
-        <v>-11.1</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1700,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>540.3</v>
+        <v>533</v>
       </c>
       <c r="D24" s="5">
-        <v>533</v>
+        <v>533.5</v>
       </c>
       <c r="E24" s="7">
-        <v>-7.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1717,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>46</v>
+        <v>44.32</v>
       </c>
       <c r="D25" s="5">
-        <v>44.32</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.68</v>
+        <v>43</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1734,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>35.6</v>
+        <v>30.99</v>
       </c>
       <c r="D26" s="5">
-        <v>30.99</v>
+        <v>35.72</v>
       </c>
       <c r="E26" s="7">
-        <v>-4.61</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1751,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>43.88</v>
+        <v>39.23</v>
       </c>
       <c r="D27" s="5">
-        <v>39.23</v>
+        <v>39.71</v>
       </c>
       <c r="E27" s="7">
-        <v>-4.65</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1768,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>13.63</v>
+        <v>14.07</v>
       </c>
       <c r="D28" s="5">
-        <v>14.07</v>
+        <v>-11.19</v>
       </c>
       <c r="E28" s="6">
-        <v>0.44</v>
+        <v>-25.26</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1785,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>60.57</v>
+        <v>27.04</v>
       </c>
       <c r="D29" s="5">
-        <v>27.04</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-33.53</v>
+        <v>-5.51</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-32.55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1802,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-1.22</v>
+        <v>-64.34</v>
       </c>
       <c r="D30" s="5">
-        <v>-64.34</v>
+        <v>-50.5</v>
       </c>
       <c r="E30" s="7">
-        <v>-63.12</v>
+        <v>13.84</v>
       </c>
     </row>
   </sheetData>
@@ -1872,13 +1873,13 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.4</v>
+        <v>-2.7</v>
       </c>
       <c r="G2" s="10">
         <v>-4</v>
@@ -2000,13 +2001,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1251</v>
+        <v>0.12</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.015</v>
+        <v>-0.0117</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.066</v>
+        <v>-0.0596</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -151,16 +151,40 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>39.7 → 50.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>39.7</t>
+  </si>
+  <si>
+    <t>50.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -246,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,17 +386,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -744,8 +769,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -885,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2510.8</v>
+        <v>2458.3</v>
       </c>
       <c r="D2">
-        <v>-0.59</v>
+        <v>-2.09</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -897,46 +921,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-12.78</v>
+        <v>-14.61</v>
       </c>
       <c r="H2">
-        <v>15.76</v>
+        <v>13.34</v>
       </c>
       <c r="I2">
-        <v>-2.49</v>
+        <v>-4.31</v>
       </c>
       <c r="J2">
-        <v>-2</v>
+        <v>-3.14</v>
       </c>
       <c r="K2">
-        <v>0.6</v>
+        <v>0.22</v>
       </c>
       <c r="L2">
-        <v>-8.029999999999999</v>
+        <v>-9.16</v>
       </c>
       <c r="M2">
-        <v>12</v>
+        <v>11.36</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="P2">
-        <v>2554.5</v>
+        <v>2532.36</v>
       </c>
       <c r="Q2">
-        <v>2562.98</v>
+        <v>2558.64</v>
       </c>
       <c r="R2">
-        <v>2608.22</v>
+        <v>2604.39</v>
       </c>
       <c r="S2">
-        <v>2577.78</v>
+        <v>2576.87</v>
       </c>
       <c r="T2">
-        <v>-2.6</v>
+        <v>-4.6</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -951,43 +975,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>43</v>
+        <v>38.64</v>
       </c>
       <c r="Z2">
-        <v>-7.26</v>
+        <v>-15.48</v>
       </c>
       <c r="AA2">
-        <v>-2.12</v>
+        <v>-4.79</v>
       </c>
       <c r="AB2">
-        <v>-5.14</v>
+        <v>-10.69</v>
       </c>
       <c r="AC2">
-        <v>15.82</v>
+        <v>6.75</v>
       </c>
       <c r="AD2">
-        <v>30.56</v>
+        <v>19.3</v>
       </c>
       <c r="AE2">
-        <v>63.8</v>
+        <v>63.66</v>
       </c>
       <c r="AF2">
-        <v>-11.19</v>
+        <v>-0.35</v>
       </c>
       <c r="AG2">
-        <v>2682.24</v>
+        <v>2686.64</v>
       </c>
       <c r="AH2">
-        <v>2443.72</v>
+        <v>2430.65</v>
       </c>
       <c r="AI2">
-        <v>2510.43</v>
+        <v>2677.88</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>21.09</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -998,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>706.65</v>
+        <v>712.1</v>
       </c>
       <c r="D3">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1010,25 +1034,25 @@
         <v>700.8</v>
       </c>
       <c r="G3">
-        <v>-30</v>
+        <v>-29.46</v>
       </c>
       <c r="H3">
-        <v>0.83</v>
+        <v>1.61</v>
       </c>
       <c r="I3">
-        <v>-0.61</v>
+        <v>-1.14</v>
       </c>
       <c r="J3">
-        <v>-3.86</v>
+        <v>-3.02</v>
       </c>
       <c r="K3">
-        <v>-5.41</v>
+        <v>-3.59</v>
       </c>
       <c r="L3">
-        <v>-25.66</v>
+        <v>-24.61</v>
       </c>
       <c r="M3">
-        <v>-1.17</v>
+        <v>-0.89</v>
       </c>
       <c r="N3">
         <v>66</v>
@@ -1037,19 +1061,19 @@
         <v>26</v>
       </c>
       <c r="P3">
-        <v>709.73</v>
+        <v>708.09</v>
       </c>
       <c r="Q3">
-        <v>721.97</v>
+        <v>721.02</v>
       </c>
       <c r="R3">
-        <v>757.6</v>
+        <v>755.92</v>
       </c>
       <c r="S3">
-        <v>841.02</v>
+        <v>839.62</v>
       </c>
       <c r="T3">
-        <v>-15.98</v>
+        <v>-15.19</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1064,43 +1088,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.72</v>
+        <v>39.85</v>
       </c>
       <c r="Z3">
-        <v>-12.24</v>
+        <v>-11.66</v>
       </c>
       <c r="AA3">
-        <v>-11.98</v>
+        <v>-11.91</v>
       </c>
       <c r="AB3">
-        <v>-0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AC3">
-        <v>42.84</v>
+        <v>56.66</v>
       </c>
       <c r="AD3">
-        <v>45.57</v>
+        <v>44.51</v>
       </c>
       <c r="AE3">
-        <v>12.48</v>
+        <v>12.29</v>
       </c>
       <c r="AF3">
-        <v>-5.51</v>
+        <v>-47.89</v>
       </c>
       <c r="AG3">
-        <v>740.14</v>
+        <v>739.1799999999999</v>
       </c>
       <c r="AH3">
-        <v>703.8</v>
+        <v>702.87</v>
       </c>
       <c r="AI3">
         <v>740.42</v>
       </c>
       <c r="AJ3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK3">
-        <v>28</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1111,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>533.5</v>
+        <v>546.4</v>
       </c>
       <c r="D4">
-        <v>0.09</v>
+        <v>2.42</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1123,46 +1147,46 @@
         <v>533</v>
       </c>
       <c r="G4">
-        <v>-32.28</v>
+        <v>-30.64</v>
       </c>
       <c r="H4">
-        <v>0.09</v>
+        <v>2.51</v>
       </c>
       <c r="I4">
-        <v>-2.65</v>
+        <v>-0.29</v>
       </c>
       <c r="J4">
-        <v>-2.11</v>
+        <v>0.72</v>
       </c>
       <c r="K4">
-        <v>-7.27</v>
+        <v>-3.21</v>
       </c>
       <c r="L4">
-        <v>-31.76</v>
+        <v>-30.19</v>
       </c>
       <c r="M4">
-        <v>-5.96</v>
+        <v>-5.56</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>539.63</v>
+        <v>539.3099999999999</v>
       </c>
       <c r="Q4">
-        <v>542</v>
+        <v>542.3200000000001</v>
       </c>
       <c r="R4">
-        <v>553.15</v>
+        <v>552.37</v>
       </c>
       <c r="S4">
-        <v>642.66</v>
+        <v>641.58</v>
       </c>
       <c r="T4">
-        <v>-16.99</v>
+        <v>-14.84</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1177,43 +1201,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.71</v>
+        <v>50.38</v>
       </c>
       <c r="Z4">
-        <v>-3.67</v>
+        <v>-3.04</v>
       </c>
       <c r="AA4">
-        <v>-3.35</v>
+        <v>-3.29</v>
       </c>
       <c r="AB4">
-        <v>-0.32</v>
+        <v>0.25</v>
       </c>
       <c r="AC4">
-        <v>15.23</v>
+        <v>27.74</v>
       </c>
       <c r="AD4">
-        <v>32.18</v>
+        <v>24.41</v>
       </c>
       <c r="AE4">
-        <v>9.51</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AF4">
-        <v>-50.5</v>
+        <v>148.69</v>
       </c>
       <c r="AG4">
-        <v>555.2</v>
+        <v>555.62</v>
       </c>
       <c r="AH4">
-        <v>528.8099999999999</v>
+        <v>529.02</v>
       </c>
       <c r="AI4">
         <v>563.65</v>
       </c>
       <c r="AJ4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK4">
-        <v>23.58</v>
+        <v>22.17</v>
       </c>
     </row>
   </sheetData>
@@ -1364,7 +1388,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1374,12 +1398,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1387,428 +1446,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-1.19</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-2</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.8100000000000001</v>
+      <c r="D7" s="6">
+        <v>-3.14</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-5.55</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-3.86</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.69</v>
+      <c r="D8" s="6">
+        <v>-3.02</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-0.55</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-2.11</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.56</v>
+      <c r="D9" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.83</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-5.33</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-2.49</v>
       </c>
+      <c r="D10" s="6">
+        <v>-4.31</v>
+      </c>
       <c r="E10" s="7">
-        <v>2.84</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-3.63</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-0.61</v>
       </c>
+      <c r="D11" s="6">
+        <v>-1.14</v>
+      </c>
       <c r="E11" s="7">
-        <v>3.02</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-3.62</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-2.65</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.97</v>
+      <c r="D12" s="6">
+        <v>-0.29</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.36</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="6">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-9.16</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-25.66</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-24.61</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-31.76</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-30.19</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-5.41</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.59</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-7.27</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-3.21</v>
+      </c>
+      <c r="E18" s="8">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-12.78</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-14.61</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-30</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-29.46</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-32.28</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-30.64</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2510.8</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2458.3</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-52.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>706.65</v>
+      </c>
+      <c r="D23" s="6">
+        <v>712.1</v>
+      </c>
+      <c r="E23" s="8">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>533.5</v>
+      </c>
+      <c r="D24" s="6">
+        <v>546.4</v>
+      </c>
+      <c r="E24" s="8">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>43</v>
+      </c>
+      <c r="D25" s="6">
+        <v>38.64</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-4.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>35.72</v>
+      </c>
+      <c r="D26" s="6">
+        <v>39.85</v>
+      </c>
+      <c r="E26" s="8">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>39.71</v>
+      </c>
+      <c r="D27" s="6">
+        <v>50.38</v>
+      </c>
+      <c r="E27" s="8">
+        <v>10.67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-11.19</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="E28" s="8">
+        <v>10.84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
         <v>-5.51</v>
       </c>
-      <c r="D13" s="5">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-26.36</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-25.66</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D29" s="6">
+        <v>-47.89</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-42.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-30.96</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-31.76</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2.3</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-7.08</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-5.41</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-7.1</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-7.27</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-12.26</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-12.78</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-30.58</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-30</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-32.34</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-32.28</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2525.7</v>
-      </c>
-      <c r="D22" s="5">
-        <v>2510.8</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-14.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>700.8</v>
-      </c>
-      <c r="D23" s="5">
-        <v>706.65</v>
-      </c>
-      <c r="E23" s="7">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>533</v>
-      </c>
-      <c r="D24" s="5">
-        <v>533.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>44.32</v>
-      </c>
-      <c r="D25" s="5">
-        <v>43</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>30.99</v>
-      </c>
-      <c r="D26" s="5">
-        <v>35.72</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4.73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>39.23</v>
-      </c>
-      <c r="D27" s="5">
-        <v>39.71</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>14.07</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-11.19</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-25.26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>27.04</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-5.51</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-32.55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-64.34</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-50.5</v>
       </c>
-      <c r="E30" s="7">
-        <v>13.84</v>
+      <c r="D30" s="6">
+        <v>148.69</v>
+      </c>
+      <c r="E30" s="8">
+        <v>199.19</v>
       </c>
     </row>
   </sheetData>
@@ -1834,60 +1893,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>39.5</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>43</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-2.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-1.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1989,25 +2048,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.12</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0117</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0596</v>
+      <c r="A2" s="14">
+        <v>0.1136</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0089</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0556</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -175,16 +175,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>39.7 → 50.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>39.7</t>
+    <t>50.4 → 42.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.4</t>
+  </si>
+  <si>
+    <t>42.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -396,8 +396,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -769,7 +769,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -909,10 +911,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2458.3</v>
+        <v>2432</v>
       </c>
       <c r="D2">
-        <v>-2.09</v>
+        <v>-1.07</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -921,46 +923,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-14.61</v>
+        <v>-15.52</v>
       </c>
       <c r="H2">
-        <v>13.34</v>
+        <v>12.13</v>
       </c>
       <c r="I2">
-        <v>-4.31</v>
+        <v>-7.25</v>
       </c>
       <c r="J2">
-        <v>-3.14</v>
+        <v>-4.44</v>
       </c>
       <c r="K2">
-        <v>0.22</v>
+        <v>-2.85</v>
       </c>
       <c r="L2">
-        <v>-9.16</v>
+        <v>-11.2</v>
       </c>
       <c r="M2">
-        <v>11.36</v>
+        <v>11.56</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P2">
-        <v>2532.36</v>
+        <v>2494.34</v>
       </c>
       <c r="Q2">
-        <v>2558.64</v>
+        <v>2552.24</v>
       </c>
       <c r="R2">
-        <v>2604.39</v>
+        <v>2600.9</v>
       </c>
       <c r="S2">
-        <v>2576.87</v>
+        <v>2575.84</v>
       </c>
       <c r="T2">
-        <v>-4.6</v>
+        <v>-5.58</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,43 +977,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>38.64</v>
+        <v>36.63</v>
       </c>
       <c r="Z2">
-        <v>-15.48</v>
+        <v>-23.84</v>
       </c>
       <c r="AA2">
-        <v>-4.79</v>
+        <v>-8.6</v>
       </c>
       <c r="AB2">
-        <v>-10.69</v>
+        <v>-15.24</v>
       </c>
       <c r="AC2">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>19.3</v>
+        <v>7.52</v>
       </c>
       <c r="AE2">
-        <v>63.66</v>
+        <v>62.08</v>
       </c>
       <c r="AF2">
-        <v>-0.35</v>
+        <v>-65.48999999999999</v>
       </c>
       <c r="AG2">
-        <v>2686.64</v>
+        <v>2692.19</v>
       </c>
       <c r="AH2">
-        <v>2430.65</v>
+        <v>2412.3</v>
       </c>
       <c r="AI2">
-        <v>2677.88</v>
+        <v>2639.05</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>21.6</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +1024,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>712.1</v>
+        <v>710.5</v>
       </c>
       <c r="D3">
-        <v>0.77</v>
+        <v>-0.22</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1034,46 +1036,46 @@
         <v>700.8</v>
       </c>
       <c r="G3">
-        <v>-29.46</v>
+        <v>-29.62</v>
       </c>
       <c r="H3">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="I3">
-        <v>-1.14</v>
+        <v>0.21</v>
       </c>
       <c r="J3">
-        <v>-3.02</v>
+        <v>-2.8</v>
       </c>
       <c r="K3">
-        <v>-3.59</v>
+        <v>-3.77</v>
       </c>
       <c r="L3">
-        <v>-24.61</v>
+        <v>-25.56</v>
       </c>
       <c r="M3">
-        <v>-0.89</v>
+        <v>-0.98</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P3">
-        <v>708.09</v>
+        <v>708.39</v>
       </c>
       <c r="Q3">
-        <v>721.02</v>
+        <v>720</v>
       </c>
       <c r="R3">
-        <v>755.92</v>
+        <v>754.15</v>
       </c>
       <c r="S3">
-        <v>839.62</v>
+        <v>838.2</v>
       </c>
       <c r="T3">
-        <v>-15.19</v>
+        <v>-15.24</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,34 +1090,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>39.85</v>
+        <v>39.06</v>
       </c>
       <c r="Z3">
-        <v>-11.66</v>
+        <v>-11.21</v>
       </c>
       <c r="AA3">
-        <v>-11.91</v>
+        <v>-11.77</v>
       </c>
       <c r="AB3">
-        <v>0.25</v>
+        <v>0.57</v>
       </c>
       <c r="AC3">
-        <v>56.66</v>
+        <v>83.88</v>
       </c>
       <c r="AD3">
-        <v>44.51</v>
+        <v>61.13</v>
       </c>
       <c r="AE3">
-        <v>12.29</v>
+        <v>11.84</v>
       </c>
       <c r="AF3">
-        <v>-47.89</v>
+        <v>-53.84</v>
       </c>
       <c r="AG3">
-        <v>739.1799999999999</v>
+        <v>738.1</v>
       </c>
       <c r="AH3">
-        <v>702.87</v>
+        <v>701.9</v>
       </c>
       <c r="AI3">
         <v>740.42</v>
@@ -1124,7 +1126,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>26.77</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1137,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>546.4</v>
+        <v>533.2</v>
       </c>
       <c r="D4">
-        <v>2.42</v>
+        <v>-2.42</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1147,46 +1149,46 @@
         <v>533</v>
       </c>
       <c r="G4">
-        <v>-30.64</v>
+        <v>-32.32</v>
       </c>
       <c r="H4">
-        <v>2.51</v>
+        <v>0.04</v>
       </c>
       <c r="I4">
-        <v>-0.29</v>
+        <v>-1.87</v>
       </c>
       <c r="J4">
-        <v>0.72</v>
+        <v>-1.26</v>
       </c>
       <c r="K4">
-        <v>-3.21</v>
+        <v>-4.89</v>
       </c>
       <c r="L4">
-        <v>-30.19</v>
+        <v>-31.33</v>
       </c>
       <c r="M4">
-        <v>-5.56</v>
+        <v>-5.97</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>539.3099999999999</v>
+        <v>537.28</v>
       </c>
       <c r="Q4">
-        <v>542.3200000000001</v>
+        <v>541.98</v>
       </c>
       <c r="R4">
-        <v>552.37</v>
+        <v>551.37</v>
       </c>
       <c r="S4">
-        <v>641.58</v>
+        <v>640.4400000000001</v>
       </c>
       <c r="T4">
-        <v>-14.84</v>
+        <v>-16.74</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,34 +1203,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>50.38</v>
+        <v>42.16</v>
       </c>
       <c r="Z4">
-        <v>-3.04</v>
+        <v>-3.56</v>
       </c>
       <c r="AA4">
-        <v>-3.29</v>
+        <v>-3.34</v>
       </c>
       <c r="AB4">
-        <v>0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AC4">
-        <v>27.74</v>
+        <v>31.72</v>
       </c>
       <c r="AD4">
-        <v>24.41</v>
+        <v>24.9</v>
       </c>
       <c r="AE4">
-        <v>9.880000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="AF4">
-        <v>148.69</v>
+        <v>-53.88</v>
       </c>
       <c r="AG4">
-        <v>555.62</v>
+        <v>555.87</v>
       </c>
       <c r="AH4">
-        <v>529.02</v>
+        <v>528.1</v>
       </c>
       <c r="AI4">
         <v>563.65</v>
@@ -1237,7 +1239,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>22.17</v>
+        <v>20.89</v>
       </c>
     </row>
   </sheetData>
@@ -1470,13 +1472,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-2</v>
+        <v>-3.14</v>
       </c>
       <c r="D7" s="6">
-        <v>-3.14</v>
+        <v>-4.44</v>
       </c>
       <c r="E7" s="7">
-        <v>-1.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1487,13 +1489,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-3.86</v>
+        <v>-3.02</v>
       </c>
       <c r="D8" s="6">
-        <v>-3.02</v>
+        <v>-2.8</v>
       </c>
       <c r="E8" s="8">
-        <v>0.84</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1504,13 +1506,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.11</v>
+        <v>0.72</v>
       </c>
       <c r="D9" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.83</v>
+        <v>-1.26</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1521,13 +1523,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.49</v>
+        <v>-4.31</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.31</v>
+        <v>-7.25</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.82</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1538,13 +1540,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.61</v>
+        <v>-1.14</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.53</v>
+        <v>0.21</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.35</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1555,13 +1557,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.65</v>
+        <v>-0.29</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.29</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2.36</v>
+        <v>-1.87</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1572,13 +1574,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-8.029999999999999</v>
+        <v>-9.16</v>
       </c>
       <c r="D13" s="6">
-        <v>-9.16</v>
+        <v>-11.2</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.13</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1589,13 +1591,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-25.66</v>
+        <v>-24.61</v>
       </c>
       <c r="D14" s="6">
-        <v>-24.61</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.05</v>
+        <v>-25.56</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1606,13 +1608,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-31.76</v>
+        <v>-30.19</v>
       </c>
       <c r="D15" s="6">
-        <v>-30.19</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.57</v>
+        <v>-31.33</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1623,13 +1625,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>0.6</v>
+        <v>0.22</v>
       </c>
       <c r="D16" s="6">
-        <v>0.22</v>
+        <v>-2.85</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.38</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1640,13 +1642,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.41</v>
+        <v>-3.59</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.59</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.82</v>
+        <v>-3.77</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1657,13 +1659,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-7.27</v>
+        <v>-3.21</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.21</v>
-      </c>
-      <c r="E18" s="8">
-        <v>4.06</v>
+        <v>-4.89</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1674,13 +1676,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-12.78</v>
+        <v>-14.61</v>
       </c>
       <c r="D19" s="6">
-        <v>-14.61</v>
+        <v>-15.52</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.83</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1691,13 +1693,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-30</v>
+        <v>-29.46</v>
       </c>
       <c r="D20" s="6">
-        <v>-29.46</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.54</v>
+        <v>-29.62</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1708,13 +1710,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-32.28</v>
+        <v>-30.64</v>
       </c>
       <c r="D21" s="6">
-        <v>-30.64</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.64</v>
+        <v>-32.32</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1725,13 +1727,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>2510.8</v>
+        <v>2458.3</v>
       </c>
       <c r="D22" s="6">
-        <v>2458.3</v>
+        <v>2432</v>
       </c>
       <c r="E22" s="7">
-        <v>-52.5</v>
+        <v>-26.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1742,13 +1744,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>706.65</v>
+        <v>712.1</v>
       </c>
       <c r="D23" s="6">
-        <v>712.1</v>
-      </c>
-      <c r="E23" s="8">
-        <v>5.45</v>
+        <v>710.5</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1759,13 +1761,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>533.5</v>
+        <v>546.4</v>
       </c>
       <c r="D24" s="6">
-        <v>546.4</v>
-      </c>
-      <c r="E24" s="8">
-        <v>12.9</v>
+        <v>533.2</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-13.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1776,13 +1778,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>43</v>
+        <v>38.64</v>
       </c>
       <c r="D25" s="6">
-        <v>38.64</v>
+        <v>36.63</v>
       </c>
       <c r="E25" s="7">
-        <v>-4.36</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1793,13 +1795,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>35.72</v>
+        <v>39.85</v>
       </c>
       <c r="D26" s="6">
-        <v>39.85</v>
-      </c>
-      <c r="E26" s="8">
-        <v>4.13</v>
+        <v>39.06</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1810,13 +1812,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>39.71</v>
+        <v>50.38</v>
       </c>
       <c r="D27" s="6">
-        <v>50.38</v>
-      </c>
-      <c r="E27" s="8">
-        <v>10.67</v>
+        <v>42.16</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-8.220000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1827,13 +1829,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-11.19</v>
+        <v>-0.35</v>
       </c>
       <c r="D28" s="6">
-        <v>-0.35</v>
-      </c>
-      <c r="E28" s="8">
-        <v>10.84</v>
+        <v>-65.48999999999999</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-65.14</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1844,13 +1846,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>-5.51</v>
+        <v>-47.89</v>
       </c>
       <c r="D29" s="6">
-        <v>-47.89</v>
+        <v>-53.84</v>
       </c>
       <c r="E29" s="7">
-        <v>-42.38</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1861,13 +1863,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-50.5</v>
+        <v>148.69</v>
       </c>
       <c r="D30" s="6">
-        <v>148.69</v>
-      </c>
-      <c r="E30" s="8">
-        <v>199.19</v>
+        <v>-53.88</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-202.57</v>
       </c>
     </row>
   </sheetData>
@@ -1932,16 +1934,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>43</v>
+        <v>39.3</v>
       </c>
       <c r="E2" s="11">
         <v>0</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.8</v>
+        <v>-2.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-2.2</v>
+        <v>-3.8</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2060,13 +2062,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1136</v>
+        <v>0.1156</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0089</v>
+        <v>-0.0098</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0556</v>
+        <v>-0.0597</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.4 → 42.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>42.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -769,9 +741,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -911,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2432</v>
+        <v>2447.3</v>
       </c>
       <c r="D2">
-        <v>-1.07</v>
+        <v>0.63</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -923,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-15.52</v>
+        <v>-14.99</v>
       </c>
       <c r="H2">
-        <v>12.13</v>
+        <v>12.83</v>
       </c>
       <c r="I2">
-        <v>-7.25</v>
+        <v>-3.84</v>
       </c>
       <c r="J2">
-        <v>-4.44</v>
+        <v>-4.4</v>
       </c>
       <c r="K2">
-        <v>-2.85</v>
+        <v>-0.02</v>
       </c>
       <c r="L2">
-        <v>-11.2</v>
+        <v>-10.2</v>
       </c>
       <c r="M2">
-        <v>11.56</v>
+        <v>10.71</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P2">
-        <v>2494.34</v>
+        <v>2474.82</v>
       </c>
       <c r="Q2">
-        <v>2552.24</v>
+        <v>2548.86</v>
       </c>
       <c r="R2">
-        <v>2600.9</v>
+        <v>2596.78</v>
       </c>
       <c r="S2">
-        <v>2575.84</v>
+        <v>2574.87</v>
       </c>
       <c r="T2">
-        <v>-5.58</v>
+        <v>-4.95</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -977,43 +947,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>36.63</v>
+        <v>38.63</v>
       </c>
       <c r="Z2">
-        <v>-23.84</v>
+        <v>-28.9</v>
       </c>
       <c r="AA2">
-        <v>-8.6</v>
+        <v>-12.66</v>
       </c>
       <c r="AB2">
-        <v>-15.24</v>
+        <v>-16.24</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD2">
-        <v>7.52</v>
+        <v>3.07</v>
       </c>
       <c r="AE2">
-        <v>62.08</v>
+        <v>59.22</v>
       </c>
       <c r="AF2">
-        <v>-65.48999999999999</v>
+        <v>-36.62</v>
       </c>
       <c r="AG2">
-        <v>2692.19</v>
+        <v>2695.71</v>
       </c>
       <c r="AH2">
-        <v>2412.3</v>
+        <v>2402.01</v>
       </c>
       <c r="AI2">
-        <v>2639.05</v>
+        <v>2621.16</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>23.26</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1024,10 +994,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>710.5</v>
+        <v>703</v>
       </c>
       <c r="D3">
-        <v>-0.22</v>
+        <v>-1.06</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1036,46 +1006,46 @@
         <v>700.8</v>
       </c>
       <c r="G3">
-        <v>-29.62</v>
+        <v>-30.36</v>
       </c>
       <c r="H3">
-        <v>1.38</v>
+        <v>0.31</v>
       </c>
       <c r="I3">
-        <v>0.21</v>
+        <v>-1.25</v>
       </c>
       <c r="J3">
-        <v>-2.8</v>
+        <v>-3.83</v>
       </c>
       <c r="K3">
-        <v>-3.77</v>
+        <v>-5.87</v>
       </c>
       <c r="L3">
-        <v>-25.56</v>
+        <v>-26.87</v>
       </c>
       <c r="M3">
-        <v>-0.98</v>
+        <v>-1.28</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>708.39</v>
+        <v>706.61</v>
       </c>
       <c r="Q3">
-        <v>720</v>
+        <v>718.7</v>
       </c>
       <c r="R3">
-        <v>754.15</v>
+        <v>752.25</v>
       </c>
       <c r="S3">
-        <v>838.2</v>
+        <v>836.67</v>
       </c>
       <c r="T3">
-        <v>-15.24</v>
+        <v>-15.98</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1090,34 +1060,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>39.06</v>
+        <v>35.49</v>
       </c>
       <c r="Z3">
-        <v>-11.21</v>
+        <v>-11.32</v>
       </c>
       <c r="AA3">
-        <v>-11.77</v>
+        <v>-11.68</v>
       </c>
       <c r="AB3">
-        <v>0.57</v>
+        <v>0.36</v>
       </c>
       <c r="AC3">
-        <v>83.88</v>
+        <v>82.53</v>
       </c>
       <c r="AD3">
-        <v>61.13</v>
+        <v>74.36</v>
       </c>
       <c r="AE3">
-        <v>11.84</v>
+        <v>11.53</v>
       </c>
       <c r="AF3">
-        <v>-53.84</v>
+        <v>-23.64</v>
       </c>
       <c r="AG3">
-        <v>738.1</v>
+        <v>737.78</v>
       </c>
       <c r="AH3">
-        <v>701.9</v>
+        <v>699.61</v>
       </c>
       <c r="AI3">
         <v>740.42</v>
@@ -1126,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>25.14</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1137,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>533.2</v>
+        <v>533.8</v>
       </c>
       <c r="D4">
-        <v>-2.42</v>
+        <v>0.11</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1149,46 +1119,46 @@
         <v>533</v>
       </c>
       <c r="G4">
-        <v>-32.32</v>
+        <v>-32.24</v>
       </c>
       <c r="H4">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="I4">
-        <v>-1.87</v>
+        <v>-1.2</v>
       </c>
       <c r="J4">
-        <v>-1.26</v>
+        <v>-1.15</v>
       </c>
       <c r="K4">
-        <v>-4.89</v>
+        <v>-2.87</v>
       </c>
       <c r="L4">
-        <v>-31.33</v>
+        <v>-29.23</v>
       </c>
       <c r="M4">
-        <v>-5.97</v>
+        <v>-6.19</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>537.28</v>
+        <v>535.98</v>
       </c>
       <c r="Q4">
-        <v>541.98</v>
+        <v>541.87</v>
       </c>
       <c r="R4">
-        <v>551.37</v>
+        <v>550.53</v>
       </c>
       <c r="S4">
-        <v>640.4400000000001</v>
+        <v>639.3</v>
       </c>
       <c r="T4">
-        <v>-16.74</v>
+        <v>-16.5</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1203,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>42.16</v>
+        <v>42.61</v>
       </c>
       <c r="Z4">
-        <v>-3.56</v>
+        <v>-3.88</v>
       </c>
       <c r="AA4">
-        <v>-3.34</v>
+        <v>-3.45</v>
       </c>
       <c r="AB4">
-        <v>-0.22</v>
+        <v>-0.43</v>
       </c>
       <c r="AC4">
-        <v>31.72</v>
+        <v>38.06</v>
       </c>
       <c r="AD4">
-        <v>24.9</v>
+        <v>32.51</v>
       </c>
       <c r="AE4">
-        <v>10.12</v>
+        <v>10.44</v>
       </c>
       <c r="AF4">
-        <v>-53.88</v>
+        <v>22.75</v>
       </c>
       <c r="AG4">
-        <v>555.87</v>
+        <v>555.99</v>
       </c>
       <c r="AH4">
-        <v>528.1</v>
+        <v>527.76</v>
       </c>
       <c r="AI4">
         <v>563.65</v>
@@ -1239,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>20.89</v>
+        <v>20.43</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1400,47 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1448,428 +1383,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-3.14</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-4.44</v>
       </c>
-      <c r="E7" s="7">
-        <v>-1.3</v>
+      <c r="D7" s="5">
+        <v>-4.4</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.04</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-3.02</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-2.8</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.22</v>
+      <c r="D8" s="5">
+        <v>-3.83</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-1.26</v>
       </c>
-      <c r="E9" s="7">
-        <v>-1.98</v>
+      <c r="D9" s="5">
+        <v>-1.15</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.11</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-4.31</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-7.25</v>
       </c>
-      <c r="E10" s="7">
-        <v>-2.94</v>
+      <c r="D10" s="5">
+        <v>-3.84</v>
+      </c>
+      <c r="E10" s="6">
+        <v>3.41</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>0.21</v>
       </c>
-      <c r="E11" s="8">
-        <v>1.35</v>
+      <c r="D11" s="5">
+        <v>-1.25</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-0.29</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-1.87</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.58</v>
+      <c r="D12" s="5">
+        <v>-1.2</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.67</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-9.16</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-11.2</v>
       </c>
-      <c r="E13" s="7">
-        <v>-2.04</v>
+      <c r="D13" s="5">
+        <v>-10.2</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-24.61</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-25.56</v>
       </c>
+      <c r="D14" s="5">
+        <v>-26.87</v>
+      </c>
       <c r="E14" s="7">
-        <v>-0.95</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-30.19</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-31.33</v>
       </c>
-      <c r="E15" s="7">
-        <v>-1.14</v>
+      <c r="D15" s="5">
+        <v>-29.23</v>
+      </c>
+      <c r="E15" s="6">
+        <v>2.1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-2.85</v>
       </c>
-      <c r="E16" s="7">
-        <v>-3.07</v>
+      <c r="D16" s="5">
+        <v>-0.02</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2.83</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-3.59</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-3.77</v>
       </c>
+      <c r="D17" s="5">
+        <v>-5.87</v>
+      </c>
       <c r="E17" s="7">
-        <v>-0.18</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-3.21</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-4.89</v>
       </c>
-      <c r="E18" s="7">
-        <v>-1.68</v>
+      <c r="D18" s="5">
+        <v>-2.87</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.02</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-14.61</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-15.52</v>
       </c>
-      <c r="E19" s="7">
-        <v>-0.91</v>
+      <c r="D19" s="5">
+        <v>-14.99</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.53</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-29.46</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-29.62</v>
       </c>
+      <c r="D20" s="5">
+        <v>-30.36</v>
+      </c>
       <c r="E20" s="7">
-        <v>-0.16</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-30.64</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-32.32</v>
       </c>
-      <c r="E21" s="7">
-        <v>-1.68</v>
+      <c r="D21" s="5">
+        <v>-32.24</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.08</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>2458.3</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>2432</v>
       </c>
-      <c r="E22" s="7">
-        <v>-26.3</v>
+      <c r="D22" s="5">
+        <v>2447.3</v>
+      </c>
+      <c r="E22" s="6">
+        <v>15.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>712.1</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>710.5</v>
       </c>
+      <c r="D23" s="5">
+        <v>703</v>
+      </c>
       <c r="E23" s="7">
-        <v>-1.6</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>546.4</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>533.2</v>
       </c>
-      <c r="E24" s="7">
-        <v>-13.2</v>
+      <c r="D24" s="5">
+        <v>533.8</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="5">
+        <v>66</v>
+      </c>
+      <c r="D25" s="5">
+        <v>34</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="5">
+        <v>34</v>
+      </c>
+      <c r="D26" s="5">
+        <v>66</v>
+      </c>
+      <c r="E26" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>38.64</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C27" s="5">
         <v>36.63</v>
       </c>
-      <c r="E25" s="7">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D27" s="5">
+        <v>38.63</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>39.85</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C28" s="5">
         <v>39.06</v>
       </c>
-      <c r="E26" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D28" s="5">
+        <v>35.49</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>50.38</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C29" s="5">
         <v>42.16</v>
       </c>
-      <c r="E27" s="7">
-        <v>-8.220000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="D29" s="5">
+        <v>42.61</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-0.35</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C30" s="5">
         <v>-65.48999999999999</v>
       </c>
-      <c r="E28" s="7">
-        <v>-65.14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="D30" s="5">
+        <v>-36.62</v>
+      </c>
+      <c r="E30" s="6">
+        <v>28.87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-47.89</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C31" s="5">
         <v>-53.84</v>
       </c>
-      <c r="E29" s="7">
-        <v>-5.95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="D31" s="5">
+        <v>-23.64</v>
+      </c>
+      <c r="E31" s="6">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>148.69</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C32" s="5">
         <v>-53.88</v>
       </c>
-      <c r="E30" s="7">
-        <v>-202.57</v>
+      <c r="D32" s="5">
+        <v>22.75</v>
+      </c>
+      <c r="E32" s="6">
+        <v>76.63</v>
       </c>
     </row>
   </sheetData>
@@ -1895,60 +1864,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-2.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-3.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-3.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-2.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2050,25 +2019,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1156</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0098</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0597</v>
+      <c r="A2" s="13">
+        <v>0.1071</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0128</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0619</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -881,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2447.3</v>
+        <v>2440</v>
       </c>
       <c r="D2">
-        <v>0.63</v>
+        <v>-0.3</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -893,46 +893,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-14.99</v>
+        <v>-15.24</v>
       </c>
       <c r="H2">
-        <v>12.83</v>
+        <v>12.5</v>
       </c>
       <c r="I2">
-        <v>-3.84</v>
+        <v>-3.39</v>
       </c>
       <c r="J2">
-        <v>-4.4</v>
+        <v>-2.98</v>
       </c>
       <c r="K2">
-        <v>-0.02</v>
+        <v>2.1</v>
       </c>
       <c r="L2">
-        <v>-10.2</v>
+        <v>-10.51</v>
       </c>
       <c r="M2">
-        <v>10.71</v>
+        <v>10.77</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="P2">
-        <v>2474.82</v>
+        <v>2457.68</v>
       </c>
       <c r="Q2">
-        <v>2548.86</v>
+        <v>2546.36</v>
       </c>
       <c r="R2">
-        <v>2596.78</v>
+        <v>2590.67</v>
       </c>
       <c r="S2">
-        <v>2574.87</v>
+        <v>2573.87</v>
       </c>
       <c r="T2">
-        <v>-4.95</v>
+        <v>-5.2</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +947,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>38.63</v>
+        <v>38.01</v>
       </c>
       <c r="Z2">
-        <v>-28.9</v>
+        <v>-33.12</v>
       </c>
       <c r="AA2">
-        <v>-12.66</v>
+        <v>-16.75</v>
       </c>
       <c r="AB2">
-        <v>-16.24</v>
+        <v>-16.37</v>
       </c>
       <c r="AC2">
-        <v>2.45</v>
+        <v>4.15</v>
       </c>
       <c r="AD2">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="AE2">
-        <v>59.22</v>
+        <v>57.59</v>
       </c>
       <c r="AF2">
-        <v>-36.62</v>
+        <v>-48.05</v>
       </c>
       <c r="AG2">
-        <v>2695.71</v>
+        <v>2699.01</v>
       </c>
       <c r="AH2">
-        <v>2402.01</v>
+        <v>2393.71</v>
       </c>
       <c r="AI2">
-        <v>2621.16</v>
+        <v>2601.42</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>24.7</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,58 +994,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>703</v>
+        <v>687.1</v>
       </c>
       <c r="D3">
-        <v>-1.06</v>
+        <v>-2.26</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
       </c>
       <c r="F3">
-        <v>700.8</v>
+        <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-30.36</v>
+        <v>-31.94</v>
       </c>
       <c r="H3">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-1.25</v>
+        <v>-1.95</v>
       </c>
       <c r="J3">
-        <v>-3.83</v>
+        <v>-5.75</v>
       </c>
       <c r="K3">
-        <v>-5.87</v>
+        <v>-7.72</v>
       </c>
       <c r="L3">
-        <v>-26.87</v>
+        <v>-28.68</v>
       </c>
       <c r="M3">
-        <v>-1.28</v>
+        <v>-1.63</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="P3">
-        <v>706.61</v>
+        <v>703.87</v>
       </c>
       <c r="Q3">
-        <v>718.7</v>
+        <v>716.6</v>
       </c>
       <c r="R3">
-        <v>752.25</v>
+        <v>750.0700000000001</v>
       </c>
       <c r="S3">
-        <v>836.67</v>
+        <v>835.12</v>
       </c>
       <c r="T3">
-        <v>-15.98</v>
+        <v>-17.72</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1060,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.49</v>
+        <v>29.36</v>
       </c>
       <c r="Z3">
-        <v>-11.32</v>
+        <v>-12.55</v>
       </c>
       <c r="AA3">
-        <v>-11.68</v>
+        <v>-11.86</v>
       </c>
       <c r="AB3">
-        <v>0.36</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AC3">
-        <v>82.53</v>
+        <v>49.2</v>
       </c>
       <c r="AD3">
-        <v>74.36</v>
+        <v>71.87</v>
       </c>
       <c r="AE3">
-        <v>11.53</v>
+        <v>11.84</v>
       </c>
       <c r="AF3">
-        <v>-23.64</v>
+        <v>51.49</v>
       </c>
       <c r="AG3">
-        <v>737.78</v>
+        <v>739.7</v>
       </c>
       <c r="AH3">
-        <v>699.61</v>
+        <v>693.5</v>
       </c>
       <c r="AI3">
-        <v>740.42</v>
+        <v>729.0700000000001</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>22.02</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,58 +1107,58 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>533.8</v>
+        <v>514</v>
       </c>
       <c r="D4">
-        <v>0.11</v>
+        <v>-3.71</v>
       </c>
       <c r="E4">
         <v>787.8</v>
       </c>
       <c r="F4">
-        <v>533</v>
+        <v>514</v>
       </c>
       <c r="G4">
-        <v>-32.24</v>
+        <v>-34.76</v>
       </c>
       <c r="H4">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.2</v>
+        <v>-3.56</v>
       </c>
       <c r="J4">
-        <v>-1.15</v>
+        <v>-4.1</v>
       </c>
       <c r="K4">
-        <v>-2.87</v>
+        <v>-5.73</v>
       </c>
       <c r="L4">
-        <v>-29.23</v>
+        <v>-32.33</v>
       </c>
       <c r="M4">
-        <v>-6.19</v>
+        <v>-6.74</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>535.98</v>
+        <v>532.1799999999999</v>
       </c>
       <c r="Q4">
-        <v>541.87</v>
+        <v>540.72</v>
       </c>
       <c r="R4">
-        <v>550.53</v>
+        <v>549.41</v>
       </c>
       <c r="S4">
-        <v>639.3</v>
+        <v>638.05</v>
       </c>
       <c r="T4">
-        <v>-16.5</v>
+        <v>-19.44</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,43 +1173,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>42.61</v>
+        <v>33.25</v>
       </c>
       <c r="Z4">
-        <v>-3.88</v>
+        <v>-5.66</v>
       </c>
       <c r="AA4">
-        <v>-3.45</v>
+        <v>-3.89</v>
       </c>
       <c r="AB4">
-        <v>-0.43</v>
+        <v>-1.77</v>
       </c>
       <c r="AC4">
-        <v>38.06</v>
+        <v>13.75</v>
       </c>
       <c r="AD4">
-        <v>32.51</v>
+        <v>27.84</v>
       </c>
       <c r="AE4">
-        <v>10.44</v>
+        <v>11.53</v>
       </c>
       <c r="AF4">
-        <v>22.75</v>
+        <v>257.38</v>
       </c>
       <c r="AG4">
-        <v>555.99</v>
+        <v>559.49</v>
       </c>
       <c r="AH4">
-        <v>527.76</v>
+        <v>521.95</v>
       </c>
       <c r="AI4">
-        <v>563.65</v>
+        <v>556.36</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>20.43</v>
+        <v>23.66</v>
       </c>
     </row>
   </sheetData>
@@ -1407,13 +1407,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.44</v>
+        <v>-4.4</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.4</v>
+        <v>-2.98</v>
       </c>
       <c r="E7" s="6">
-        <v>0.04</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1424,13 +1424,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.8</v>
+        <v>-3.83</v>
       </c>
       <c r="D8" s="5">
-        <v>-3.83</v>
+        <v>-5.75</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.03</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1441,13 +1441,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-1.26</v>
+        <v>-1.15</v>
       </c>
       <c r="D9" s="5">
-        <v>-1.15</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.11</v>
+        <v>-4.1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1458,13 +1458,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-7.25</v>
+        <v>-3.84</v>
       </c>
       <c r="D10" s="5">
-        <v>-3.84</v>
+        <v>-3.39</v>
       </c>
       <c r="E10" s="6">
-        <v>3.41</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1475,13 +1475,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>0.21</v>
+        <v>-1.25</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.25</v>
+        <v>-1.95</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.46</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1492,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-1.87</v>
+        <v>-1.2</v>
       </c>
       <c r="D12" s="5">
-        <v>-1.2</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.67</v>
+        <v>-3.56</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.36</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1509,13 +1509,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-11.2</v>
+        <v>-10.2</v>
       </c>
       <c r="D13" s="5">
-        <v>-10.2</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1</v>
+        <v>-10.51</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1526,13 +1526,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-25.56</v>
+        <v>-26.87</v>
       </c>
       <c r="D14" s="5">
-        <v>-26.87</v>
+        <v>-28.68</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.31</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1543,13 +1543,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-31.33</v>
+        <v>-29.23</v>
       </c>
       <c r="D15" s="5">
-        <v>-29.23</v>
-      </c>
-      <c r="E15" s="6">
-        <v>2.1</v>
+        <v>-32.33</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1560,13 +1560,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>-2.85</v>
+        <v>-0.02</v>
       </c>
       <c r="D16" s="5">
-        <v>-0.02</v>
+        <v>2.1</v>
       </c>
       <c r="E16" s="6">
-        <v>2.83</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1577,13 +1577,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-3.77</v>
+        <v>-5.87</v>
       </c>
       <c r="D17" s="5">
-        <v>-5.87</v>
+        <v>-7.72</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.1</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1594,13 +1594,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-4.89</v>
+        <v>-2.87</v>
       </c>
       <c r="D18" s="5">
-        <v>-2.87</v>
-      </c>
-      <c r="E18" s="6">
-        <v>2.02</v>
+        <v>-5.73</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.86</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1611,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-15.52</v>
+        <v>-14.99</v>
       </c>
       <c r="D19" s="5">
-        <v>-14.99</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.53</v>
+        <v>-15.24</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1628,13 +1628,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-29.62</v>
+        <v>-30.36</v>
       </c>
       <c r="D20" s="5">
-        <v>-30.36</v>
+        <v>-31.94</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.74</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1645,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-32.32</v>
+        <v>-32.24</v>
       </c>
       <c r="D21" s="5">
-        <v>-32.24</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.08</v>
+        <v>-34.76</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.52</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1662,13 +1662,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>2432</v>
+        <v>2447.3</v>
       </c>
       <c r="D22" s="5">
-        <v>2447.3</v>
-      </c>
-      <c r="E22" s="6">
-        <v>15.3</v>
+        <v>2440</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-7.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1679,13 +1679,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>710.5</v>
+        <v>703</v>
       </c>
       <c r="D23" s="5">
-        <v>703</v>
+        <v>687.1</v>
       </c>
       <c r="E23" s="7">
-        <v>-7.5</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1696,13 +1696,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>533.2</v>
+        <v>533.8</v>
       </c>
       <c r="D24" s="5">
-        <v>533.8</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.6</v>
+        <v>514</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-19.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1713,13 +1713,13 @@
         <v>13</v>
       </c>
       <c r="C25" s="5">
+        <v>34</v>
+      </c>
+      <c r="D25" s="5">
         <v>66</v>
       </c>
-      <c r="D25" s="5">
-        <v>34</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-32</v>
+      <c r="E25" s="6">
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1730,13 +1730,13 @@
         <v>13</v>
       </c>
       <c r="C26" s="5">
+        <v>66</v>
+      </c>
+      <c r="D26" s="5">
         <v>34</v>
       </c>
-      <c r="D26" s="5">
-        <v>66</v>
-      </c>
-      <c r="E26" s="6">
-        <v>32</v>
+      <c r="E26" s="7">
+        <v>-32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1747,13 +1747,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>36.63</v>
+        <v>38.63</v>
       </c>
       <c r="D27" s="5">
-        <v>38.63</v>
-      </c>
-      <c r="E27" s="6">
-        <v>2</v>
+        <v>38.01</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1764,13 +1764,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="5">
-        <v>39.06</v>
+        <v>35.49</v>
       </c>
       <c r="D28" s="5">
-        <v>35.49</v>
+        <v>29.36</v>
       </c>
       <c r="E28" s="7">
-        <v>-3.57</v>
+        <v>-6.13</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1781,13 +1781,13 @@
         <v>24</v>
       </c>
       <c r="C29" s="5">
-        <v>42.16</v>
+        <v>42.61</v>
       </c>
       <c r="D29" s="5">
-        <v>42.61</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.45</v>
+        <v>33.25</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-9.359999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1798,13 +1798,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-65.48999999999999</v>
+        <v>-36.62</v>
       </c>
       <c r="D30" s="5">
-        <v>-36.62</v>
-      </c>
-      <c r="E30" s="6">
-        <v>28.87</v>
+        <v>-48.05</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-11.43</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1815,13 +1815,13 @@
         <v>31</v>
       </c>
       <c r="C31" s="5">
-        <v>-53.84</v>
+        <v>-23.64</v>
       </c>
       <c r="D31" s="5">
-        <v>-23.64</v>
+        <v>51.49</v>
       </c>
       <c r="E31" s="6">
-        <v>30.2</v>
+        <v>75.13</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1832,13 +1832,13 @@
         <v>31</v>
       </c>
       <c r="C32" s="5">
-        <v>-53.88</v>
+        <v>22.75</v>
       </c>
       <c r="D32" s="5">
-        <v>22.75</v>
+        <v>257.38</v>
       </c>
       <c r="E32" s="6">
-        <v>76.63</v>
+        <v>234.63</v>
       </c>
     </row>
   </sheetData>
@@ -1903,16 +1903,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>38.9</v>
+        <v>33.5</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-3.1</v>
+        <v>-4.3</v>
       </c>
       <c r="G2" s="10">
-        <v>-2.9</v>
+        <v>-3.8</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2031,13 +2031,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1071</v>
+        <v>0.1077</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0128</v>
+        <v>-0.0163</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0619</v>
+        <v>-0.0674</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,7 +157,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.4 → 34.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.4</t>
+  </si>
+  <si>
+    <t>34.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -359,14 +386,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -881,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2440</v>
+        <v>2433.8</v>
       </c>
       <c r="D2">
-        <v>-0.3</v>
+        <v>-0.25</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -893,46 +921,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-15.24</v>
+        <v>-15.46</v>
       </c>
       <c r="H2">
-        <v>12.5</v>
+        <v>12.21</v>
       </c>
       <c r="I2">
-        <v>-3.39</v>
+        <v>-3.07</v>
       </c>
       <c r="J2">
-        <v>-2.98</v>
+        <v>-2.26</v>
       </c>
       <c r="K2">
-        <v>2.1</v>
+        <v>-0.9</v>
       </c>
       <c r="L2">
-        <v>-10.51</v>
+        <v>-12.93</v>
       </c>
       <c r="M2">
-        <v>10.77</v>
+        <v>10.37</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>2457.68</v>
+        <v>2442.28</v>
       </c>
       <c r="Q2">
-        <v>2546.36</v>
+        <v>2543.07</v>
       </c>
       <c r="R2">
-        <v>2590.67</v>
+        <v>2584.15</v>
       </c>
       <c r="S2">
-        <v>2573.87</v>
+        <v>2572.9</v>
       </c>
       <c r="T2">
-        <v>-5.2</v>
+        <v>-5.41</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -947,43 +975,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>38.01</v>
+        <v>37.47</v>
       </c>
       <c r="Z2">
-        <v>-33.12</v>
+        <v>-36.54</v>
       </c>
       <c r="AA2">
-        <v>-16.75</v>
+        <v>-20.71</v>
       </c>
       <c r="AB2">
-        <v>-16.37</v>
+        <v>-15.83</v>
       </c>
       <c r="AC2">
-        <v>4.15</v>
+        <v>5.18</v>
       </c>
       <c r="AD2">
-        <v>2.2</v>
+        <v>3.93</v>
       </c>
       <c r="AE2">
-        <v>57.59</v>
+        <v>56.84</v>
       </c>
       <c r="AF2">
-        <v>-48.05</v>
+        <v>-56.36</v>
       </c>
       <c r="AG2">
-        <v>2699.01</v>
+        <v>2702.65</v>
       </c>
       <c r="AH2">
-        <v>2393.71</v>
+        <v>2383.5</v>
       </c>
       <c r="AI2">
-        <v>2601.42</v>
+        <v>2595.07</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>27.08</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -994,10 +1022,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>687.1</v>
+        <v>693.8</v>
       </c>
       <c r="D3">
-        <v>-2.26</v>
+        <v>0.98</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1006,46 +1034,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-31.94</v>
+        <v>-31.27</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I3">
-        <v>-1.95</v>
+        <v>-1.82</v>
       </c>
       <c r="J3">
-        <v>-5.75</v>
+        <v>-4.83</v>
       </c>
       <c r="K3">
-        <v>-7.72</v>
+        <v>-10.18</v>
       </c>
       <c r="L3">
-        <v>-28.68</v>
+        <v>-28.18</v>
       </c>
       <c r="M3">
-        <v>-1.63</v>
+        <v>-1.28</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P3">
-        <v>703.87</v>
+        <v>701.3</v>
       </c>
       <c r="Q3">
-        <v>716.6</v>
+        <v>715.04</v>
       </c>
       <c r="R3">
-        <v>750.0700000000001</v>
+        <v>748.03</v>
       </c>
       <c r="S3">
-        <v>835.12</v>
+        <v>833.59</v>
       </c>
       <c r="T3">
-        <v>-17.72</v>
+        <v>-16.77</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1060,43 +1088,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>29.36</v>
+        <v>34.49</v>
       </c>
       <c r="Z3">
-        <v>-12.55</v>
+        <v>-12.83</v>
       </c>
       <c r="AA3">
-        <v>-11.86</v>
+        <v>-12.05</v>
       </c>
       <c r="AB3">
-        <v>-0.6899999999999999</v>
+        <v>-0.78</v>
       </c>
       <c r="AC3">
-        <v>49.2</v>
+        <v>34.86</v>
       </c>
       <c r="AD3">
-        <v>71.87</v>
+        <v>55.53</v>
       </c>
       <c r="AE3">
-        <v>11.84</v>
+        <v>11.59</v>
       </c>
       <c r="AF3">
-        <v>51.49</v>
+        <v>2.96</v>
       </c>
       <c r="AG3">
-        <v>739.7</v>
+        <v>739.9</v>
       </c>
       <c r="AH3">
-        <v>693.5</v>
+        <v>690.1799999999999</v>
       </c>
       <c r="AI3">
-        <v>729.0700000000001</v>
+        <v>725.12</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>23.43</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1107,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>514</v>
+        <v>526.15</v>
       </c>
       <c r="D4">
-        <v>-3.71</v>
+        <v>2.36</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1119,46 +1147,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-34.76</v>
+        <v>-33.21</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="I4">
-        <v>-3.56</v>
+        <v>-1.38</v>
       </c>
       <c r="J4">
-        <v>-4.1</v>
+        <v>-2.02</v>
       </c>
       <c r="K4">
-        <v>-5.73</v>
+        <v>-5.26</v>
       </c>
       <c r="L4">
-        <v>-32.33</v>
+        <v>-30.2</v>
       </c>
       <c r="M4">
-        <v>-6.74</v>
+        <v>-6.25</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>532.1799999999999</v>
+        <v>530.71</v>
       </c>
       <c r="Q4">
-        <v>540.72</v>
+        <v>540.13</v>
       </c>
       <c r="R4">
-        <v>549.41</v>
+        <v>548.51</v>
       </c>
       <c r="S4">
-        <v>638.05</v>
+        <v>636.87</v>
       </c>
       <c r="T4">
-        <v>-19.44</v>
+        <v>-17.39</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1173,43 +1201,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.25</v>
+        <v>41.71</v>
       </c>
       <c r="Z4">
-        <v>-5.66</v>
+        <v>-6.03</v>
       </c>
       <c r="AA4">
-        <v>-3.89</v>
+        <v>-4.32</v>
       </c>
       <c r="AB4">
-        <v>-1.77</v>
+        <v>-1.71</v>
       </c>
       <c r="AC4">
-        <v>13.75</v>
+        <v>21.58</v>
       </c>
       <c r="AD4">
-        <v>27.84</v>
+        <v>24.46</v>
       </c>
       <c r="AE4">
-        <v>11.53</v>
+        <v>11.95</v>
       </c>
       <c r="AF4">
-        <v>257.38</v>
+        <v>48.22</v>
       </c>
       <c r="AG4">
-        <v>559.49</v>
+        <v>559.98</v>
       </c>
       <c r="AH4">
-        <v>521.95</v>
+        <v>520.28</v>
       </c>
       <c r="AI4">
-        <v>556.36</v>
+        <v>553.28</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>23.66</v>
+        <v>26.51</v>
       </c>
     </row>
   </sheetData>
@@ -1370,12 +1398,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1383,462 +1446,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>50</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.4</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-2.98</v>
       </c>
-      <c r="E7" s="6">
-        <v>1.42</v>
+      <c r="D7" s="6">
+        <v>-2.26</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.72</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-3.83</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-5.75</v>
       </c>
+      <c r="D8" s="6">
+        <v>-4.83</v>
+      </c>
       <c r="E8" s="7">
-        <v>-1.92</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-1.15</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-4.1</v>
       </c>
+      <c r="D9" s="6">
+        <v>-2.02</v>
+      </c>
       <c r="E9" s="7">
-        <v>-2.95</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-3.84</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-3.39</v>
       </c>
-      <c r="E10" s="6">
-        <v>0.45</v>
+      <c r="D10" s="6">
+        <v>-3.07</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-1.25</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-1.95</v>
       </c>
+      <c r="D11" s="6">
+        <v>-1.82</v>
+      </c>
       <c r="E11" s="7">
-        <v>-0.7</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-1.2</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-3.56</v>
       </c>
+      <c r="D12" s="6">
+        <v>-1.38</v>
+      </c>
       <c r="E12" s="7">
-        <v>-2.36</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-10.2</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-10.51</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.31</v>
+      <c r="D13" s="6">
+        <v>-12.93</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-26.87</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-28.68</v>
       </c>
+      <c r="D14" s="6">
+        <v>-28.18</v>
+      </c>
       <c r="E14" s="7">
-        <v>-1.81</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-29.23</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-32.33</v>
       </c>
+      <c r="D15" s="6">
+        <v>-30.2</v>
+      </c>
       <c r="E15" s="7">
-        <v>-3.1</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>-0.02</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>2.1</v>
       </c>
-      <c r="E16" s="6">
-        <v>2.12</v>
+      <c r="D16" s="6">
+        <v>-0.9</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-5.87</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-7.72</v>
       </c>
-      <c r="E17" s="7">
-        <v>-1.85</v>
+      <c r="D17" s="6">
+        <v>-10.18</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-2.87</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-5.73</v>
       </c>
+      <c r="D18" s="6">
+        <v>-5.26</v>
+      </c>
       <c r="E18" s="7">
-        <v>-2.86</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-14.99</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-15.24</v>
       </c>
-      <c r="E19" s="7">
-        <v>-0.25</v>
+      <c r="D19" s="6">
+        <v>-15.46</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-30.36</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-31.94</v>
       </c>
+      <c r="D20" s="6">
+        <v>-31.27</v>
+      </c>
       <c r="E20" s="7">
-        <v>-1.58</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-32.24</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-34.76</v>
       </c>
+      <c r="D21" s="6">
+        <v>-33.21</v>
+      </c>
       <c r="E21" s="7">
-        <v>-2.52</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>2447.3</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>2440</v>
       </c>
-      <c r="E22" s="7">
-        <v>-7.3</v>
+      <c r="D22" s="6">
+        <v>2433.8</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-6.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>703</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>687.1</v>
       </c>
+      <c r="D23" s="6">
+        <v>693.8</v>
+      </c>
       <c r="E23" s="7">
-        <v>-15.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>533.8</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>514</v>
       </c>
+      <c r="D24" s="6">
+        <v>526.15</v>
+      </c>
       <c r="E24" s="7">
-        <v>-19.8</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="6">
+        <v>66</v>
+      </c>
+      <c r="D25" s="6">
         <v>34</v>
       </c>
-      <c r="D25" s="5">
+      <c r="E25" s="8">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>34</v>
+      </c>
+      <c r="D26" s="6">
         <v>66</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E26" s="7">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>38.01</v>
+      </c>
+      <c r="D27" s="6">
+        <v>37.47</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="6">
+        <v>29.36</v>
+      </c>
+      <c r="D28" s="6">
+        <v>34.49</v>
+      </c>
+      <c r="E28" s="7">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="5">
-        <v>66</v>
-      </c>
-      <c r="D26" s="5">
-        <v>34</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="6">
+        <v>33.25</v>
+      </c>
+      <c r="D29" s="6">
+        <v>41.71</v>
+      </c>
+      <c r="E29" s="7">
+        <v>8.460000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>38.63</v>
-      </c>
-      <c r="D27" s="5">
-        <v>38.01</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-48.05</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-56.36</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-8.31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="5">
-        <v>35.49</v>
-      </c>
-      <c r="D28" s="5">
-        <v>29.36</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-6.13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
+        <v>51.49</v>
+      </c>
+      <c r="D31" s="6">
+        <v>2.96</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-48.53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="5">
-        <v>42.61</v>
-      </c>
-      <c r="D29" s="5">
-        <v>33.25</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-9.359999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-36.62</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-48.05</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-11.43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-23.64</v>
-      </c>
-      <c r="D31" s="5">
-        <v>51.49</v>
-      </c>
-      <c r="E31" s="6">
-        <v>75.13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="5">
-        <v>22.75</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C32" s="6">
         <v>257.38</v>
       </c>
-      <c r="E32" s="6">
-        <v>234.63</v>
+      <c r="D32" s="6">
+        <v>48.22</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-209.16</v>
       </c>
     </row>
   </sheetData>
@@ -1864,60 +1927,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>36.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>33.5</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>37.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <v>-4.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-3.8</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-5.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2019,25 +2082,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1077</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0163</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0674</v>
+      <c r="A2" s="14">
+        <v>0.1037</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0128</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0625</v>
       </c>
     </row>
   </sheetData>

--- a/HDFC_GROUP_Technical_Metrics.xlsx
+++ b/HDFC_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.4 → 34.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.4</t>
-  </si>
-  <si>
-    <t>34.5</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -270,14 +243,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -310,13 +283,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,15 +359,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -769,7 +741,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -909,10 +882,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>2433.8</v>
+        <v>2403.9</v>
       </c>
       <c r="D2">
-        <v>-0.25</v>
+        <v>-1.23</v>
       </c>
       <c r="E2">
         <v>2878.78</v>
@@ -921,46 +894,46 @@
         <v>2168.96</v>
       </c>
       <c r="G2">
-        <v>-15.46</v>
+        <v>-16.5</v>
       </c>
       <c r="H2">
-        <v>12.21</v>
+        <v>10.83</v>
       </c>
       <c r="I2">
-        <v>-3.07</v>
+        <v>-2.21</v>
       </c>
       <c r="J2">
-        <v>-2.26</v>
+        <v>-3.82</v>
       </c>
       <c r="K2">
-        <v>-0.9</v>
+        <v>-8.35</v>
       </c>
       <c r="L2">
-        <v>-12.93</v>
+        <v>-13.08</v>
       </c>
       <c r="M2">
-        <v>10.37</v>
+        <v>10.09</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P2">
-        <v>2442.28</v>
+        <v>2431.4</v>
       </c>
       <c r="Q2">
-        <v>2543.07</v>
+        <v>2539.02</v>
       </c>
       <c r="R2">
-        <v>2584.15</v>
+        <v>2576.23</v>
       </c>
       <c r="S2">
-        <v>2572.9</v>
+        <v>2571.87</v>
       </c>
       <c r="T2">
-        <v>-5.41</v>
+        <v>-6.53</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,43 +948,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>37.47</v>
+        <v>34.87</v>
       </c>
       <c r="Z2">
-        <v>-36.54</v>
+        <v>-41.19</v>
       </c>
       <c r="AA2">
-        <v>-20.71</v>
+        <v>-24.81</v>
       </c>
       <c r="AB2">
-        <v>-15.83</v>
+        <v>-16.39</v>
       </c>
       <c r="AC2">
-        <v>5.18</v>
+        <v>2.72</v>
       </c>
       <c r="AD2">
-        <v>3.93</v>
+        <v>4.02</v>
       </c>
       <c r="AE2">
-        <v>56.84</v>
+        <v>57.62</v>
       </c>
       <c r="AF2">
-        <v>-56.36</v>
+        <v>-17.73</v>
       </c>
       <c r="AG2">
-        <v>2702.65</v>
+        <v>2708.61</v>
       </c>
       <c r="AH2">
-        <v>2383.5</v>
+        <v>2369.43</v>
       </c>
       <c r="AI2">
-        <v>2595.07</v>
+        <v>2568.2</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>29.63</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,10 +995,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>693.8</v>
+        <v>708.25</v>
       </c>
       <c r="D3">
-        <v>0.98</v>
+        <v>2.08</v>
       </c>
       <c r="E3">
         <v>1009.5</v>
@@ -1034,46 +1007,46 @@
         <v>687.1</v>
       </c>
       <c r="G3">
-        <v>-31.27</v>
+        <v>-29.84</v>
       </c>
       <c r="H3">
-        <v>0.98</v>
+        <v>3.08</v>
       </c>
       <c r="I3">
-        <v>-1.82</v>
+        <v>-0.54</v>
       </c>
       <c r="J3">
-        <v>-4.83</v>
+        <v>-2.31</v>
       </c>
       <c r="K3">
-        <v>-10.18</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L3">
-        <v>-28.18</v>
+        <v>-26.62</v>
       </c>
       <c r="M3">
-        <v>-1.28</v>
+        <v>-0.87</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="P3">
-        <v>701.3</v>
+        <v>700.53</v>
       </c>
       <c r="Q3">
-        <v>715.04</v>
+        <v>714.1</v>
       </c>
       <c r="R3">
-        <v>748.03</v>
+        <v>746.17</v>
       </c>
       <c r="S3">
-        <v>833.59</v>
+        <v>832.1799999999999</v>
       </c>
       <c r="T3">
-        <v>-16.77</v>
+        <v>-14.89</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,34 +1061,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.49</v>
+        <v>43.95</v>
       </c>
       <c r="Z3">
-        <v>-12.83</v>
+        <v>-11.76</v>
       </c>
       <c r="AA3">
-        <v>-12.05</v>
+        <v>-11.99</v>
       </c>
       <c r="AB3">
-        <v>-0.78</v>
+        <v>0.23</v>
       </c>
       <c r="AC3">
-        <v>34.86</v>
+        <v>49.64</v>
       </c>
       <c r="AD3">
-        <v>55.53</v>
+        <v>44.57</v>
       </c>
       <c r="AE3">
-        <v>11.59</v>
+        <v>12.7</v>
       </c>
       <c r="AF3">
-        <v>2.96</v>
+        <v>19.26</v>
       </c>
       <c r="AG3">
-        <v>739.9</v>
+        <v>738.48</v>
       </c>
       <c r="AH3">
-        <v>690.1799999999999</v>
+        <v>689.73</v>
       </c>
       <c r="AI3">
         <v>725.12</v>
@@ -1124,7 +1097,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>24.84</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1108,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>526.15</v>
+        <v>530</v>
       </c>
       <c r="D4">
-        <v>2.36</v>
+        <v>0.73</v>
       </c>
       <c r="E4">
         <v>787.8</v>
@@ -1147,46 +1120,46 @@
         <v>514</v>
       </c>
       <c r="G4">
-        <v>-33.21</v>
+        <v>-32.72</v>
       </c>
       <c r="H4">
-        <v>2.36</v>
+        <v>3.11</v>
       </c>
       <c r="I4">
-        <v>-1.38</v>
+        <v>-3</v>
       </c>
       <c r="J4">
-        <v>-2.02</v>
+        <v>-1.5</v>
       </c>
       <c r="K4">
-        <v>-5.26</v>
+        <v>-8.81</v>
       </c>
       <c r="L4">
-        <v>-30.2</v>
+        <v>-30.36</v>
       </c>
       <c r="M4">
-        <v>-6.25</v>
+        <v>-6.11</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P4">
-        <v>530.71</v>
+        <v>527.4299999999999</v>
       </c>
       <c r="Q4">
-        <v>540.13</v>
+        <v>539.84</v>
       </c>
       <c r="R4">
-        <v>548.51</v>
+        <v>547.75</v>
       </c>
       <c r="S4">
-        <v>636.87</v>
+        <v>635.6900000000001</v>
       </c>
       <c r="T4">
-        <v>-17.39</v>
+        <v>-16.63</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,34 +1174,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.71</v>
+        <v>44.13</v>
       </c>
       <c r="Z4">
-        <v>-6.03</v>
+        <v>-5.94</v>
       </c>
       <c r="AA4">
-        <v>-4.32</v>
+        <v>-4.64</v>
       </c>
       <c r="AB4">
-        <v>-1.71</v>
+        <v>-1.3</v>
       </c>
       <c r="AC4">
-        <v>21.58</v>
+        <v>32.64</v>
       </c>
       <c r="AD4">
-        <v>24.46</v>
+        <v>22.65</v>
       </c>
       <c r="AE4">
-        <v>11.95</v>
+        <v>12.05</v>
       </c>
       <c r="AF4">
-        <v>48.22</v>
+        <v>44.16</v>
       </c>
       <c r="AG4">
-        <v>559.98</v>
+        <v>560.12</v>
       </c>
       <c r="AH4">
-        <v>520.28</v>
+        <v>519.55</v>
       </c>
       <c r="AI4">
         <v>553.28</v>
@@ -1237,7 +1210,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>26.51</v>
+        <v>26.43</v>
       </c>
     </row>
   </sheetData>
@@ -1398,47 +1371,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1446,462 +1384,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-2.26</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.72</v>
+      <c r="D7" s="5">
+        <v>-3.82</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.75</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-4.83</v>
       </c>
+      <c r="D8" s="5">
+        <v>-2.31</v>
+      </c>
       <c r="E8" s="7">
-        <v>0.92</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-4.1</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-2.02</v>
       </c>
+      <c r="D9" s="5">
+        <v>-1.5</v>
+      </c>
       <c r="E9" s="7">
-        <v>2.08</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-3.07</v>
       </c>
+      <c r="D10" s="5">
+        <v>-2.21</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.32</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-1.95</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-1.82</v>
       </c>
+      <c r="D11" s="5">
+        <v>-0.54</v>
+      </c>
       <c r="E11" s="7">
-        <v>0.13</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-3.56</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-1.38</v>
       </c>
-      <c r="E12" s="7">
-        <v>2.18</v>
+      <c r="D12" s="5">
+        <v>-3</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-10.51</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-12.93</v>
       </c>
-      <c r="E13" s="8">
-        <v>-2.42</v>
+      <c r="D13" s="5">
+        <v>-13.08</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-28.68</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-28.18</v>
       </c>
+      <c r="D14" s="5">
+        <v>-26.62</v>
+      </c>
       <c r="E14" s="7">
-        <v>0.5</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-32.33</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-30.2</v>
       </c>
-      <c r="E15" s="7">
-        <v>2.13</v>
+      <c r="D15" s="5">
+        <v>-30.36</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>2.1</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-0.9</v>
       </c>
-      <c r="E16" s="8">
-        <v>-3</v>
+      <c r="D16" s="5">
+        <v>-8.35</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-7.45</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-7.72</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-10.18</v>
       </c>
-      <c r="E17" s="8">
-        <v>-2.46</v>
+      <c r="D17" s="5">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-5.73</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-5.26</v>
       </c>
-      <c r="E18" s="7">
-        <v>0.47</v>
+      <c r="D18" s="5">
+        <v>-8.81</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-3.55</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-15.24</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-15.46</v>
       </c>
-      <c r="E19" s="8">
-        <v>-0.22</v>
+      <c r="D19" s="5">
+        <v>-16.5</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-31.94</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-31.27</v>
       </c>
+      <c r="D20" s="5">
+        <v>-29.84</v>
+      </c>
       <c r="E20" s="7">
-        <v>0.67</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-34.76</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-33.21</v>
       </c>
+      <c r="D21" s="5">
+        <v>-32.72</v>
+      </c>
       <c r="E21" s="7">
-        <v>1.55</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>2440</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>2433.8</v>
       </c>
-      <c r="E22" s="8">
-        <v>-6.2</v>
+      <c r="D22" s="5">
+        <v>2403.9</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-29.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>687.1</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>693.8</v>
       </c>
+      <c r="D23" s="5">
+        <v>708.25</v>
+      </c>
       <c r="E23" s="7">
-        <v>6.7</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>514</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>526.15</v>
       </c>
+      <c r="D24" s="5">
+        <v>530</v>
+      </c>
       <c r="E24" s="7">
-        <v>12.15</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
+        <v>34</v>
+      </c>
+      <c r="D25" s="5">
         <v>66</v>
       </c>
-      <c r="D25" s="6">
+      <c r="E25" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="5">
+        <v>66</v>
+      </c>
+      <c r="D26" s="5">
         <v>34</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E26" s="6">
         <v>-32</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>37.47</v>
+      </c>
+      <c r="D27" s="5">
+        <v>34.87</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="5">
+        <v>34.49</v>
+      </c>
+      <c r="D28" s="5">
+        <v>43.95</v>
+      </c>
+      <c r="E28" s="7">
+        <v>9.460000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="6">
-        <v>34</v>
-      </c>
-      <c r="D26" s="6">
-        <v>66</v>
-      </c>
-      <c r="E26" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="5">
+        <v>41.71</v>
+      </c>
+      <c r="D29" s="5">
+        <v>44.13</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>38.01</v>
-      </c>
-      <c r="D27" s="6">
-        <v>37.47</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-56.36</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-17.73</v>
+      </c>
+      <c r="E30" s="7">
+        <v>38.63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>29.36</v>
-      </c>
-      <c r="D28" s="6">
-        <v>34.49</v>
-      </c>
-      <c r="E28" s="7">
-        <v>5.13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5">
+        <v>2.96</v>
+      </c>
+      <c r="D31" s="5">
+        <v>19.26</v>
+      </c>
+      <c r="E31" s="7">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="6">
-        <v>33.25</v>
-      </c>
-      <c r="D29" s="6">
-        <v>41.71</v>
-      </c>
-      <c r="E29" s="7">
-        <v>8.460000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-48.05</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-56.36</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-8.31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>51.49</v>
-      </c>
-      <c r="D31" s="6">
-        <v>2.96</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-48.53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>257.38</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="5">
         <v>48.22</v>
       </c>
-      <c r="E32" s="8">
-        <v>-209.16</v>
+      <c r="D32" s="5">
+        <v>44.16</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-4.06</v>
       </c>
     </row>
   </sheetData>
@@ -1927,60 +1865,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>36.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>37.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>41</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-5.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-2.5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2082,25 +2020,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1037</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0128</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0625</v>
+      <c r="A2" s="13">
+        <v>0.1009</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0611</v>
       </c>
     </row>
   </sheetData>
